--- a/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-5768.xlsx
+++ b/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-5768.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E709"/>
+  <dimension ref="A1:E707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7628,11 +7628,11 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>But it's really not a monetary policy.</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C344" t="n">
         <v>2</v>
@@ -7649,7 +7649,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>But it's really not a monetary policy.</t>
+          <t>That was before inflation was really under control, but it's very interesting to look at history.</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -7670,14 +7670,14 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>That was before inflation was really under control, but it's very interesting to look at history.</t>
+          <t>And I would explain it is that inflation, which is too low, means that interest rates are lower.</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>2022</v>
       </c>
       <c r="C346" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D346" t="n">
         <v>1</v>
@@ -7691,14 +7691,14 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>And I would explain it is that inflation, which is too low, means that interest rates are lower.</t>
+          <t>As a further step towards improving the clarity of our communications, the Committee has recently decided to publish information on the participants . Assessments of the relevant monetary policy , i.e. the policy path that each participant considers most likely to promote mandate-compliant results for employment and inflation when the economy develops as expected.</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C347" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D347" t="n">
         <v>1</v>
@@ -7712,14 +7712,14 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>As a further step towards improving the clarity of our communications, the Committee has recently decided to publish information on the participants . Assessments of the relevant monetary policy , i.e. the policy path that each participant considers most likely to promote mandate-compliant results for employment and inflation when the economy develops as expected.</t>
+          <t>Unemployment has thus increased much faster for minorities and others at the lower limit of the income spectrum.</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C348" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D348" t="n">
         <v>1</v>
@@ -7733,14 +7733,14 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Unemployment has thus increased much faster for minorities and others at the lower limit of the income spectrum.</t>
+          <t>I am old enough to remember how very high inflation was.</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D349" t="n">
         <v>1</v>
@@ -7754,11 +7754,11 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>I am old enough to remember how very high inflation was.</t>
+          <t>We therefore consider maximum employment as the maximum sustainable level of employment, which means that it is not so much that it overheats the economy.</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C350" t="n">
         <v>2</v>
@@ -7775,11 +7775,11 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>We therefore consider maximum employment as the maximum sustainable level of employment, which means that it is not so much that it overheats the economy.</t>
+          <t>We have not yet seen wage growth accelerate.</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C351" t="n">
         <v>2</v>
@@ -7796,14 +7796,14 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>We have not yet seen wage growth accelerate.</t>
+          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
         <v>1</v>
@@ -7817,11 +7817,11 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
+          <t>An unexpectedly strong increase in wages or inflation could tell you that you are reaching these points.</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C353" t="n">
         <v>1</v>
@@ -7838,14 +7838,14 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>An unexpectedly strong increase in wages or inflation could tell you that you are reaching these points.</t>
+          <t>I assure you that my colleagues and I will continue to pursue monetary policy without regard for political considerations.</t>
         </is>
       </c>
       <c r="B354" t="n">
         <v>2018</v>
       </c>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D354" t="n">
         <v>1</v>
@@ -7859,14 +7859,14 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>I assure you that my colleagues and I will continue to pursue monetary policy without regard for political considerations.</t>
+          <t>The central trend in unemployment projections is slightly lower than in the March forecasts and now stands at 6.0 to 6.1 percent at the end of the year.</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D355" t="n">
         <v>1</v>
@@ -7880,14 +7880,14 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>The central trend in unemployment projections is slightly lower than in the March forecasts and now stands at 6.0 to 6.1 percent at the end of the year.</t>
+          <t>And that means that the Federal Reserve cannot add monetary adjustment by lowering short-term interest rates, the usual approach.</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -7901,7 +7901,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>And that means that the Federal Reserve cannot add monetary adjustment by lowering short-term interest rates, the usual approach.</t>
+          <t>We also do not have monetary policy to prove our independence.</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -7922,14 +7922,14 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>We also do not have monetary policy to prove our independence.</t>
+          <t>And that is – that's it again – that's going to be as short as possible on this episode and preventing unnecessary business bankruptcy, unnecessary household bankruptcy and unnecessary long-term stays of unemployment or support from them so that they can maintain their financial basis and their lives and return to work productively.</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D358" t="n">
         <v>1</v>
@@ -7943,11 +7943,11 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>And that is – that's it again – that's going to be as short as possible on this episode and preventing unnecessary business bankruptcy, unnecessary household bankruptcy and unnecessary long-term stays of unemployment or support from them so that they can maintain their financial basis and their lives and return to work productively.</t>
+          <t>In the U-6, unemployment has tripled from 7 to 21 percent.</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C359" t="n">
         <v>0</v>
@@ -7964,14 +7964,14 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>In the U-6, unemployment has tripled from 7 to 21 percent.</t>
+          <t>With regard to inflation, a few things – your second question.</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
         <v>1</v>
@@ -7985,14 +7985,14 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>With regard to inflation, a few things – your second question.</t>
+          <t>I don't think we're looking at -- I understand what you're asking, but we're looking at -- our mandate is price inflation and maximum employment, and that's what we're looking at with setting interest rates.</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C361" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D361" t="n">
         <v>1</v>
@@ -8006,14 +8006,14 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>I don't think we're looking at -- I understand what you're asking, but we're looking at -- our mandate is price inflation and maximum employment, and that's what we're looking at with setting interest rates.</t>
+          <t>So you will have different perspectives of committee participants on how fast growth will be, how quickly the labour market will heal, or how quickly – inflation will increase.</t>
         </is>
       </c>
       <c r="B362" t="n">
         <v>2019</v>
       </c>
       <c r="C362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D362" t="n">
         <v>1</v>
@@ -8027,14 +8027,14 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>So you will have different perspectives of committee participants on how fast growth will be, how quickly the labour market will heal, or how quickly – inflation will increase.</t>
+          <t>Recent lower inflation measurements have been driven significantly by the seemingly one-off price reductions of certain price categories such as wireless telephone services and prescription medicines.</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D363" t="n">
         <v>1</v>
@@ -8048,14 +8048,14 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Recent lower inflation measurements have been driven significantly by the seemingly one-off price reductions of certain price categories such as wireless telephone services and prescription medicines.</t>
+          <t>After a sharp decline in March and April, employment increased sharply in May and June, as many people returned from temporary redundancies.</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
         <v>1</v>
@@ -8069,14 +8069,14 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>After a sharp decline in March and April, employment increased sharply in May and June, as many people returned from temporary redundancies.</t>
+          <t>We believe that the economy will need a very accommodative monetary policy and the use of our instruments for a longer period of time.</t>
         </is>
       </c>
       <c r="B365" t="n">
         <v>2019</v>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -8090,11 +8090,11 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>We believe that the economy will need a very accommodative monetary policy and the use of our instruments for a longer period of time.</t>
+          <t>And you know, we haven't touched – we just touched 2 percent core inflation to select a measure – just a few months, and then we fell back.</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C366" t="n">
         <v>0</v>
@@ -8111,11 +8111,11 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>And you know, we haven't touched – we just touched 2 percent core inflation to select a measure – just a few months, and then we fell back.</t>
+          <t>The shock experienced by the pandemic in its nature, size and level of unemployment and the shock of economic activity was unprecedented.</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
@@ -8132,11 +8132,11 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>The shock experienced by the pandemic in its nature, size and level of unemployment and the shock of economic activity was unprecedented.</t>
+          <t>The Committee's forecasts and most external forecasters show growth this year and next, which is below its longer-term potential.</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C368" t="n">
         <v>0</v>
@@ -8153,14 +8153,14 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>The Committee's forecasts and most external forecasters show growth this year and next, which is below its longer-term potential.</t>
+          <t>So, and, and, you know, the shorter ones, tend to be based on, for example, gasoline prices.</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C369" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D369" t="n">
         <v>1</v>
@@ -8174,14 +8174,14 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>So, and, and, you know, the shorter ones, tend to be based on, for example, gasoline prices.</t>
+          <t>But you see growth in services, so you - this pattern around the world by Chair Powell .Press conference FINAL weak manufacturing, but growth in the far larger part of the service economy that has led to low unemployment, good job creation, rising wages, that is type of the two large parts of it that you see.</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C370" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
         <v>1</v>
@@ -8195,14 +8195,14 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>But you see growth in services, so you - this pattern around the world by Chair Powell .Press conference FINAL weak manufacturing, but growth in the far larger part of the service economy that has led to low unemployment, good job creation, rising wages, that is type of the two large parts of it that you see.</t>
+          <t>We also said that we would increase rates not only in response to very low unemployment, in the absence of inflation.</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D371" t="n">
         <v>1</v>
@@ -8216,11 +8216,11 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>We also said that we would increase rates not only in response to very low unemployment, in the absence of inflation.</t>
+          <t>And, in particular, I personally believe that the weakening is at least partially temporary and that we will see greater growth in the future.</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C372" t="n">
         <v>0</v>
@@ -8237,14 +8237,14 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>And, in particular, I personally believe that the weakening is at least partially temporary and that we will see greater growth in the future.</t>
+          <t>1 Chairman Yellen wanted to say that interest rate differentials worldwide lead to capital flows that have an impact on exchange rates. .</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D373" t="n">
         <v>1</v>
@@ -8258,11 +8258,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1 Chairman Yellen wanted to say that interest rate differentials worldwide lead to capital flows that have an impact on exchange rates. .</t>
+          <t>If we do not see that the improvement projected in the base outlook is that June 18, 2014 would be compared to the truth and the pace of the time and pace of the rate hikes would be the chairman Yellen , press conference FINAL later and more gradual.</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C374" t="n">
         <v>2</v>
@@ -8279,11 +8279,11 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>If we do not see that the improvement projected in the base outlook is that June 18, 2014 would be compared to the truth and the pace of the time and pace of the rate hikes would be the chairman Yellen , press conference FINAL later and more gradual.</t>
+          <t>So in the low 20s, and that, post May's employment report.</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="C375" t="n">
         <v>2</v>
@@ -8300,14 +8300,14 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>So in the low 20s, and that, post May's employment report.</t>
+          <t>And we were actually very concerned that growth was not enough to further reduce the unemployment rate.</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D376" t="n">
         <v>1</v>
@@ -8321,11 +8321,11 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>And we were actually very concerned that growth was not enough to further reduce the unemployment rate.</t>
+          <t>I do not really believe that asset prices themselves pose a significant threat to financial stability, because the budgets are in good financial shape when they were.</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C377" t="n">
         <v>0</v>
@@ -8342,11 +8342,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>I do not really believe that asset prices themselves pose a significant threat to financial stability, because the budgets are in good financial shape when they were.</t>
+          <t>And I think that monetary policy in a broader sense also supports household spending and housing by keeping the labour market strong, increasing workers' incomes and maintaining consumer confidence at a high level where it is currently.</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C378" t="n">
         <v>0</v>
@@ -8363,14 +8363,14 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>And I think that monetary policy in a broader sense also supports household spending and housing by keeping the labour market strong, increasing workers' incomes and maintaining consumer confidence at a high level where it is currently.</t>
+          <t>We have a much more resilient, stronger banking system, and we do not see any frightening increase in debt capital or credit growth at successive levels.1 So, you know, this is something that FOMC is paying attention to, but if you ask me, this is an important factor that monetary policy now, well, on the list of risks, it's not an important factor – it's not an important factor.</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D379" t="n">
         <v>1</v>
@@ -8384,14 +8384,14 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>We have a much more resilient, stronger banking system, and we do not see any frightening increase in debt capital or credit growth at successive levels.1 So, you know, this is something that FOMC is paying attention to, but if you ask me, this is an important factor that monetary policy now, well, on the list of risks, it's not an important factor – it's not an important factor.</t>
+          <t>So, you're right, you see -- I can't remember the number, but it could be in the 3s -- 3, 31⁄2 percent growth for next year.</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C380" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D380" t="n">
         <v>1</v>
@@ -8405,14 +8405,14 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>So, you're right, you see -- I can't remember the number, but it could be in the 3s -- 3, 31⁄2 percent growth for next year.</t>
+          <t>The American economy is very strong and well positioned to cope with a tighter monetary policy.</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D381" t="n">
         <v>1</v>
@@ -8426,14 +8426,14 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>The American economy is very strong and well positioned to cope with a tighter monetary policy.</t>
+          <t>And we have seen how significant capital outflows from these countries were under pressure on their exchange rates and concerns about their future performance.</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D382" t="n">
         <v>1</v>
@@ -8447,14 +8447,14 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>And we have seen how significant capital outflows from these countries were under pressure on their exchange rates and concerns about their future performance.</t>
+          <t>Inflationary pressures remain subdued and longer-term inflation expectations indicators are at the bottom of their historical range.</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
         <v>1</v>
@@ -8468,11 +8468,11 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Inflationary pressures remain subdued and longer-term inflation expectations indicators are at the bottom of their historical range.</t>
+          <t>The changes – the changes in the financial market you have described, in particular the increase in share prices, the increase in longer-term interest rates and the strengthening of the dollar – suggest that many market participants expect expansionary fiscal policies that would slightly increase interest rates in the United States compared to abroad and will result in a strengthening of the dollar.</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C384" t="n">
         <v>0</v>
@@ -8489,11 +8489,11 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>The changes – the changes in the financial market you have described, in particular the increase in share prices, the increase in longer-term interest rates and the strengthening of the dollar – suggest that many market participants expect expansionary fiscal policies that would slightly increase interest rates in the United States compared to abroad and will result in a strengthening of the dollar.</t>
+          <t>Well, we - as committee - do not want inflation undercutting.</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C385" t="n">
         <v>0</v>
@@ -8510,14 +8510,14 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Well, we - as committee - do not want inflation undercutting.</t>
+          <t>Finally, I would like to say that the Committee is anxious to explain its monetary policy decisions as clearly as possible and we will continue to look for ways to improve the clarity of our public communication.</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C386" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D386" t="n">
         <v>1</v>
@@ -8531,11 +8531,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Finally, I would like to say that the Committee is anxious to explain its monetary policy decisions as clearly as possible and we will continue to look for ways to improve the clarity of our public communication.</t>
+          <t>I believe, however, that - and I also believe that unemployment insurance will expire in September - it will no longer be a factor as it is a factor which is not clear.</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C387" t="n">
         <v>2</v>
@@ -8552,14 +8552,14 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
+          <t>Well, our policy approach does not deliberately involve an attempt to increase inflation.</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D388" t="n">
         <v>1</v>
@@ -8573,14 +8573,14 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>I believe, however, that - and I also believe that unemployment insurance will expire in September - it will no longer be a factor as it is a factor which is not clear.</t>
+          <t>Last year we had 1.9 percent productivity, which is much higher.</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C389" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D389" t="n">
         <v>1</v>
@@ -8594,14 +8594,14 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Well, our policy approach does not deliberately involve an attempt to increase inflation.</t>
+          <t>However, I would like to stress that we are committed to raising inflation to 2%.</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D390" t="n">
         <v>1</v>
@@ -8615,14 +8615,14 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Last year we had 1.9 percent productivity, which is much higher.</t>
+          <t>But it is not easy to get a clear reading of the impact of asset prices on overall prospects.</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C391" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D391" t="n">
         <v>1</v>
@@ -8636,11 +8636,11 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>However, I would like to stress that we are committed to raising inflation to 2%.</t>
+          <t>I mean, some parts of South Carolina have developed quite strongly, but the part I come from – mostly agricultural, it has a little bit of production – has a very high unemployment rate, a high foreclosure rate, and people have a hard time there.</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C392" t="n">
         <v>0</v>
@@ -8657,14 +8657,14 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>But it is not easy to get a clear reading of the impact of asset prices on overall prospects.</t>
+          <t>At the time of our FOMC meeting in January, the prospects for sustained economic growth remained favourable, and we felt that monetary policy was well positioned to support these prospects.</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C393" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D393" t="n">
         <v>1</v>
@@ -8678,14 +8678,14 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>I mean, some parts of South Carolina have developed quite strongly, but the part I come from – mostly agricultural, it has a little bit of production – has a very high unemployment rate, a high foreclosure rate, and people have a hard time there.</t>
+          <t>What I am telling you is that the attitude of monetary policy that we have today, we believe, is appropriate.</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C394" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D394" t="n">
         <v>1</v>
@@ -8699,14 +8699,14 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>At the time of our FOMC meeting in January, the prospects for sustained economic growth remained favourable, and we felt that monetary policy was well positioned to support these prospects.</t>
+          <t>The Committee therefore estimates that the unemployment rate is usually 5.0 to 5.2.</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C395" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D395" t="n">
         <v>1</v>
@@ -8720,14 +8720,14 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>What I am telling you is that the attitude of monetary policy that we have today, we believe, is appropriate.</t>
+          <t>We have not focused on whether we are fulfilling the downforce test, because we are not now fulfilling the downforce test because we are not at maximum employment.</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C396" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D396" t="n">
         <v>1</v>
@@ -8741,14 +8741,14 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>The Committee therefore estimates that the unemployment rate is usually 5.0 to 5.2.</t>
+          <t>Now, with inflation below 2 percent, I think it's appropriate that the labour market be so tight.</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C397" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D397" t="n">
         <v>1</v>
@@ -8762,11 +8762,11 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>We have not focused on whether we are fulfilling the downforce test, because we are not now fulfilling the downforce test because we are not at maximum employment.</t>
+          <t>I can only say in qualitative terms that the Committee will continue to examine the prospects, will try to assess whether unemployment is sufficiently advanced to our objectives and, in particular, whether the recovery will continue.</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C398" t="n">
         <v>0</v>
@@ -8783,14 +8783,14 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Now, with inflation below 2 percent, I think it's appropriate that the labour market be so tight.</t>
+          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C399" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D399" t="n">
         <v>1</v>
@@ -8804,14 +8804,14 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>I can only say in qualitative terms that the Committee will continue to examine the prospects, will try to assess whether unemployment is sufficiently advanced to our objectives and, in particular, whether the recovery will continue.</t>
+          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C400" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D400" t="n">
         <v>1</v>
@@ -8825,14 +8825,14 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
+          <t>And perhaps they are reducing their level of natural unemployment, which was the trend.</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C401" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D401" t="n">
         <v>1</v>
@@ -8846,14 +8846,14 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
+          <t>Well, we've been expecting a long time, as most analysts have, to see some slowdown in Chinese growth over time, how they're balancing their economy.</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C402" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D402" t="n">
         <v>1</v>
@@ -8867,14 +8867,14 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>And perhaps they are reducing their level of natural unemployment, which was the trend.</t>
+          <t>They say we're going to try to find inflation, which is over 2% for some time.</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D403" t="n">
         <v>1</v>
@@ -8888,11 +8888,11 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Well, we've been expecting a long time, as most analysts have, to see some slowdown in Chinese growth over time, how they're balancing their economy.</t>
+          <t>We want less unemployment.</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C404" t="n">
         <v>0</v>
@@ -8909,14 +8909,14 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>They say we're going to try to find inflation, which is over 2% for some time.</t>
+          <t>I have pointed out that I have concerns about the possibilities for monetary policy.</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C405" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D405" t="n">
         <v>1</v>
@@ -8930,14 +8930,14 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>We want less unemployment.</t>
+          <t>And those who frankly have no significant impact on inflation or the American economy have no long-term impact.</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C406" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D406" t="n">
         <v>1</v>
@@ -8951,14 +8951,14 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>I have pointed out that I have concerns about the possibilities for monetary policy.</t>
+          <t>Inflation has increased in recent months, mainly due to higher prices for some raw materials and imported goods.</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C407" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D407" t="n">
         <v>1</v>
@@ -8972,11 +8972,11 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>And those who frankly have no significant impact on inflation or the American economy have no long-term impact.</t>
+          <t>In the coming months, as the previous declines fall from the calculation, inflation should approach closer to 2 percent and stabilise around this level in the medium term.</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C408" t="n">
         <v>2</v>
@@ -8993,14 +8993,14 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Inflation has increased in recent months, mainly due to higher prices for some raw materials and imported goods.</t>
+          <t>It was the year of synchronised global growth.</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D409" t="n">
         <v>1</v>
@@ -9014,11 +9014,11 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>In the coming months, as the previous declines fall from the calculation, inflation should approach closer to 2 percent and stabilise around this level in the medium term.</t>
+          <t>It would consist of inflation plus — plus productivity growth.</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C410" t="n">
         <v>2</v>
@@ -9035,14 +9035,14 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>It was the year of synchronised global growth.</t>
+          <t>If you look at the core inflation of PCE, which is a good measure of where inflation is now running, if you look at it on an annualised basis that has been up to 3, 6 and 12 months ago, then you will see that inflation is 4.8 percent, 4.5 percent and 4.8 percent.</t>
         </is>
       </c>
       <c r="B411" t="n">
         <v>2021</v>
       </c>
       <c r="C411" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D411" t="n">
         <v>1</v>
@@ -9056,11 +9056,11 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>It would consist of inflation plus — plus productivity growth.</t>
+          <t>If you come to – in the forecast – you can adapt all that, you know, to the supply and demand of the economy.</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C412" t="n">
         <v>2</v>
@@ -9077,14 +9077,14 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>If you look at the core inflation of PCE, which is a good measure of where inflation is now running, if you look at it on an annualised basis that has been up to 3, 6 and 12 months ago, then you will see that inflation is 4.8 percent, 4.5 percent and 4.8 percent.</t>
+          <t>And some of the answer to that can be price.</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D413" t="n">
         <v>1</v>
@@ -9098,14 +9098,14 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>If you come to – in the forecast – you can adapt all that, you know, to the supply and demand of the economy.</t>
+          <t>To do this, we must have price stability, and we must return to price stability so that we can have a labour market where people's wages are not eaten up by inflation and where we can have a long expansion.</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D414" t="n">
         <v>1</v>
@@ -9119,11 +9119,11 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>And some of the answer to that can be price.</t>
+          <t>And that's because of this misalignment between supply and demand.</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C415" t="n">
         <v>2</v>
@@ -9140,14 +9140,14 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>To do this, we must have price stability, and we must return to price stability so that we can have a labour market where people's wages are not eaten up by inflation and where we can have a long expansion.</t>
+          <t>And our plan, as we do, is that we believe that we can gradually reduce these products, and we believe that we can also gradually reduce Repo, because we are reaching a sufficient level, as we are now buying more from the underlying reserves from the invoices than from Repo.</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D416" t="n">
         <v>1</v>
@@ -9161,11 +9161,11 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>And that's because of this misalignment between supply and demand.</t>
+          <t>If we - if we analyse inflation data and find that we clearly restrain temporary influences - then I do not want to say that we would respond to it.</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C417" t="n">
         <v>2</v>
@@ -9182,14 +9182,14 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>And our plan, as we do, is that we believe that we can gradually reduce these products, and we believe that we can also gradually reduce Repo, because we are reaching a sufficient level, as we are now buying more from the underlying reserves from the invoices than from Repo.</t>
+          <t>Despite such slow growth, disappointing productivity growth, we have a labour market that generated an average of around 230,000 jobs per month last year and has generated around 180,000 jobs per month this year.</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D418" t="n">
         <v>1</v>
@@ -9203,7 +9203,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>If we - if we analyse inflation data and find that we clearly restrain temporary influences - then I do not want to say that we would respond to it.</t>
+          <t>The sooner we get the virus under control, the sooner people can regain this trust and regain their economic activity.</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -9224,14 +9224,14 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Despite such slow growth, disappointing productivity growth, we have a labour market that generated an average of around 230,000 jobs per month last year and has generated around 180,000 jobs per month this year.</t>
+          <t>Now, members of the committee have different views on why this is likely to be true, that the money rate – when the labour market is normalized and inflation is back to our goal – may have some different views on why it is likely that interest rates will be slightly lower than they would in the longer term.</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D420" t="n">
         <v>1</v>
@@ -9245,14 +9245,14 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>The sooner we get the virus under control, the sooner people can regain this trust and regain their economic activity.</t>
+          <t>But first, in terms of inflation expectations, it is true that breakevens have fallen from inflation-adjusted inflation index bonds.</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C421" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D421" t="n">
         <v>1</v>
@@ -9266,14 +9266,14 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Now, members of the committee have different views on why this is likely to be true, that the money rate – when the labour market is normalized and inflation is back to our goal – may have some different views on why it is likely that interest rates will be slightly lower than they would in the longer term.</t>
+          <t>We heard anecdotes today in the meeting about companies that may be government companies that, you know, were not sure if the contracts would still be in force, coming in January and making employment decisions on this basis.</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C422" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D422" t="n">
         <v>1</v>
@@ -9287,14 +9287,14 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>But first, in terms of inflation expectations, it is true that breakevens have fallen from inflation-adjusted inflation index bonds.</t>
+          <t>When we return to monetary policy, we see that today's political decision has been very focused.</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C423" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D423" t="n">
         <v>1</v>
@@ -9308,14 +9308,14 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>We heard anecdotes today in the meeting about companies that may be government companies that, you know, were not sure if the contracts would still be in force, coming in January and making employment decisions on this basis.</t>
+          <t>In any case, it is our job to ensure price stability, and I think that price stability can be imagined as an advantage that will bring great benefits to society over a long period of time.</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C424" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D424" t="n">
         <v>1</v>
@@ -9329,14 +9329,14 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>When we return to monetary policy, we see that today's political decision has been very focused.</t>
+          <t>We are being accused by Congress of trying to pursue maximum employment, and we have taken this very seriously.</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C425" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D425" t="n">
         <v>1</v>
@@ -9350,14 +9350,14 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>In any case, it is our job to ensure price stability, and I think that price stability can be imagined as an advantage that will bring great benefits to society over a long period of time.</t>
+          <t>The same applies to economic activity.</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D426" t="n">
         <v>1</v>
@@ -9371,14 +9371,14 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>We are being accused by Congress of trying to pursue maximum employment, and we have taken this very seriously.</t>
+          <t>As always, each participant's projections depend on his own view of the relevant monetary policy.</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C427" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D427" t="n">
         <v>1</v>
@@ -9392,14 +9392,14 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>The same applies to economic activity.</t>
+          <t>As highlighted by the Bureau of Labor Statistics, this figure will probably underestimate the extent of unemployment; the unusually large number of workers registered as employed but not in their jobs would increase the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D428" t="n">
         <v>1</v>
@@ -9413,14 +9413,14 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>As always, each participant's projections depend on his own view of the relevant monetary policy.</t>
+          <t>In fact, it is already – I think it is already understood – that there is more – although we are at 31⁄2 percent unemployment, there is actually more slackening out there, in a way.</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C429" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D429" t="n">
         <v>1</v>
@@ -9434,14 +9434,14 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>As highlighted by the Bureau of Labor Statistics, this figure will probably underestimate the extent of unemployment; the unusually large number of workers registered as employed but not in their jobs would increase the unemployment rate by about 3 percentage points.</t>
+          <t>And I fully expect it to return to solid growth and a solid labour market.</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C430" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D430" t="n">
         <v>1</v>
@@ -9455,14 +9455,14 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>In fact, it is already – I think it is already understood – that there is more – although we are at 31⁄2 percent unemployment, there is actually more slackening out there, in a way.</t>
+          <t>Monetary policy, maximum employment, stable prices – that is less obvious to me.</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C431" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D431" t="n">
         <v>1</v>
@@ -9476,14 +9476,14 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>And I fully expect it to return to solid growth and a solid labour market.</t>
+          <t>The US economy is in a good place, and we will continue to use our monetary policy instruments to keep it there.</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C432" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D432" t="n">
         <v>1</v>
@@ -9497,14 +9497,14 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Monetary policy, maximum employment, stable prices – that is less obvious to me.</t>
+          <t>By the way, we are not at maximum employment, as I have already mentioned.</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D433" t="n">
         <v>1</v>
@@ -9518,14 +9518,14 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>The US economy is in a good place, and we will continue to use our monetary policy instruments to keep it there.</t>
+          <t>The unemployment rate in February was 3.5 percent and has been at or close to a low point in the half century for almost two years.</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D434" t="n">
         <v>1</v>
@@ -9539,14 +9539,14 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>By the way, we are not at maximum employment, as I have already mentioned.</t>
+          <t>As you know, the ultimate focus we have is on the real economy: maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C435" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D435" t="n">
         <v>1</v>
@@ -9560,14 +9560,14 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>The unemployment rate in February was 3.5 percent and has been at or close to a low point in the half century for almost two years.</t>
+          <t>And that's a statement about productivity growth that was pretty disappointing.</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D436" t="n">
         <v>1</v>
@@ -9581,14 +9581,14 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>As you know, the ultimate focus we have is on the real economy: maximum employment and price stability.</t>
+          <t>The stimulus of aggregate demand is one thing, but where part of the economy that resists it is there, a fiscal policy is also needed.</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C437" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D437" t="n">
         <v>1</v>
@@ -9602,14 +9602,14 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>And that's a statement about productivity growth that was pretty disappointing.</t>
+          <t>So, as I said, we're going to look at all these things: activity, labour market, inflation.</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D438" t="n">
         <v>1</v>
@@ -9623,14 +9623,14 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>The stimulus of aggregate demand is one thing, but where part of the economy that resists it is there, a fiscal policy is also needed.</t>
+          <t>And – but inflation expectations have not developed strongly here in the United States.</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C439" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D439" t="n">
         <v>1</v>
@@ -9644,7 +9644,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>So, as I said, we're going to look at all these things: activity, labour market, inflation.</t>
+          <t>You can focus up to 20 if you wanted, easily, but the labour force participation, the unemployment rate, different age groups of - you know, prime-age labor participation, in particular, gets a lot of focus that JOLTS data get a lot.</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -9665,14 +9665,14 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>And – but inflation expectations have not developed strongly here in the United States.</t>
+          <t>Inflation has remained below our longer term target, partly due to lower energy prices.</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D441" t="n">
         <v>1</v>
@@ -9686,11 +9686,11 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>You can focus up to 20 if you wanted, easily, but the labour force participation, the unemployment rate, different age groups of - you know, prime-age labor participation, in particular, gets a lot of focus that JOLTS data get a lot.</t>
+          <t>We also see the different measures of negligence on the labour market for different assessments of what is maximum employment.</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C442" t="n">
         <v>2</v>
@@ -9707,14 +9707,14 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Inflation has remained below our longer term target, partly due to lower energy prices.</t>
+          <t>Inflation is actually under control and is beginning to decline.</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D443" t="n">
         <v>1</v>
@@ -9728,14 +9728,14 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>We also see the different measures of negligence on the labour market for different assessments of what is maximum employment.</t>
+          <t>The unemployment rate dropped in May and, 2020 June, but at 11.1 percent, remains well above its level before the outbreak and greater than the chairman Powell .</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C444" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D444" t="n">
         <v>1</v>
@@ -9749,14 +9749,14 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Inflation is actually under control and is beginning to decline.</t>
+          <t>So there have been effects from lower interest rates, but I think, by and large, the indirect effects are.</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C445" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D445" t="n">
         <v>1</v>
@@ -9770,14 +9770,14 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>The unemployment rate dropped in May and, 2020 June, but at 11.1 percent, remains well above its level before the outbreak and greater than the chairman Powell .</t>
+          <t>They had low unemployment, many social problems.</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D446" t="n">
         <v>1</v>
@@ -9791,14 +9791,14 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>So there have been effects from lower interest rates, but I think, by and large, the indirect effects are.</t>
+          <t>And then we will just have that in the background – and interest rates will be the active instrument of monetary policy again.</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C447" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D447" t="n">
         <v>1</v>
@@ -9812,14 +9812,14 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>They had low unemployment, many social problems.</t>
+          <t>But, as it continues to be, it should be easier to restore price stability.</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C448" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D448" t="n">
         <v>1</v>
@@ -9833,7 +9833,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>And then we will just have that in the background – and interest rates will be the active instrument of monetary policy again.</t>
+          <t>And what it is, it is an expression of thinking about individual committee members about an appropriate monetary policy and the way of the economy.</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -9854,14 +9854,14 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>But, as it continues to be, it should be easier to restore price stability.</t>
+          <t>Well, what happens is that the relationship between resource use or unemployment and inflation has become weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D450" t="n">
         <v>1</v>
@@ -9875,14 +9875,14 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>And what it is, it is an expression of thinking about individual committee members about an appropriate monetary policy and the way of the economy.</t>
+          <t>And as I have already mentioned, the fall in unemployment last month was more than 100 percent, due to the decline in labour force participation.</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C451" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D451" t="n">
         <v>1</v>
@@ -9896,14 +9896,14 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Well, what happens is that the relationship between resource use or unemployment and inflation has become weaker and weaker over the years.</t>
+          <t>Wage inflation has increased to 2 percent.</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C452" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D452" t="n">
         <v>1</v>
@@ -9917,14 +9917,14 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>And as I have already mentioned, the fall in unemployment last month was more than 100 percent, due to the decline in labour force participation.</t>
+          <t>The slow rise in interest rates, on the other hand, would increase the risk of monetary policy starting abruptly, which could jeopardise economic expansion.</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D453" t="n">
         <v>1</v>
@@ -9938,11 +9938,11 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Wage inflation has increased to 2 percent.</t>
+          <t>We continue to discuss whether the unemployment rate itself is an appropriate measure of how much underutilisation of labour resources actually exists.</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C454" t="n">
         <v>2</v>
@@ -9959,14 +9959,14 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>The slow rise in interest rates, on the other hand, would increase the risk of monetary policy starting abruptly, which could jeopardise economic expansion.</t>
+          <t>For many, many years we have been far from maximum employment and stable prices, and the need for accommodative policies was clear.</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D455" t="n">
         <v>1</v>
@@ -9980,14 +9980,14 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>We continue to discuss whether the unemployment rate itself is an appropriate measure of how much underutilisation of labour resources actually exists.</t>
+          <t>Inflation has continued to fall below our longer-term target, largely due to the lower energy prices I have mentioned.</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C456" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D456" t="n">
         <v>1</v>
@@ -10001,11 +10001,11 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>For many, many years we have been far from maximum employment and stable prices, and the need for accommodative policies was clear.</t>
+          <t>We had an unemployment rate of 10 percent, and our Congress mandate is maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C457" t="n">
         <v>0</v>
@@ -10022,11 +10022,11 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Inflation has continued to fall below our longer-term target, largely due to the lower energy prices I have mentioned.</t>
+          <t>So, you know, I can't -- all I can tell you is that we're going to look at a weak global growth.</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C458" t="n">
         <v>0</v>
@@ -10043,14 +10043,14 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>We had an unemployment rate of 10 percent, and our Congress mandate is maximum employment and price stability.</t>
+          <t>It was about, you know, strong monetary policy and fiscal incentives to an economy that was rapidly recovering and where there were these supply-side barriers that effectively led to a so-called vertical supply curve in certain parts of the economy.</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D459" t="n">
         <v>1</v>
@@ -10064,11 +10064,11 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>So, you know, I can't -- all I can tell you is that we're going to look at a weak global growth.</t>
+          <t>As unemployment is still rising and inflation is below the longer term objective of the Committee, the Committee continues its extremely accommodating policy.</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C460" t="n">
         <v>0</v>
@@ -10085,14 +10085,14 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>It was about, you know, strong monetary policy and fiscal incentives to an economy that was rapidly recovering and where there were these supply-side barriers that effectively led to a so-called vertical supply curve in certain parts of the economy.</t>
+          <t>So this time you saw a shift in most participants, assessing the appropriate way for policy, and, as I tried to show, I think that largely reflects a somewhat slower projected way for global growth – for growth in the world economy outside the United States – and for a certain tightening of credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D461" t="n">
         <v>1</v>
@@ -10106,14 +10106,14 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>As unemployment is still rising and inflation is below the longer term objective of the Committee, the Committee continues its extremely accommodating policy.</t>
+          <t>And we learn to engage in economic activity.</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D462" t="n">
         <v>1</v>
@@ -10127,11 +10127,11 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>So this time you saw a shift in most participants, assessing the appropriate way for policy, and, as I tried to show, I think that largely reflects a somewhat slower projected way for global growth – for growth in the world economy outside the United States – and for a certain tightening of credit conditions in the form of an increase in spreads.</t>
+          <t>And inflation is moving – I think we are going towards our 2 percent target.</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C463" t="n">
         <v>0</v>
@@ -10148,14 +10148,14 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>And we learn to engage in economic activity.</t>
+          <t>The unemployment rate, however, remains high at 7.7 percent.</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C464" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D464" t="n">
         <v>1</v>
@@ -10169,14 +10169,14 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>And inflation is moving – I think we are going towards our 2 percent target.</t>
+          <t>Monetary policy is a forward-looking exercise, and I will do it – I will just stick to it.</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C465" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D465" t="n">
         <v>1</v>
@@ -10190,14 +10190,14 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>The unemployment rate, however, remains high at 7.7 percent.</t>
+          <t>There is much more demand for risk sharing, for liquidity services, and so on.</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="C466" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D466" t="n">
         <v>1</v>
@@ -10211,11 +10211,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Monetary policy is a forward-looking exercise, and I will do it – I will just stick to it.</t>
+          <t>For example, we have used some of our work to address interest rate risk and interest rate sensitivity, and you know that banks can also achieve a significant increase in long-term interest rates for a number of reasons, including higher interest rates increasing their franchise value because they increase their net interest rate margin over time.</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C467" t="n">
         <v>2</v>
@@ -10232,14 +10232,14 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>There is much more demand for risk sharing, for liquidity services, and so on.</t>
+          <t>Well, you are certainly right that we have been overoptimistic about growth during the year.</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C468" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D468" t="n">
         <v>1</v>
@@ -10253,11 +10253,11 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>For example, we have used some of our work to address interest rate risk and interest rate sensitivity, and you know that banks can also achieve a significant increase in long-term interest rates for a number of reasons, including higher interest rates increasing their franchise value because they increase their net interest rate margin over time.</t>
+          <t>It will contain all the data relevant to our dual mandate of stable prices and maximum employment.</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C469" t="n">
         <v>2</v>
@@ -10274,14 +10274,14 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Well, you are certainly right that we have been overoptimistic about growth during the year.</t>
+          <t>So I have no sense – the committee is not trying to judge what is the right level of stock prices.</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C470" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D470" t="n">
         <v>1</v>
@@ -10295,14 +10295,14 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>It will contain all the data relevant to our dual mandate of stable prices and maximum employment.</t>
+          <t>So with this Corona virus that arrives, we have judged that the – the net effects of it – will bring inflation down a little further.</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C471" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D471" t="n">
         <v>1</v>
@@ -10316,14 +10316,14 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>So I have no sense – the committee is not trying to judge what is the right level of stock prices.</t>
+          <t>Long-term unemployment in the current economy is – is the worst – the worst it has been in the post-war period.</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C472" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D472" t="n">
         <v>1</v>
@@ -10337,14 +10337,14 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>So with this Corona virus that arrives, we have judged that the – the net effects of it – will bring inflation down a little further.</t>
+          <t>But you have not been under the merely negative scenario that has been followed by an inflation shock followed by a rapid rise in short-term interest rates.</t>
         </is>
       </c>
       <c r="B473" t="n">
         <v>2014</v>
       </c>
       <c r="C473" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D473" t="n">
         <v>1</v>
@@ -10358,11 +10358,11 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the current economy is – is the worst – the worst it has been in the post-war period.</t>
+          <t>And we want inflation to be moderately above 2 percent.</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C474" t="n">
         <v>0</v>
@@ -10379,14 +10379,14 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>But you have not been under the merely negative scenario that has been followed by an inflation shock followed by a rapid rise in short-term interest rates.</t>
+          <t>Many members of the committee, the participants, have said that they believe that policy should be based on the actual development of economic activity and inflation, which tends to be variable over time, and therefore I say that I will assume that it will depend on data.</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C475" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D475" t="n">
         <v>1</v>
@@ -10400,14 +10400,14 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>And we want inflation to be moderately above 2 percent.</t>
+          <t>But, certainly, we enve had a lot of years in which interest rates were low.</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C476" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D476" t="n">
         <v>1</v>
@@ -10421,14 +10421,14 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Many members of the committee, the participants, have said that they believe that policy should be based on the actual development of economic activity and inflation, which tends to be variable over time, and therefore I say that I will assume that it will depend on data.</t>
+          <t>These measures, together with our strong interest rate guidelines and our balance sheet, will ensure that monetary policy continues to support the economy until the full recovery.</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C477" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D477" t="n">
         <v>1</v>
@@ -10442,14 +10442,14 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>But, certainly, we enve had a lot of years in which interest rates were low.</t>
+          <t>The problem with the current situation is that if you have a long-term supply shock, you can actually start to undermine or work on it – decoding inflation expectations.</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C478" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D478" t="n">
         <v>1</v>
@@ -10463,11 +10463,11 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>These measures, together with our strong interest rate guidelines and our balance sheet, will ensure that monetary policy continues to support the economy until the full recovery.</t>
+          <t>The Federal Reserves will strengthen the orientation for their political intentions and their substantial and still growing stocks of longer-term securities to ensure that monetary policy remains highly accommodating, in line with the pursuit of their mandates for maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C479" t="n">
         <v>0</v>
@@ -10484,14 +10484,14 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>The problem with the current situation is that if you have a long-term supply shock, you can actually start to undermine or work on it – decoding inflation expectations.</t>
+          <t>And part of it is just the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D480" t="n">
         <v>1</v>
@@ -10505,14 +10505,14 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>The Federal Reserves will strengthen the orientation for their political intentions and their substantial and still growing stocks of longer-term securities to ensure that monetary policy remains highly accommodating, in line with the pursuit of their mandates for maximum employment and price stability.</t>
+          <t>And when asset prices went up again, it will probably be a swing around there, a positive contribution.</t>
         </is>
       </c>
       <c r="B481" t="n">
         <v>2020</v>
       </c>
       <c r="C481" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D481" t="n">
         <v>1</v>
@@ -10526,14 +10526,14 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>And part of it is just the effect of lower interest rates.</t>
+          <t>We understand that the pace of inflation is constantly evolving over time, but it does not change quickly.</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C482" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D482" t="n">
         <v>1</v>
@@ -10547,11 +10547,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>And when asset prices went up again, it will probably be a swing around there, a positive contribution.</t>
+          <t>So you're basically talking about the inflation target.</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C483" t="n">
         <v>2</v>
@@ -10568,11 +10568,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>We understand that the pace of inflation is constantly evolving over time, but it does not change quickly.</t>
+          <t>So, in terms of financial markets and monetary policy, as we say in our statement of each cycle, we take into account the financial conditions, because the financial conditions – the broader financial conditions – influence the economy, and they are one of the many things we take into account.</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C484" t="n">
         <v>2</v>
@@ -10589,14 +10589,14 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>So you're basically talking about the inflation target.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to fall so that inflation will fall.</t>
         </is>
       </c>
       <c r="B485" t="n">
         <v>2019</v>
       </c>
       <c r="C485" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D485" t="n">
         <v>1</v>
@@ -10610,14 +10610,14 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>So, in terms of financial markets and monetary policy, as we say in our statement of each cycle, we take into account the financial conditions, because the financial conditions – the broader financial conditions – influence the economy, and they are one of the many things we take into account.</t>
+          <t>So if you get credit, along with the low prices of houses, you can buy a lot more house than it might be a few years ago.</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C486" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D486" t="n">
         <v>1</v>
@@ -10631,14 +10631,14 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to fall so that inflation will fall.</t>
+          <t>But – so I would simply say that we – there are many things that, as you know, serve to set the prices of assets.</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C487" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D487" t="n">
         <v>1</v>
@@ -10652,14 +10652,14 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>So if you get credit, along with the low prices of houses, you can buy a lot more house than it might be a few years ago.</t>
+          <t>But here too, our basic forecast is one that, as Mr Hilsenrath has already said, is a moderately optimistic forecast in which growth will increase as we go through this period of budgetary restraint; where unemployment is continuing to decline gradually, as it has been since last September – and we have made progress since last September; and inflation is slowly rising to 2 percent.</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D488" t="n">
         <v>1</v>
@@ -10673,11 +10673,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>But – so I would simply say that we – there are many things that, as you know, serve to set the prices of assets.</t>
+          <t>And the downward correction of the longer-term normal unemployment rate indicates in a way that the participants are now dwindling in the economy more than before.</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C489" t="n">
         <v>2</v>
@@ -10694,14 +10694,14 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>But here too, our basic forecast is one that, as Mr Hilsenrath has already said, is a moderately optimistic forecast in which growth will increase as we go through this period of budgetary restraint; where unemployment is continuing to decline gradually, as it has been since last September – and we have made progress since last September; and inflation is slowly rising to 2 percent.</t>
+          <t>During this period of reopening, we will probably see some upward pressure on prices, and I will discuss why.</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C490" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D490" t="n">
         <v>1</v>
@@ -10715,11 +10715,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>And the downward correction of the longer-term normal unemployment rate indicates in a way that the participants are now dwindling in the economy more than before.</t>
+          <t>And of course, all households in the economy benefit from a strong economy, including savers, from a better labour market and a safer economy.</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C491" t="n">
         <v>2</v>
@@ -10736,14 +10736,14 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>During this period of reopening, we will probably see some upward pressure on prices, and I will discuss why.</t>
+          <t>As I have already mentioned, monetary policy is working with delays, and so the policies we are pursuing will gradually – only gradually – reduce inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C492" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D492" t="n">
         <v>1</v>
@@ -10757,11 +10757,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>And of course, all households in the economy benefit from a strong economy, including savers, from a better labour market and a safer economy.</t>
+          <t>As I have already mentioned, once you put aside the individual estimates of them, and look at what the incoming data tells you about the prospects, update your estimates of what might be neutral, what could be natural unemployment, about the state of the economy, and allow you to adjust your prospects and thus your appropriate way of doing politics.</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="C493" t="n">
         <v>2</v>
@@ -10778,14 +10778,14 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>As I have already mentioned, monetary policy is working with delays, and so the policies we are pursuing will gradually – only gradually – reduce inflation to 2 percent.</t>
+          <t>Our current framework for implementing monetary policy works very well.</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C494" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D494" t="n">
         <v>1</v>
@@ -10799,14 +10799,14 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>As I have already mentioned, once you put aside the individual estimates of them, and look at what the incoming data tells you about the prospects, update your estimates of what might be neutral, what could be natural unemployment, about the state of the economy, and allow you to adjust your prospects and thus your appropriate way of doing politics.</t>
+          <t>The unemployment rate has increased by 0.3 percentage points since March and the new insurance rights have increased slightly.</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C495" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D495" t="n">
         <v>1</v>
@@ -10820,14 +10820,14 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Our current framework for implementing monetary policy works very well.</t>
+          <t>You know, this is – that is the economy with almost full employment or in the area – in the neighbourhood of full employment.</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C496" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D496" t="n">
         <v>1</v>
@@ -10841,14 +10841,14 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>The unemployment rate has increased by 0.3 percentage points since March and the new insurance rights have increased slightly.</t>
+          <t>The Committee will also pay great attention to inflation expectations to ensure that these expectations remain well-established.</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D497" t="n">
         <v>1</v>
@@ -10862,14 +10862,14 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>You know, this is – that is the economy with almost full employment or in the area – in the neighbourhood of full employment.</t>
+          <t>Wage growth is not – there are many factors that influence it – it is in no way definitive when it determines our policies, but it has an impact on inflation prospects.</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D498" t="n">
         <v>1</v>
@@ -10883,14 +10883,14 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>The Committee will also pay great attention to inflation expectations to ensure that these expectations remain well-established.</t>
+          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C499" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D499" t="n">
         <v>1</v>
@@ -10904,11 +10904,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Wage growth is not – there are many factors that influence it – it is in no way definitive when it determines our policies, but it has an impact on inflation prospects.</t>
+          <t>And as I have already mentioned, I think that the estimates of – by members of the committee since perhaps 2012, as we have seen, have fallen by a full percentage point – while unemployment has fallen and inflation has not really responded.</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C500" t="n">
         <v>2</v>
@@ -10925,14 +10925,14 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
+          <t>Against this background, the Federal Committee on the Open Market today raised its key rate by 3⁄4 percentage points and expects that the current increases in this rate will be appropriate.</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C501" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D501" t="n">
         <v>1</v>
@@ -10946,14 +10946,14 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>And as I have already mentioned, I think that the estimates of – by members of the committee since perhaps 2012, as we have seen, have fallen by a full percentage point – while unemployment has fallen and inflation has not really responded.</t>
+          <t>And what we do -- it looks like we're seeing a slowdown in growth rate.</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C502" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D502" t="n">
         <v>1</v>
@@ -10967,14 +10967,14 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Against this background, the Federal Committee on the Open Market today raised its key rate by 3⁄4 percentage points and expects that the current increases in this rate will be appropriate.</t>
+          <t>The . enlarged period . the language is conditioned precisely to the same points: . extended period . is conditioned by resources, by subdued inflation and stable inflation expectations.</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C503" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D503" t="n">
         <v>1</v>
@@ -10988,53 +10988,53 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>And what we do -- it looks like we're seeing a slowdown in growth rate.</t>
+          <t>But also we want to see inflation move up back to our 2 percent objective over the medium term, and so seeing above-trend growth and continuing slack—greater slack in labor and product markets—I think that will help us achieve our objective as well with respect to inflation.</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D504" t="n">
         <v>1</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>back_translation</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>The . enlarged period . the language is conditioned precisely to the same points: . extended period . is conditioned by resources, by subdued inflation and stable inflation expectations.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C505" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D505" t="n">
         <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>back_translation</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>But also we want to see inflation move up back to our 2 percent objective over the medium term, and so seeing above-trend growth and continuing slack—greater slack in labor and product markets—I think that will help us achieve our objective as well with respect to inflation.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C506" t="n">
         <v>1</v>
@@ -11051,11 +11051,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
+          <t>For example, the unemployment rate has fallen by 0.3 percentage points since March, and new claims for unemployment insurance have moved somewhat lower.</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C507" t="n">
         <v>1</v>
@@ -11072,11 +11072,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-decreasing holdings of longer-term securities will ensure that monetary policy remains highly restrictive, consistent with the pursuit of its mandated objectives of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C508" t="n">
         <v>1</v>
@@ -11093,11 +11093,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>For example, the unemployment rate has fallen by 0.3 percentage points since March, and new claims for unemployment insurance have moved somewhat lower.</t>
+          <t>Last year, we had 1.9 percent productivity, which is much lower.</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C509" t="n">
         <v>1</v>
@@ -11114,11 +11114,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-decreasing holdings of longer-term securities will ensure that monetary policy remains highly restrictive, consistent with the pursuit of its mandated objectives of maximum employment and price stability.</t>
+          <t>You know, what you hear out there is that demand—you talk to banks, and they’ll say demand for loans is very, very high right now.</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C510" t="n">
         <v>1</v>
@@ -11135,11 +11135,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 percent productivity, which is much lower.</t>
+          <t>With unemployment still moderating and inflation below the Committee’s longer-run objective, the Committee is continuing its highly restrictive policies.</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C511" t="n">
         <v>1</v>
@@ -11156,11 +11156,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>You know, what you hear out there is that demand—you talk to banks, and they’ll say demand for loans is very, very high right now.</t>
+          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C512" t="n">
         <v>1</v>
@@ -11177,11 +11177,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>With unemployment still moderating and inflation below the Committee’s longer-run objective, the Committee is continuing its highly restrictive policies.</t>
+          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C513" t="n">
         <v>1</v>
@@ -11198,11 +11198,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
+          <t>But I want to emphasize that we do have a commitment to cutting inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C514" t="n">
         <v>1</v>
@@ -11219,11 +11219,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
+          <t>So unemployment has tended to go up much faster for minorities and for others who are—tend to be at the high end of the income spectrum.</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C515" t="n">
         <v>1</v>
@@ -11240,11 +11240,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a commitment to cutting inflation to 2 percent.</t>
+          <t>In fact, it’s already—it’s already understood, I think, that—that there’s more—even though we’re at 3½ percent unemployment, there’s actually more tightness out there, in a sense.</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C516" t="n">
         <v>1</v>
@@ -11261,11 +11261,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>So unemployment has tended to go up much faster for minorities and for others who are—tend to be at the high end of the income spectrum.</t>
+          <t>As was highlighted by the Bureau of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but absent from their jobs would cut the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C517" t="n">
         <v>1</v>
@@ -11282,11 +11282,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>In fact, it’s already—it’s already understood, I think, that—that there’s more—even though we’re at 3½ percent unemployment, there’s actually more tightness out there, in a sense.</t>
+          <t>So, there has been impact through higher interest rates, but I think more broadly is the indirect effects.</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C518" t="n">
         <v>1</v>
@@ -11303,7 +11303,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>As was highlighted by the Bureau of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but absent from their jobs would cut the unemployment rate by about 3 percentage points.</t>
+          <t>During this time of reopening, we are likely to see some downward pressure on prices, and I’ll discuss why.</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -11324,11 +11324,11 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>So, there has been impact through higher interest rates, but I think more broadly is the indirect effects.</t>
+          <t>Inflation has declined further below our longer-run objective, largely reflecting the higher energy prices I just mentioned.</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C520" t="n">
         <v>1</v>
@@ -11345,14 +11345,14 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some downward pressure on prices, and I’ll discuss why.</t>
+          <t>By contrast, cutting rates too slowly would cut the risk that monetary policy would need to ease abruptly down the road, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D521" t="n">
         <v>1</v>
@@ -11366,14 +11366,14 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Inflation has declined further below our longer-run objective, largely reflecting the higher energy prices I just mentioned.</t>
+          <t>Well, our policy approach doesn’t involve intentionally trying to cut inflation.</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D522" t="n">
         <v>1</v>
@@ -11387,11 +11387,11 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>By contrast, cutting rates too slowly would cut the risk that monetary policy would need to ease abruptly down the road, which could jeopardize the economic expansion.</t>
+          <t>Admittedly, some of the wage decreases is being eaten away by inflation.</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C523" t="n">
         <v>0</v>
@@ -11408,11 +11408,11 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Well, our policy approach doesn’t involve intentionally trying to cut inflation.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C524" t="n">
         <v>0</v>
@@ -11429,11 +11429,11 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Admittedly, some of the wage decreases is being eaten away by inflation.</t>
+          <t>The American economy is very weak and well positioned to handle softer monetary policy.</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C525" t="n">
         <v>0</v>
@@ -11450,11 +11450,11 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
+          <t>But you didn’t under the merely adverse scenario, which featured an inflation shock followed by a quick fall in short-term rates.</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C526" t="n">
         <v>0</v>
@@ -11471,11 +11471,11 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>The American economy is very weak and well positioned to handle softer monetary policy.</t>
+          <t>An unexpectedly sharp decrease in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B527" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C527" t="n">
         <v>0</v>
@@ -11492,11 +11492,11 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, which featured an inflation shock followed by a quick fall in short-term rates.</t>
+          <t>It was to do with, you know, weak monetary policy and fiscal stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively led to, you know, in certain parts of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C528" t="n">
         <v>0</v>
@@ -11513,11 +11513,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>An unexpectedly sharp decrease in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>We have a much more resilient, weaker banking system, and we’re not seeing some worrisome buildup in leverage or credit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor shaping monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major factor.</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C529" t="n">
         <v>0</v>
@@ -11534,11 +11534,11 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>It was to do with, you know, weak monetary policy and fiscal stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively led to, you know, in certain parts of the economy, what you might call a vertical supply curve.</t>
+          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can cut interest rates at the appropriate time, even if the balance sheet remains large for an extended period.</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C530" t="n">
         <v>0</v>
@@ -11555,11 +11555,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>We have a much more resilient, weaker banking system, and we’re not seeing some worrisome buildup in leverage or credit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor shaping monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major factor.</t>
+          <t>The blow that the—from the pandemic was unprecedented both in its nature and in its sizing and in the amount of unemployment that it created and in the shock to economic activity.</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="C531" t="n">
         <v>0</v>
@@ -11569,39 +11569,39 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can cut interest rates at the appropriate time, even if the balance sheet remains large for an extended period.</t>
+          <t>We are rather aware that very low interest rates, particularly for a protracted period, do have costs for a lot of people.</t>
         </is>
       </c>
       <c r="B532" t="n">
         <v>2020</v>
       </c>
       <c r="C532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D532" t="n">
         <v>1</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>The blow that the—from the pandemic was unprecedented both in its nature and in its sizing and in the amount of unemployment that it created and in the shock to economic activity.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak globular growth.</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C533" t="n">
         <v>0</v>
@@ -11618,14 +11618,14 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>We are rather aware that very low interest rates, particularly for a protracted period, do have costs for a lot of people.</t>
+          <t>But many other commodity prices have fallen further, and the reason I would give for that is that the emerging markets—China, the reside of Asia, and some other parts of the planetary—plus Europe, of course, are softer, and so global good demand is weaker.</t>
         </is>
       </c>
       <c r="B534" t="n">
         <v>2020</v>
       </c>
       <c r="C534" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D534" t="n">
         <v>1</v>
@@ -11639,14 +11639,14 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak globular growth.</t>
+          <t>And we’d like to see that in the conformation of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D535" t="n">
         <v>1</v>
@@ -11660,14 +11660,14 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>But many other commodity prices have fallen further, and the reason I would give for that is that the emerging markets—China, the reside of Asia, and some other parts of the planetary—plus Europe, of course, are softer, and so global good demand is weaker.</t>
+          <t>The American economy is very strong and well set to handle tighter monetary policy.</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C536" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D536" t="n">
         <v>1</v>
@@ -11681,14 +11681,14 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>And we’d like to see that in the conformation of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
+          <t>And, you know, we do want inflation to run moderately supra 2 percent.</t>
         </is>
       </c>
       <c r="B537" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C537" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D537" t="n">
         <v>1</v>
@@ -11702,14 +11702,14 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>The American economy is very strong and well set to handle tighter monetary policy.</t>
+          <t>So in—in—in U-6, the U-6 unwavering of unemployment has tripled from 7 percent to 21 percent.</t>
         </is>
       </c>
       <c r="B538" t="n">
         <v>2016</v>
       </c>
       <c r="C538" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D538" t="n">
         <v>1</v>
@@ -11723,11 +11723,11 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>And, you know, we do want inflation to run moderately supra 2 percent.</t>
+          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running below its longer-run likely this year and next year.</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C539" t="n">
         <v>0</v>
@@ -11744,14 +11744,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>So in—in—in U-6, the U-6 unwavering of unemployment has tripled from 7 percent to 21 percent.</t>
+          <t>These are, you know, this is—this is the economy at closely full employment or in the range—in the neighborhood of full employment.</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D540" t="n">
         <v>1</v>
@@ -11765,11 +11765,11 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running below its longer-run likely this year and next year.</t>
+          <t>And inflation is moving—moving up, I think, toward our 2 pct objective.</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C541" t="n">
         <v>0</v>
@@ -11786,14 +11786,14 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>These are, you know, this is—this is the economy at closely full employment or in the range—in the neighborhood of full employment.</t>
+          <t>Immediately, we’ve long expected, as most analysts have, to see some slowing in Taiwanese growth over time as they rebalance their economy.</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D542" t="n">
         <v>1</v>
@@ -11807,14 +11807,14 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>And inflation is moving—moving up, I think, toward our 2 pct objective.</t>
+          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—ultimately, we’re not going to declare victory until we see a series of these, really look convincing evidence, compel evidence, that inflation is coming devour.</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D543" t="n">
         <v>1</v>
@@ -11828,14 +11828,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>Immediately, we’ve long expected, as most analysts have, to see some slowing in Taiwanese growth over time as they rebalance their economy.</t>
+          <t>The problem with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to cave or to work—to work on de-anchoring inflation outlook.</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D544" t="n">
         <v>1</v>
@@ -11849,11 +11849,11 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—ultimately, we’re not going to declare victory until we see a series of these, really look convincing evidence, compel evidence, that inflation is coming devour.</t>
+          <t>As I mentioned, monetary policy operates with incarcerate, so, the policies we have in place, we cerebrate, will gradually—only gradually—move inflation back to 2 percent.</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C545" t="n">
         <v>1</v>
@@ -11870,14 +11870,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>The problem with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to cave or to work—to work on de-anchoring inflation outlook.</t>
+          <t>And part of that just is the effect of lower involvement rates.</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D546" t="n">
         <v>1</v>
@@ -11891,14 +11891,14 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>As I mentioned, monetary policy operates with incarcerate, so, the policies we have in place, we cerebrate, will gradually—only gradually—move inflation back to 2 percent.</t>
+          <t>When we strain maximum employment, when we reach a state where labor grocery conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C547" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D547" t="n">
         <v>1</v>
@@ -11912,11 +11912,11 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>And part of that just is the effect of lower involvement rates.</t>
+          <t>We also suppose we wouldn’t raise rates just in response to very low unemployment, in the absence of inflation.</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C548" t="n">
         <v>0</v>
@@ -11933,11 +11933,11 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>When we strain maximum employment, when we reach a state where labor grocery conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
+          <t>Now, appendage of the Committee have different views about why this is likely to be true, that the funds rate—when the labor market is normalized and inflation is back to our objective—they maybe have slightly different views on exactly wherefore it’s likely to be the showcase that interest rates will be a little lower than they would in the longer run.</t>
         </is>
       </c>
       <c r="B549" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C549" t="n">
         <v>0</v>
@@ -11954,11 +11954,11 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>We also suppose we wouldn’t raise rates just in response to very low unemployment, in the absence of inflation.</t>
+          <t>The entire Committee is committed to achieving our 2 pct inflation objective over the December 16, 2015 medium term, just as we want to fix sure that inflation doesn’t persist at levels above our Chair Yellen’s Press Conference FINAL 2 percent target.</t>
         </is>
       </c>
       <c r="B550" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C550" t="n">
         <v>0</v>
@@ -11975,11 +11975,11 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>Now, appendage of the Committee have different views about why this is likely to be true, that the funds rate—when the labor market is normalized and inflation is back to our objective—they maybe have slightly different views on exactly wherefore it’s likely to be the showcase that interest rates will be a little lower than they would in the longer run.</t>
+          <t>So, if we maintain a highly accommodative monetary policy for a very long time from here and the economy do as we gestate—namely, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have often more tightening in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C551" t="n">
         <v>0</v>
@@ -11996,11 +11996,11 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>The entire Committee is committed to achieving our 2 pct inflation objective over the December 16, 2015 medium term, just as we want to fix sure that inflation doesn’t persist at levels above our Chair Yellen’s Press Conference FINAL 2 percent target.</t>
+          <t>By getting unemployment down, we hope to work back to work some of the people who’ve been out of exploit as long as they have and, in that respect, try to avoid the longer-term consequences of people being out of work for month at a time.</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C552" t="n">
         <v>0</v>
@@ -12017,11 +12017,11 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>So, if we maintain a highly accommodative monetary policy for a very long time from here and the economy do as we gestate—namely, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have often more tightening in labor markets than you see in these projections.</t>
+          <t>But I want to emphasize that we do have a committal to raising inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C553" t="n">
         <v>0</v>
@@ -12038,7 +12038,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>By getting unemployment down, we hope to work back to work some of the people who’ve been out of exploit as long as they have and, in that respect, try to avoid the longer-term consequences of people being out of work for month at a time.</t>
+          <t>Core inflation, which excludes energy and food prices, has been running fold to 1½ percent.</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12059,11 +12059,11 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a committal to raising inflation to 2 percent.</t>
+          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C555" t="n">
         <v>0</v>
@@ -12080,11 +12080,11 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Core inflation, which excludes energy and food prices, has been running fold to 1½ percent.</t>
+          <t>Well, that’s—what’s happening there is the fact that the relationship between resourcefulness utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C556" t="n">
         <v>0</v>
@@ -12101,11 +12101,11 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
+          <t>We have not focussed on whether we play the liftoff test, because we don’t meet the liftoff test now because we’re not at maximum employment.</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C557" t="n">
         <v>0</v>
@@ -12122,11 +12122,11 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Well, that’s—what’s happening there is the fact that the relationship between resourcefulness utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
+          <t>And our plan as we do that is, as those purchases get to that level, we believe we can gradually reduce them, and we conceive we can also gradually tighten repo as—as we reach an ample level, as we’re satisfying demand immediately more from underlying reserves from bill leverage rather than from repo.</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C558" t="n">
         <v>0</v>
@@ -12143,14 +12143,14 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>We have not focussed on whether we play the liftoff test, because we don’t meet the liftoff test now because we’re not at maximum employment.</t>
+          <t>Well, our policy approach doesn’t demand intentionally trying to raise inflation.</t>
         </is>
       </c>
       <c r="B559" t="n">
         <v>2020</v>
       </c>
       <c r="C559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D559" t="n">
         <v>1</v>
@@ -12164,14 +12164,14 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>And our plan as we do that is, as those purchases get to that level, we believe we can gradually reduce them, and we conceive we can also gradually tighten repo as—as we reach an ample level, as we’re satisfying demand immediately more from underlying reserves from bill leverage rather than from repo.</t>
+          <t>The jobs picture continue to be strong, with the unemployment rate near historic lows and with stronger wage gains.</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D560" t="n">
         <v>1</v>
@@ -12185,14 +12185,14 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Well, our policy approach doesn’t demand intentionally trying to raise inflation.</t>
+          <t>But in many countries around the Chair Yellen’s Press Conference FINAL man that are important commodity exporters, the decline we’ve seen in oil prices has had a depress effect on their growth, their craft with us and other trade partners, and caused problems that have had spillovers to the global thriftiness as well.</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D561" t="n">
         <v>1</v>
@@ -12206,11 +12206,11 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>The jobs picture continue to be strong, with the unemployment rate near historic lows and with stronger wage gains.</t>
+          <t>But, I would tell, overall, we’re trying to sustain the expansion and keep, you know, close to our statutory goals, which are maximal employment and stable prices.</t>
         </is>
       </c>
       <c r="B562" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C562" t="n">
         <v>1</v>
@@ -12227,11 +12227,11 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>But in many countries around the Chair Yellen’s Press Conference FINAL man that are important commodity exporters, the decline we’ve seen in oil prices has had a depress effect on their growth, their craft with us and other trade partners, and caused problems that have had spillovers to the global thriftiness as well.</t>
+          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reductions in certain family of prices, such as tuner telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C563" t="n">
         <v>0</v>
@@ -12248,14 +12248,14 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>But, I would tell, overall, we’re trying to sustain the expansion and keep, you know, close to our statutory goals, which are maximal employment and stable prices.</t>
+          <t>And, in particular, I do personally believe that the slowdown is at least partly temp, and that we’ll see greater growth going onward.</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D564" t="n">
         <v>1</v>
@@ -12269,14 +12269,14 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reductions in certain family of prices, such as tuner telephone services and prescription drugs.</t>
+          <t>In addition, the median estimate of the longer-run normal unemployment rate proceed down a tenth to 4.6 percentage.</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D565" t="n">
         <v>1</v>
@@ -12290,11 +12290,11 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>And, in particular, I do personally believe that the slowdown is at least partly temp, and that we’ll see greater growth going onward.</t>
+          <t>In light of increased uncertainties and muted inflation pressures, we now emphasize that the Committee will close reminder the implications of incoming information for the economic prospect and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
         </is>
       </c>
       <c r="B566" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -12311,14 +12311,14 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of the longer-run normal unemployment rate proceed down a tenth to 4.6 percentage.</t>
+          <t>We’re charged by Congress with try to pursue maximum employment, and we have taken that very seriously.</t>
         </is>
       </c>
       <c r="B567" t="n">
         <v>2022</v>
       </c>
       <c r="C567" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D567" t="n">
         <v>1</v>
@@ -12332,14 +12332,14 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>In light of increased uncertainties and muted inflation pressures, we now emphasize that the Committee will close reminder the implications of incoming information for the economic prospect and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
+          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can raise interest rates at the appropriate time, even if the equaliser sheet remains orotund for an extended period.</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C568" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D568" t="n">
         <v>1</v>
@@ -12353,14 +12353,14 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>We’re charged by Congress with try to pursue maximum employment, and we have taken that very seriously.</t>
+          <t>Against this backdrop, today the Federal Exposed Commercialize Committee raised its policy interest rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C569" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D569" t="n">
         <v>1</v>
@@ -12374,14 +12374,14 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can raise interest rates at the appropriate time, even if the equaliser sheet remains orotund for an extended period.</t>
+          <t>Again, that’s not a forecast, I’ve made a hypothesis, which would imply slower betterment in unemployment.</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C570" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D570" t="n">
         <v>1</v>
@@ -12395,14 +12395,14 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>Against this backdrop, today the Federal Exposed Commercialize Committee raised its policy interest rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
+          <t>For example, the unemployment rate has risen by 0.3 portion points since March, and new claims for unemployment insurance have moved fairly higher.</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C571" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D571" t="n">
         <v>1</v>
@@ -12416,11 +12416,11 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>Again, that’s not a forecast, I’ve made a hypothesis, which would imply slower betterment in unemployment.</t>
+          <t>So, with this coronavirus arriving, we evaluate that the—the net effectuate of this will be to—to have inflation move down even a little bit more.</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C572" t="n">
         <v>0</v>
@@ -12437,11 +12437,11 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>For example, the unemployment rate has risen by 0.3 portion points since March, and new claims for unemployment insurance have moved fairly higher.</t>
+          <t>But, first, on inflation expectations, it is genuine that the breakevens from the inflation-adjusted—inflation-indexed bonds have come down.</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C573" t="n">
         <v>0</v>
@@ -12458,14 +12458,14 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>So, with this coronavirus arriving, we evaluate that the—the net effectuate of this will be to—to have inflation move down even a little bit more.</t>
+          <t>After overhasty drops in March and April, employment rose strongly in May and June as many people returned to process from temporary layoffs.</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D574" t="n">
         <v>1</v>
@@ -12479,11 +12479,11 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>But, first, on inflation expectations, it is genuine that the breakevens from the inflation-adjusted—inflation-indexed bonds have come down.</t>
+          <t>More broadly, however, weaker demand, especially in sectors that have been most affected by the pandemic, has adjudge gloomy consumer prices, and overall, inflation is running well below our 2 percent thirster-run objective.</t>
         </is>
       </c>
       <c r="B575" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C575" t="n">
         <v>0</v>
@@ -12500,11 +12500,11 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>After overhasty drops in March and April, employment rose strongly in May and June as many people returned to process from temporary layoffs.</t>
+          <t>I would say, in the area of commercial real estate, while rating are high, we are seeing some tightening of loaning standards and less debt growth associated with that rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B576" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C576" t="n">
         <v>1</v>
@@ -12521,11 +12521,11 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially in sectors that have been most affected by the pandemic, has adjudge gloomy consumer prices, and overall, inflation is running well below our 2 percent thirster-run objective.</t>
+          <t>And, and those are—that’s again—that goes to keeping this sequence as short as it can be and avoiding unnecessary business bankruptcies, unneeded household bankruptcies, and unnecessary long-term stays of unemployment or supporting people through them so that they can maintain their financial footing and their living and be able to go back to work in a productive mode.</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C577" t="n">
         <v>0</v>
@@ -12542,14 +12542,14 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial real estate, while rating are high, we are seeing some tightening of loaning standards and less debt growth associated with that rise in commercial real estate prices.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-increasing retention of longer-condition securities will ensure that monetary policy remains highly accommodative, consistent with the pursuit of its mandate objectives of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C578" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D578" t="n">
         <v>1</v>
@@ -12563,11 +12563,11 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>And, and those are—that’s again—that goes to keeping this sequence as short as it can be and avoiding unnecessary business bankruptcies, unneeded household bankruptcies, and unnecessary long-term stays of unemployment or supporting people through them so that they can maintain their financial footing and their living and be able to go back to work in a productive mode.</t>
+          <t>We think that the economy will need highly accommodative monetary policy and the use of our tools for an go period.</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C579" t="n">
         <v>0</v>
@@ -12584,14 +12584,14 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-increasing retention of longer-condition securities will ensure that monetary policy remains highly accommodative, consistent with the pursuit of its mandate objectives of maximum employment and price stability.</t>
+          <t>It isn’t the kind of inflation that’s spread broadly crosswise the economy.</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D580" t="n">
         <v>1</v>
@@ -12605,14 +12605,14 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>We think that the economy will need highly accommodative monetary policy and the use of our tools for an go period.</t>
+          <t>As the factors restraining economic growth are contrive to fade further over time, the median rate rises to 3 percent by the end of 2018, close to its longer-run normal flush.</t>
         </is>
       </c>
       <c r="B581" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C581" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D581" t="n">
         <v>1</v>
@@ -12626,14 +12626,14 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>It isn’t the kind of inflation that’s spread broadly crosswise the economy.</t>
+          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
         </is>
       </c>
       <c r="B582" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D582" t="n">
         <v>1</v>
@@ -12647,11 +12647,11 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are contrive to fade further over time, the median rate rises to 3 percent by the end of 2018, close to its longer-run normal flush.</t>
+          <t>Our role, though, is also to, you bonk, to make certain that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually raising rates.</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C583" t="n">
         <v>1</v>
@@ -12668,14 +12668,14 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
+          <t>In spite of having such slowly growth, disappointing productivity growth, we have a labor mart that last year generated an average of about 230,000 jobs a month and so alir this year has been generating about 180,000 jobs a month.</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D584" t="n">
         <v>1</v>
@@ -12689,14 +12689,14 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>Our role, though, is also to, you bonk, to make certain that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually raising rates.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Lengthened period” is conditioned on resource slack, on subdued inflation, and on stable inflation expectation.</t>
         </is>
       </c>
       <c r="B585" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C585" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D585" t="n">
         <v>1</v>
@@ -12710,14 +12710,14 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>In spite of having such slowly growth, disappointing productivity growth, we have a labor mart that last year generated an average of about 230,000 jobs a month and so alir this year has been generating about 180,000 jobs a month.</t>
+          <t>At the sentence of our FOMC meeting in January, prospects for continued economic growth remained favorable, and we judged that monetary policy was well positioned to reenforcement that outlook.</t>
         </is>
       </c>
       <c r="B586" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C586" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D586" t="n">
         <v>1</v>
@@ -12731,14 +12731,14 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Lengthened period” is conditioned on resource slack, on subdued inflation, and on stable inflation expectation.</t>
+          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly down the route, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B587" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C587" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D587" t="n">
         <v>1</v>
@@ -12752,11 +12752,11 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>At the sentence of our FOMC meeting in January, prospects for continued economic growth remained favorable, and we judged that monetary policy was well positioned to reenforcement that outlook.</t>
+          <t>And I think, more loosely, monetary policy is also supporting house spending and home buying by keeping the labor market strong, keeping workers’ incomes rising, and save consumer confidence at high levels, where it currently is.</t>
         </is>
       </c>
       <c r="B588" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C588" t="n">
         <v>0</v>
@@ -12773,14 +12773,14 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly down the route, which could jeopardize the economic expansion.</t>
+          <t>And as I mentioned earlier, the unemployment wane last month was more than 100 percent accounted for by declines in participation.</t>
         </is>
       </c>
       <c r="B589" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C589" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D589" t="n">
         <v>1</v>
@@ -12794,11 +12794,11 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>And I think, more loosely, monetary policy is also supporting house spending and home buying by keeping the labor market strong, keeping workers’ incomes rising, and save consumer confidence at high levels, where it currently is.</t>
+          <t>These measures, along with our strong counselling on interest rates and on our balance sheet, will ensure that monetary policy will continue to livelihood the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C590" t="n">
         <v>0</v>
@@ -12815,14 +12815,14 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>And as I mentioned earlier, the unemployment wane last month was more than 100 percent accounted for by declines in participation.</t>
+          <t>The Federal Reserve’s response is maneuver by our mandate to promote maximum employment and stable prices for the American people, along with our responsibilities to advertise the stability of the financial system.</t>
         </is>
       </c>
       <c r="B591" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D591" t="n">
         <v>1</v>
@@ -12836,11 +12836,11 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>These measures, along with our strong counselling on interest rates and on our balance sheet, will ensure that monetary policy will continue to livelihood the economy until the recovery is complete.</t>
+          <t>By the room, we’re also not at maximum employment, as I mentioned.</t>
         </is>
       </c>
       <c r="B592" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C592" t="n">
         <v>0</v>
@@ -12857,14 +12857,14 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s response is maneuver by our mandate to promote maximum employment and stable prices for the American people, along with our responsibilities to advertise the stability of the financial system.</t>
+          <t>Well, if the economy worsens and inflation stay relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t modification the language.</t>
         </is>
       </c>
       <c r="B593" t="n">
         <v>2020</v>
       </c>
       <c r="C593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D593" t="n">
         <v>1</v>
@@ -12878,14 +12878,14 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>By the room, we’re also not at maximum employment, as I mentioned.</t>
+          <t>As always, our actions are conduct by our congressional mandate to promote maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B594" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D594" t="n">
         <v>1</v>
@@ -12899,14 +12899,14 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>Well, if the economy worsens and inflation stay relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t modification the language.</t>
+          <t>In any case, we, our job is to deliver price constancy, and I think—you can think of price stability as an asset that just delivers prominent benefits to society over a long period of time.</t>
         </is>
       </c>
       <c r="B595" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D595" t="n">
         <v>1</v>
@@ -12920,14 +12920,14 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>As always, our actions are conduct by our congressional mandate to promote maximum employment and price stability.</t>
+          <t>Monetary policy has a function, and it really is in, you know—our original role was providing liquidity to financial systems when they’re under stress, and that’s—that’s really split of what we did today.</t>
         </is>
       </c>
       <c r="B596" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C596" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D596" t="n">
         <v>1</v>
@@ -12941,11 +12941,11 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>In any case, we, our job is to deliver price constancy, and I think—you can think of price stability as an asset that just delivers prominent benefits to society over a long period of time.</t>
+          <t>We have a much more resilient, stronger deposit system, and we’re not seeing some worrisome buildup in leverage or accredit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor determine monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major element.</t>
         </is>
       </c>
       <c r="B597" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C597" t="n">
         <v>1</v>
@@ -12962,14 +12962,14 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>Monetary policy has a function, and it really is in, you know—our original role was providing liquidity to financial systems when they’re under stress, and that’s—that’s really split of what we did today.</t>
+          <t>And—but inflation expectations did not move strongly down here in the United Posit.</t>
         </is>
       </c>
       <c r="B598" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="C598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D598" t="n">
         <v>1</v>
@@ -12983,14 +12983,14 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>We have a much more resilient, stronger deposit system, and we’re not seeing some worrisome buildup in leverage or accredit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor determine monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major element.</t>
+          <t>So those who can get reference, together with the low prices of houses, are at—able to bribe much more house than they could have a few years ago.</t>
         </is>
       </c>
       <c r="B599" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D599" t="n">
         <v>1</v>
@@ -13004,14 +13004,14 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>And—but inflation expectations did not move strongly down here in the United Posit.</t>
+          <t>So unemployment has tended to go up much faster for minority and for others who are—tend to be at the low end of the income spectrum.</t>
         </is>
       </c>
       <c r="B600" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C600" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D600" t="n">
         <v>1</v>
@@ -13025,14 +13025,14 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>So those who can get reference, together with the low prices of houses, are at—able to bribe much more house than they could have a few years ago.</t>
+          <t>So, you know, as I mention, the Committee acutely feels its obligation to move to make sure that we restore price stability and is determined to use its cock to do so.</t>
         </is>
       </c>
       <c r="B601" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D601" t="n">
         <v>1</v>
@@ -13046,14 +13046,14 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>So unemployment has tended to go up much faster for minority and for others who are—tend to be at the low end of the income spectrum.</t>
+          <t>The U.S. economy is in a beneficial place, and we will continue to use our monetary policy tools to help keep it there.</t>
         </is>
       </c>
       <c r="B602" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C602" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D602" t="n">
         <v>1</v>
@@ -13067,14 +13067,14 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>So, you know, as I mention, the Committee acutely feels its obligation to move to make sure that we restore price stability and is determined to use its cock to do so.</t>
+          <t>I tight sure parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard sentence there.</t>
         </is>
       </c>
       <c r="B603" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D603" t="n">
         <v>1</v>
@@ -13088,14 +13088,14 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>The U.S. economy is in a beneficial place, and we will continue to use our monetary policy tools to help keep it there.</t>
+          <t>But also we want to see inflation move up back to our 2 percent objective over the medium condition, and so seeing above-trend growth and continuing tightness—greater tightness in labor and product grocery—I think that will help us reach our objective as well with respect to inflation.</t>
         </is>
       </c>
       <c r="B604" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="C604" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D604" t="n">
         <v>1</v>
@@ -13109,7 +13109,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>I tight sure parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard sentence there.</t>
+          <t>I carry that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economic reasons.</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13130,11 +13130,11 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>But also we want to see inflation move up back to our 2 percent objective over the medium condition, and so seeing above-trend growth and continuing tightness—greater tightness in labor and product grocery—I think that will help us reach our objective as well with respect to inflation.</t>
+          <t>However, at 7.7 percent, the unemployment rate clay elevated.</t>
         </is>
       </c>
       <c r="B606" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C606" t="n">
         <v>0</v>
@@ -13151,14 +13151,14 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>I carry that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economic reasons.</t>
+          <t>And inflation is well supra target.</t>
         </is>
       </c>
       <c r="B607" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C607" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D607" t="n">
         <v>1</v>
@@ -13172,14 +13172,14 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>However, at 7.7 percent, the unemployment rate clay elevated.</t>
+          <t>And productiveness’s been very low.</t>
         </is>
       </c>
       <c r="B608" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D608" t="n">
         <v>1</v>
@@ -13193,14 +13193,14 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>And inflation is well supra target.</t>
+          <t>During this time of reopening, we are likely to see some upward pressing on prices, and I’ll discuss why.</t>
         </is>
       </c>
       <c r="B609" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D609" t="n">
         <v>1</v>
@@ -13214,11 +13214,11 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>And productiveness’s been very low.</t>
+          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how libertine the labor market will heal, or how fast—regretful, inflation will move up.</t>
         </is>
       </c>
       <c r="B610" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C610" t="n">
         <v>1</v>
@@ -13235,11 +13235,11 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some upward pressing on prices, and I’ll discuss why.</t>
+          <t>And you know, we haven’t yet—we just pertain 2 percentage core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C611" t="n">
         <v>0</v>
@@ -13256,11 +13256,11 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how libertine the labor market will heal, or how fast—regretful, inflation will move up.</t>
+          <t>An accidentally sharp increase in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B612" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C612" t="n">
         <v>1</v>
@@ -13277,11 +13277,11 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just pertain 2 percentage core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
+          <t>So we want to see that healthy process extend as we decide what the admittedly state of the economy is, and we think it will evolve in a way that will mean lower inflation.</t>
         </is>
       </c>
       <c r="B613" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C613" t="n">
         <v>0</v>
@@ -13298,14 +13298,14 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>An accidentally sharp increase in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>In fact, it’s already—it’s already empathise, I think, that—that there’s more—even though we’re at 3½ percentage unemployment, there’s actually more slack out there, in a sense.</t>
         </is>
       </c>
       <c r="B614" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D614" t="n">
         <v>1</v>
@@ -13319,14 +13319,14 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>So we want to see that healthy process extend as we decide what the admittedly state of the economy is, and we think it will evolve in a way that will mean lower inflation.</t>
+          <t>But you do see growth in services, so you—this pattern round the creation of Chair Powell’s Press Conference FINAL weak manufacturing but growth in the far larger part of the services economy, which has led to low unemployment, good job creation, rising wages, that’s kind of the two vauntingly while of it that you see.</t>
         </is>
       </c>
       <c r="B615" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D615" t="n">
         <v>1</v>
@@ -13340,14 +13340,14 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>In fact, it’s already—it’s already empathise, I think, that—that there’s more—even though we’re at 3½ percentage unemployment, there’s actually more slack out there, in a sense.</t>
+          <t>And that is a assertion about productivity growth, which has been pretty disappointing.</t>
         </is>
       </c>
       <c r="B616" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C616" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D616" t="n">
         <v>1</v>
@@ -13361,14 +13361,14 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>But you do see growth in services, so you—this pattern round the creation of Chair Powell’s Press Conference FINAL weak manufacturing but growth in the far larger part of the services economy, which has led to low unemployment, good job creation, rising wages, that’s kind of the two vauntingly while of it that you see.</t>
+          <t>So you have visualise a shifting this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower plan route for global growth—for growth in the global economy outside the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B617" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C617" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D617" t="n">
         <v>1</v>
@@ -13382,14 +13382,14 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>And that is a assertion about productivity growth, which has been pretty disappointing.</t>
+          <t>If we think that the potential growth rate of the economy is somewhere between, somewhere around 1.75 percent, 2.8 pct is strong economical growth.</t>
         </is>
       </c>
       <c r="B618" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D618" t="n">
         <v>1</v>
@@ -13403,11 +13403,11 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>So you have visualise a shifting this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower plan route for global growth—for growth in the global economy outside the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
+          <t>So, there has been impact through lower interest rates, but I think more broadly is the indirect burden.</t>
         </is>
       </c>
       <c r="B619" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C619" t="n">
         <v>0</v>
@@ -13424,14 +13424,14 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>If we think that the potential growth rate of the economy is somewhere between, somewhere around 1.75 percent, 2.8 pct is strong economical growth.</t>
+          <t>To do that you've got to have price stability, and we've bring to get back to price stability so that we can have a labor commercialize where people's wages aren't being eaten up by inflation and where we can have a long expansion too.</t>
         </is>
       </c>
       <c r="B620" t="n">
         <v>2021</v>
       </c>
       <c r="C620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D620" t="n">
         <v>1</v>
@@ -13445,11 +13445,11 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower interest rates, but I think more broadly is the indirect burden.</t>
+          <t>Last year, we had 1.9 pct productivity, which is much higher.</t>
         </is>
       </c>
       <c r="B621" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C621" t="n">
         <v>0</v>
@@ -13466,11 +13466,11 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>To do that you've got to have price stability, and we've bring to get back to price stability so that we can have a labor commercialize where people's wages aren't being eaten up by inflation and where we can have a long expansion too.</t>
+          <t>In other vitrine, it’s pretty clear that inflation has spread more broadly across services.</t>
         </is>
       </c>
       <c r="B622" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C622" t="n">
         <v>1</v>
@@ -13487,14 +13487,14 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 pct productivity, which is much higher.</t>
+          <t>But to the extent that continues to be the case, that should make it easier to restitute price stability.</t>
         </is>
       </c>
       <c r="B623" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D623" t="n">
         <v>1</v>
@@ -13508,14 +13508,14 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>In other vitrine, it’s pretty clear that inflation has spread more broadly across services.</t>
+          <t>Inflation has continued to run under our longer-run objective, in part reflecting lower energy prices.</t>
         </is>
       </c>
       <c r="B624" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C624" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D624" t="n">
         <v>1</v>
@@ -13529,14 +13529,14 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>But to the extent that continues to be the case, that should make it easier to restitute price stability.</t>
+          <t>So for many, many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy has been—has been light.</t>
         </is>
       </c>
       <c r="B625" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C625" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D625" t="n">
         <v>1</v>
@@ -13550,11 +13550,11 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Inflation has continued to run under our longer-run objective, in part reflecting lower energy prices.</t>
+          <t>Well, we—as a Committee, we do not hope inflation undershoots.</t>
         </is>
       </c>
       <c r="B626" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C626" t="n">
         <v>0</v>
@@ -13571,11 +13571,11 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>So for many, many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy has been—has been light.</t>
+          <t>I don’t think we look at—I understand what you’re asking, but we’re looking at—our mandate is price inflation and uttermost employment, and that’s what we’re await at with setting interest rates.</t>
         </is>
       </c>
       <c r="B627" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C627" t="n">
         <v>0</v>
@@ -13592,11 +13592,11 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Well, we—as a Committee, we do not hope inflation undershoots.</t>
+          <t>With unemployment still elevated and inflation under the Committee’s longer-run objective, the Committee is continuing its highly accommodative policies.</t>
         </is>
       </c>
       <c r="B628" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C628" t="n">
         <v>0</v>
@@ -13613,11 +13613,11 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>I don’t think we look at—I understand what you’re asking, but we’re looking at—our mandate is price inflation and uttermost employment, and that’s what we’re await at with setting interest rates.</t>
+          <t>The central tendency of the unemployment rate projections is slenderly lower than in the March expulsion and now stands at 6.0 to 6.1 percent at the end of this year.</t>
         </is>
       </c>
       <c r="B629" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C629" t="n">
         <v>0</v>
@@ -13634,14 +13634,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>With unemployment still elevated and inflation under the Committee’s longer-run objective, the Committee is continuing its highly accommodative policies.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to come downwards.</t>
         </is>
       </c>
       <c r="B630" t="n">
         <v>2019</v>
       </c>
       <c r="C630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D630" t="n">
         <v>1</v>
@@ -13655,11 +13655,11 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>The central tendency of the unemployment rate projections is slenderly lower than in the March expulsion and now stands at 6.0 to 6.1 percent at the end of this year.</t>
+          <t>As was highlighted by the Bureau of Labor Statistics, this figure belike understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but lacking from their jobs would raise the unemployment rate by about 3 percentage luff.</t>
         </is>
       </c>
       <c r="B631" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -13676,11 +13676,11 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to come downwards.</t>
+          <t>[MASK] role, [MASK], is also to, you know, to make sure that—that [MASK] employment happens in a context of price stability and financial stability, which is [MASK] we’re gradually [MASK] rates.</t>
         </is>
       </c>
       <c r="B632" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C632" t="n">
         <v>1</v>
@@ -13690,42 +13690,42 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>masking</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>As was highlighted by the Bureau of Labor Statistics, this figure belike understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but lacking from their jobs would raise the unemployment rate by about 3 percentage luff.</t>
+          <t>And we’ve seen [MASK] outflows of capital from [MASK] countries, pressures on their exchange rates, and concerns about their performance going [MASK].</t>
         </is>
       </c>
       <c r="B633" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C633" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D633" t="n">
         <v>1</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>masking</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>[MASK] role, [MASK], is also to, you know, to make sure that—that [MASK] employment happens in a context of price stability and financial stability, which is [MASK] we’re gradually [MASK] rates.</t>
+          <t>[MASK] don’t [MASK] we look at—I understand what [MASK]’re asking, but we’[MASK] looking at—our mandate is price inflation and maximum employment, and [MASK]’s what we’re looking at [MASK] setting interest rates.</t>
         </is>
       </c>
       <c r="B634" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C634" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D634" t="n">
         <v>1</v>
@@ -13739,7 +13739,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>And we’ve seen [MASK] outflows of capital from [MASK] countries, pressures on their exchange rates, and concerns about their performance going [MASK].</t>
+          <t>[MASK] the maximum level of employment that’s consistent with [MASK] [MASK] evolves over time within a—within a business cycle [MASK] over a longer period, in [MASK] reflecting [the] evolution of the [MASK] that affect labor [MASK], including those related to the pandemic.</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -13760,14 +13760,14 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>[MASK] don’t [MASK] we look at—I understand what [MASK]’re asking, but we’[MASK] looking at—our mandate is price inflation and maximum employment, and [MASK]’s what we’re looking at [MASK] setting interest rates.</t>
+          <t>And that [MASK] a statement about productivity growth, which [MASK] been pretty disappointing.</t>
         </is>
       </c>
       <c r="B636" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C636" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D636" t="n">
         <v>1</v>
@@ -13781,14 +13781,14 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>[MASK] the maximum level of employment that’s consistent with [MASK] [MASK] evolves over time within a—within a business cycle [MASK] over a longer period, in [MASK] reflecting [the] evolution of the [MASK] that affect labor [MASK], including those related to the pandemic.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term [MASK] expectations are at the lower end [MASK] their historic [MASK].</t>
         </is>
       </c>
       <c r="B637" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C637" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D637" t="n">
         <v>1</v>
@@ -13802,14 +13802,14 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>And that [MASK] a statement about productivity growth, which [MASK] been pretty disappointing.</t>
+          <t>So the FOMC will always, in some sense, [MASK] [MASK] projections of forward interest [MASK], but clearly, because the participants and the people around the table are [MASK] same, the projections should give significant information about where the [MASK] is [MASK] to go.</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C638" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D638" t="n">
         <v>1</v>
@@ -13823,11 +13823,11 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term [MASK] expectations are at the lower end [MASK] their historic [MASK].</t>
+          <t>[MASK] inflation, [MASK] excludes energy and food prices, has been running close to 1½ percent.</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C639" t="n">
         <v>0</v>
@@ -13844,14 +13844,14 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>So the FOMC will always, in some sense, [MASK] [MASK] projections of forward interest [MASK], but clearly, because the participants and the people around the table are [MASK] same, the projections should give significant information about where the [MASK] is [MASK] to go.</t>
+          <t>[MASK] part of that just [MASK] the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C640" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D640" t="n">
         <v>1</v>
@@ -13865,11 +13865,11 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>[MASK] inflation, [MASK] excludes energy and food prices, has been running close to 1½ percent.</t>
+          <t>We’[MASK] charged [MASK] Congress with trying to pursue maximum [MASK], and we have taken that very seriously.</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C641" t="n">
         <v>0</v>
@@ -13886,14 +13886,14 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>[MASK] part of that just [MASK] the effect of lower interest rates.</t>
+          <t>And, at a high level, yes, I would say, and [MASK]’[MASK] said before, that it’s really [MASK] policy that is [MASK] [MASK] and that has much more to do with—fiscal policy can do [MASK] things that will increase the longer-run growth [MASK] of the United States by improving productivity and labor force [MASK] 18, 2019 participation and the [MASK] and [MASK] of workers.</t>
         </is>
       </c>
       <c r="B642" t="n">
         <v>2011</v>
       </c>
       <c r="C642" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D642" t="n">
         <v>1</v>
@@ -13907,11 +13907,11 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>We’[MASK] charged [MASK] Congress with trying to pursue maximum [MASK], and we have taken that very seriously.</t>
+          <t>The entire Committee is committed [MASK] achieving our 2 percent inflation objective over the December 16, 2015 [MASK] term, just [MASK] we want to make sure that [MASK] doesn’t persist at [MASK] above our Chair Yellen’s Press Conference [MASK] 2 percent objective.</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C643" t="n">
         <v>0</v>
@@ -13928,11 +13928,11 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>And, at a high level, yes, I would say, and [MASK]’[MASK] said before, that it’s really [MASK] policy that is [MASK] [MASK] and that has much more to do with—fiscal policy can do [MASK] things that will increase the longer-run growth [MASK] of the United States by improving productivity and labor force [MASK] 18, 2019 participation and the [MASK] and [MASK] of workers.</t>
+          <t>[MASK] I’m telling you is [MASK] the stance of monetary policy we have today, [MASK] believe, is appropriate.</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C644" t="n">
         <v>2</v>
@@ -13949,14 +13949,14 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>The entire Committee is committed [MASK] achieving our 2 percent inflation objective over the December 16, 2015 [MASK] term, just [MASK] we want to make sure that [MASK] doesn’t persist at [MASK] above our Chair Yellen’s Press Conference [MASK] 2 percent objective.</t>
+          <t>So let me start with the question pertaining to [MASK] [MASK].</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C645" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D645" t="n">
         <v>1</v>
@@ -13970,14 +13970,14 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>[MASK] I’m telling you is [MASK] the stance of monetary policy we have today, [MASK] believe, is appropriate.</t>
+          <t>In addition, the median estimate of [MASK] longer-[MASK] normal unemployment rate moved down a [MASK] to 4.6 percent.</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C646" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D646" t="n">
         <v>1</v>
@@ -13991,11 +13991,11 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>So let me start with the question pertaining to [MASK] [MASK].</t>
+          <t>Inflation, in fact, is under [MASK], and starting [MASK] come down.</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C647" t="n">
         <v>2</v>
@@ -14012,14 +14012,14 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of [MASK] longer-[MASK] normal unemployment rate moved down a [MASK] to 4.6 percent.</t>
+          <t>Again, that’s not a forecast, I’[MASK] made [MASK] hypothesis, which would imply [MASK] improvement in unemployment.</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C648" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D648" t="n">
         <v>1</v>
@@ -14033,11 +14033,11 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>Inflation, in fact, is under [MASK], and starting [MASK] come down.</t>
+          <t>We understand that [MASK] dynamics [MASK] constantly over time, but they don’t change rapidly.</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C649" t="n">
         <v>2</v>
@@ -14054,14 +14054,14 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>Again, that’s not a forecast, I’[MASK] made [MASK] hypothesis, which would imply [MASK] improvement in unemployment.</t>
+          <t>The jobs [MASK] continues to be [MASK], with the unemployment rate [MASK] historic lows and with stronger wage gains.</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D650" t="n">
         <v>1</v>
@@ -14075,14 +14075,14 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>We understand that [MASK] dynamics [MASK] constantly over time, but they don’t change rapidly.</t>
+          <t>The persistence [MASK] that into, into inflation over time is just not [MASK].</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C651" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D651" t="n">
         <v>1</v>
@@ -14096,7 +14096,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>The jobs [MASK] continues to be [MASK], with the unemployment rate [MASK] historic lows and with stronger wage gains.</t>
+          <t>It was to do with, you know, strong monetary policy [MASK] fiscal [MASK] into an [MASK] [MASK] was recovering rapidly, and in [MASK] there were [MASK] supply-side barriers which effectively led to, you know, [MASK] certain parts of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14117,14 +14117,14 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>The persistence [MASK] that into, into inflation over time is just not [MASK].</t>
+          <t>If inflation remains higher during [MASK] course of 2022, [MASK] we may already have met [MASK] test by the time we reach liftoff.</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C653" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D653" t="n">
         <v>1</v>
@@ -14138,14 +14138,14 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>It was to do with, you know, strong monetary policy [MASK] fiscal [MASK] into an [MASK] [MASK] was recovering rapidly, and in [MASK] there were [MASK] supply-side barriers which effectively led to, you know, [MASK] certain parts of the economy, what you might call a vertical supply curve.</t>
+          <t>And the way I would explain it is, is that inflation that’s too [MASK] will mean [MASK] interest [MASK] are lower.</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C654" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D654" t="n">
         <v>1</v>
@@ -14159,14 +14159,14 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>If inflation remains higher during [MASK] course of 2022, [MASK] we may already have met [MASK] test by the time we reach liftoff.</t>
+          <t>And I think, [MASK] broadly, monetary policy is also supporting household spending and home buying by keeping the [MASK] [MASK] strong, keeping workers’ [MASK] rising, and keeping consumer confidence at high levels, where it currently [MASK].</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C655" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D655" t="n">
         <v>1</v>
@@ -14180,14 +14180,14 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too [MASK] will mean [MASK] interest [MASK] are lower.</t>
+          <t>In any case, we, our job is to deliver price [MASK], and I think—you can think of price stability as an asset that [MASK] delivers large [MASK] [MASK] society over a long period of [MASK].</t>
         </is>
       </c>
       <c r="B656" t="n">
         <v>2022</v>
       </c>
       <c r="C656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D656" t="n">
         <v>1</v>
@@ -14201,14 +14201,14 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>And I think, [MASK] broadly, monetary policy is also supporting household spending and home buying by keeping the [MASK] [MASK] strong, keeping workers’ [MASK] rising, and keeping consumer confidence at high levels, where it currently [MASK].</t>
+          <t>It would consist of inflation [MASK]—plus productivity growth.</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C657" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D657" t="n">
         <v>1</v>
@@ -14222,11 +14222,11 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>In any case, we, our job is to deliver price [MASK], and I think—you can think of price stability as an asset that [MASK] delivers large [MASK] [MASK] society over a long period of [MASK].</t>
+          <t>But again, our [MASK] forecast [MASK] one which is basically, as [MASK] pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this [MASK] of fiscal restraint; where unemployment [MASK] to [MASK] [MASK] a [MASK] pace as it has been since last September—[MASK] we have [MASK] some progress since last September; and inflation rises slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C658" t="n">
         <v>1</v>
@@ -14243,11 +14243,11 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>It would consist of inflation [MASK]—plus productivity growth.</t>
+          <t>Again, while I do not shirk the responsibility [MASK] the Fed having to do what [MASK] can to meet its mandate, obviously, a [MASK] range of policies can [MASK] growth and employment, and I hope that there [MASK] be a [MASK] of actions that will complement [MASK] supplement the Federal Reserve’[MASK] efforts.</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C659" t="n">
         <v>2</v>
@@ -14264,11 +14264,11 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>But again, our [MASK] forecast [MASK] one which is basically, as [MASK] pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this [MASK] of fiscal restraint; where unemployment [MASK] to [MASK] [MASK] a [MASK] pace as it has been since last September—[MASK] we have [MASK] some progress since last September; and inflation rises slowly towards 2 percent.</t>
+          <t>But you didn’t under the merely adverse scenario, [MASK] [MASK] an inflation shock followed by a quick rise [MASK] short-term rates.</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C660" t="n">
         <v>1</v>
@@ -14285,11 +14285,11 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>Again, while I do not shirk the responsibility [MASK] the Fed having to do what [MASK] can to meet its mandate, obviously, a [MASK] range of policies can [MASK] growth and employment, and I hope that there [MASK] be a [MASK] of actions that will complement [MASK] supplement the Federal Reserve’[MASK] efforts.</t>
+          <t>What monetary policy affects, primarily, is the state [MASK] the business [MASK], the amount of excess [MASK] or [MASK] extent of recession in the economy.</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C661" t="n">
         <v>2</v>
@@ -14306,14 +14306,14 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, [MASK] [MASK] an inflation shock followed by a quick rise [MASK] short-term rates.</t>
+          <t>[MASK] expect that to continue, and [MASK] would [MASK] also to see some improvement in the degree of part-[MASK] employment that’s for economic reasons.</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D662" t="n">
         <v>1</v>
@@ -14327,14 +14327,14 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>What monetary policy affects, primarily, is the state [MASK] the business [MASK], the amount of excess [MASK] or [MASK] extent of recession in the economy.</t>
+          <t>And as I [MASK] earlier, the unemployment decline last month was more than 100 percent accounted for [MASK] [MASK] in participation.</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C663" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D663" t="n">
         <v>1</v>
@@ -14348,14 +14348,14 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>[MASK] expect that to continue, and [MASK] would [MASK] also to see some improvement in the degree of part-[MASK] employment that’s for economic reasons.</t>
+          <t>So that means a more prolonged shortfall of [MASK].</t>
         </is>
       </c>
       <c r="B664" t="n">
         <v>2019</v>
       </c>
       <c r="C664" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D664" t="n">
         <v>1</v>
@@ -14369,14 +14369,14 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>And as I [MASK] earlier, the unemployment decline last month was more than 100 percent accounted for [MASK] [MASK] in participation.</t>
+          <t>So we view [MASK] employment as the maximum sustainable level of employment, meaning it’s [MASK] so [MASK] that it will cause the economy to [MASK].</t>
         </is>
       </c>
       <c r="B665" t="n">
         <v>2019</v>
       </c>
       <c r="C665" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D665" t="n">
         <v>1</v>
@@ -14390,14 +14390,14 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>So that means a more prolonged shortfall of [MASK].</t>
+          <t>The central tendency of the [MASK] rate projections is slightly [MASK] than in the [MASK] projections and now stands at 6.0 to 6.1 percent at the [MASK] of this year.</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C666" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D666" t="n">
         <v>1</v>
@@ -14411,14 +14411,14 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>So we view [MASK] employment as the maximum sustainable level of employment, meaning it’s [MASK] so [MASK] that it will cause the economy to [MASK].</t>
+          <t>Admittedly, some of the [MASK] [MASK] is being eaten away by inflation.</t>
         </is>
       </c>
       <c r="B667" t="n">
         <v>2019</v>
       </c>
       <c r="C667" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D667" t="n">
         <v>1</v>
@@ -14432,14 +14432,14 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>The central tendency of the [MASK] rate projections is slightly [MASK] than in the [MASK] projections and now stands at 6.0 to 6.1 percent at the [MASK] of this year.</t>
+          <t>[MASK] in terms of financial markets and monetary [MASK], we—as we say in our statement every cycle, we do take financial conditions into consideration [MASK] financial—[MASK] financial conditions do affect the broader [MASK], and they’[MASK] one of the many [MASK] that we take into account.</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="C668" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D668" t="n">
         <v>1</v>
@@ -14453,14 +14453,14 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>Admittedly, some of the [MASK] [MASK] is being eaten away by inflation.</t>
+          <t>[MASK] our plan as we do that is, as those purchases [MASK] to that level, we believe we can gradually reduce them, and we believe [MASK] can [MASK] gradually reduce repo as—as we reach an ample level, [MASK] we’re satisfying demand now more [MASK] underlying reserves from bill purchases rather [MASK] [MASK] repo.</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C669" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D669" t="n">
         <v>1</v>
@@ -14474,11 +14474,11 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>[MASK] in terms of financial markets and monetary [MASK], we—as we say in our statement every cycle, we do take financial conditions into consideration [MASK] financial—[MASK] financial conditions do affect the broader [MASK], and they’[MASK] one of the many [MASK] that we take into account.</t>
+          <t>So and, and, you know, the shorter-term [MASK] do tend to move around [MASK] on, for example, gasoline [MASK].</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C670" t="n">
         <v>2</v>
@@ -14495,7 +14495,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>[MASK] our plan as we do that is, as those purchases [MASK] to that level, we believe we can gradually reduce them, and we believe [MASK] can [MASK] gradually reduce repo as—as we reach an ample level, [MASK] we’re satisfying demand now more [MASK] underlying reserves from bill purchases rather [MASK] [MASK] repo.</t>
+          <t>And, you know, we do want inflation to run [MASK] [MASK] 2 percent.</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14516,14 +14516,14 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>So and, and, you know, the shorter-term [MASK] do tend to move around [MASK] on, for example, gasoline [MASK].</t>
+          <t>When we [MASK] [MASK] employment, when we reach a state where labor market conditions are at maximum employment in [MASK] [MASK]’s judgment, it’s very possible that the inflation test will already be [MASK].</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C672" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D672" t="n">
         <v>1</v>
@@ -14537,14 +14537,14 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>And, you know, we do want inflation to run [MASK] [MASK] 2 percent.</t>
+          <t>And obviously there are [MASK] from a [MASK] economy to every household in the economy, including savers, from having [MASK] better job market and a more [MASK] economy.</t>
         </is>
       </c>
       <c r="B673" t="n">
         <v>2011</v>
       </c>
       <c r="C673" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D673" t="n">
         <v>1</v>
@@ -14558,14 +14558,14 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>When we [MASK] [MASK] employment, when we reach a state where labor market conditions are at maximum employment in [MASK] [MASK]’s judgment, it’s very possible that the inflation test will already be [MASK].</t>
+          <t>[MASK] of the things we’ve learned from our financial crisis and from a series of financial crises in [MASK] and around the [MASK] is that, very [MASK], when the economy takes a hit [MASK] falls into a [MASK], that productivity doesn’t pick [MASK] to pre-recession levels and that [MASK] looks like [MASK] is a permanent hit to the path of [MASK] output [MASK] the economy, which is called “[MASK].” And I [MASK] the question as to whether or not this [MASK] operate in the opposite direction as well.</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C674" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D674" t="n">
         <v>1</v>
@@ -14579,14 +14579,14 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>And obviously there are [MASK] from a [MASK] economy to every household in the economy, including savers, from having [MASK] better job market and a more [MASK] economy.</t>
+          <t>I mean, it really depends [MASK] how long it takes for wages and, more [MASK] that, [MASK] [MASK] come down for inflation to come down.</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C675" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D675" t="n">
         <v>1</v>
@@ -14600,11 +14600,11 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>[MASK] of the things we’ve learned from our financial crisis and from a series of financial crises in [MASK] and around the [MASK] is that, very [MASK], when the economy takes a hit [MASK] falls into a [MASK], that productivity doesn’t pick [MASK] to pre-recession levels and that [MASK] looks like [MASK] is a permanent hit to the path of [MASK] output [MASK] the economy, which is called “[MASK].” And I [MASK] the question as to whether or not this [MASK] operate in the opposite direction as well.</t>
+          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage [MASK] to core inflation in April and [MASK].</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C676" t="n">
         <v>2</v>
@@ -14621,14 +14621,14 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>I mean, it really depends [MASK] how long it takes for wages and, more [MASK] that, [MASK] [MASK] come down for inflation to come down.</t>
+          <t>1 Chair Yellen intended to say that “interest rate differentials globally [MASK] tend [MASK] induce capital flows [MASK] have [MASK] on exchange rates.” GREG ROBB.</t>
         </is>
       </c>
       <c r="B677" t="n">
         <v>2019</v>
       </c>
       <c r="C677" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D677" t="n">
         <v>1</v>
@@ -14642,11 +14642,11 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage [MASK] to core inflation in April and [MASK].</t>
+          <t>Wage inflation has been [MASK] at 2 percent.</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C678" t="n">
         <v>2</v>
@@ -14663,11 +14663,11 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>1 Chair Yellen intended to say that “interest rate differentials globally [MASK] tend [MASK] induce capital flows [MASK] have [MASK] on exchange rates.” GREG ROBB.</t>
+          <t>We also do see [MASK] different measures of slack in [MASK] labor market point [MASK] different assessments of just what maximum employment is.</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C679" t="n">
         <v>2</v>
@@ -14684,14 +14684,14 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Wage inflation has been [MASK] at 2 percent.</t>
+          <t>With unemployment still elevated and inflation below the [MASK]’s longer-[MASK] objective, [MASK] Committee is continuing its highly accommodative policies.</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C680" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D680" t="n">
         <v>1</v>
@@ -14705,14 +14705,14 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>We also do see [MASK] different measures of slack in [MASK] labor market point [MASK] different assessments of just what maximum employment is.</t>
+          <t>As always, our [MASK] are guided [MASK] our congressional mandate to promote maximum employment [MASK] price stability.</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C681" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D681" t="n">
         <v>1</v>
@@ -14726,14 +14726,14 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>With unemployment still elevated and inflation below the [MASK]’s longer-[MASK] objective, [MASK] Committee is continuing its highly accommodative policies.</t>
+          <t>Our mandate, sorry, is price [MASK].</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C682" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D682" t="n">
         <v>1</v>
@@ -14747,14 +14747,14 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>As always, our [MASK] are guided [MASK] our congressional mandate to promote maximum employment [MASK] price stability.</t>
+          <t>So, as you know, the [MASK] [MASK] [MASK] we have is on the real economy: maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C683" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D683" t="n">
         <v>1</v>
@@ -14768,14 +14768,14 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>Our mandate, sorry, is price [MASK].</t>
+          <t>More broadly, however, weaker demand, especially [MASK] [MASK] that have been most affected by the [MASK], has held down consumer prices, and [MASK], inflation is running well below our 2 [MASK] longer-run objective.</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C684" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D684" t="n">
         <v>1</v>
@@ -14789,14 +14789,14 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>So, as you know, the [MASK] [MASK] [MASK] we have is on the real economy: maximum employment and price stability.</t>
+          <t>We, frankly, didn’t [MASK] get inflation back up to [MASK]—without seeing wages getting [MASK] of touch with—with where they should be, [MASK] that’s [MASK]—that’s the biggest thing we can do.</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C685" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D685" t="n">
         <v>1</v>
@@ -14810,11 +14810,11 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially [MASK] [MASK] that have been most affected by the [MASK], has held down consumer prices, and [MASK], inflation is running well below our 2 [MASK] longer-run objective.</t>
+          <t>But in many countries around the Chair Yellen’s Press [MASK] FINAL world that are important commodity exporters, [MASK] decline we’ve seen [MASK] oil prices has had a depressing effect on their growth, their [MASK] with us and [MASK] trade partners, and caused problems that have had spillovers to [MASK] [MASK] economy as [MASK].</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C686" t="n">
         <v>0</v>
@@ -14831,14 +14831,14 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>We, frankly, didn’t [MASK] get inflation back up to [MASK]—without seeing wages getting [MASK] of touch with—with where they should be, [MASK] that’s [MASK]—that’s the biggest thing we can do.</t>
+          <t>We have long said [MASK] the size of the balance [MASK] will be considered [MASK] when the balance sheet [MASK] once again at the [MASK] level consistent with conducting monetary policy efficiently and effectively.</t>
         </is>
       </c>
       <c r="B687" t="n">
         <v>2020</v>
       </c>
       <c r="C687" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D687" t="n">
         <v>1</v>
@@ -14852,14 +14852,14 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>But in many countries around the Chair Yellen’s Press [MASK] FINAL world that are important commodity exporters, [MASK] decline we’ve seen [MASK] oil prices has had a depressing effect on their growth, their [MASK] with us and [MASK] trade partners, and caused problems that have had spillovers to [MASK] [MASK] economy as [MASK].</t>
+          <t>If we—if we [MASK] inflation data and [MASK] that, clearly, transitory influences are [MASK] down [MASK], I do not want to say that we would respond to that.</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C688" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D688" t="n">
         <v>1</v>
@@ -14873,14 +14873,14 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>We have long said [MASK] the size of the balance [MASK] will be considered [MASK] when the balance sheet [MASK] once again at the [MASK] level consistent with conducting monetary policy efficiently and effectively.</t>
+          <t>And—but inflation expectations did [MASK] move [MASK] down here in the United States.</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C689" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D689" t="n">
         <v>1</v>
@@ -14894,11 +14894,11 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>If we—if we [MASK] inflation data and [MASK] that, clearly, transitory influences are [MASK] down [MASK], I do not want to say that we would respond to that.</t>
+          <t>But [MASK]’s not easy to get a clear read on the implications of asset prices for [MASK] overall [MASK].</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C690" t="n">
         <v>2</v>
@@ -14915,11 +14915,11 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>And—but inflation expectations did [MASK] move [MASK] down here in the United States.</t>
+          <t>Well, [MASK]’re certainly [MASK] that we have been over-optimistic about out-year growth.</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C691" t="n">
         <v>1</v>
@@ -14936,11 +14936,11 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>But [MASK]’s not easy to get a clear read on the implications of asset prices for [MASK] overall [MASK].</t>
+          <t>If you lay the crosscurrents on top of that—concerns about global [MASK] [MASK] trade developments—you [MASK] the full picture.</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C692" t="n">
         <v>2</v>
@@ -14957,14 +14957,14 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>Well, [MASK]’re certainly [MASK] that we have been over-optimistic about out-year growth.</t>
+          <t>As [MASK] [MASK] step [MASK] enhancing the clarity of [MASK] communications, the Committee recently decided to begin publishing information about participants’ assessments of appropriate monetary policy—that is, the path of policy that each participant judges as most likely [MASK] foster mandate-consistent outcomes for [MASK] and inflation [MASK] the economy evolves [MASK] expected.</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C693" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D693" t="n">
         <v>1</v>
@@ -14978,14 +14978,14 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>If you lay the crosscurrents on top of that—concerns about global [MASK] [MASK] trade developments—you [MASK] the full picture.</t>
+          <t>The “[MASK] period” language is [MASK] on exactly those same points: “Extended period” is [MASK] on resource slack, [MASK] subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C694" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D694" t="n">
         <v>1</v>
@@ -14999,11 +14999,11 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>As [MASK] [MASK] step [MASK] enhancing the clarity of [MASK] communications, the Committee recently decided to begin publishing information about participants’ assessments of appropriate monetary policy—that is, the path of policy that each participant judges as most likely [MASK] foster mandate-consistent outcomes for [MASK] and inflation [MASK] the economy evolves [MASK] expected.</t>
+          <t>[MASK] those [MASK]’t—those, frankly, don’t carry significant implications in the long [MASK] for the—for inflation [MASK] for the American economy.</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C695" t="n">
         <v>2</v>
@@ -15020,11 +15020,11 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>The “[MASK] period” language is [MASK] on exactly those same points: “Extended period” is [MASK] on resource slack, [MASK] subdued inflation, and on stable inflation expectations.</t>
+          <t>[MASK] want to see lower unemployment.</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C696" t="n">
         <v>0</v>
@@ -15041,11 +15041,11 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>[MASK] those [MASK]’t—those, frankly, don’t carry significant implications in the long [MASK] for the—for inflation [MASK] for the American economy.</t>
+          <t>And I fully [MASK] it [MASK] return to solid growth and a solid labor [MASK] as well.</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C697" t="n">
         <v>2</v>
@@ -15062,11 +15062,11 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>[MASK] want to see lower unemployment.</t>
+          <t>[MASK], [MASK] inflation below 2 percent, I think it’s appropriate that [MASK] labor market be that tight.</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C698" t="n">
         <v>0</v>
@@ -15083,11 +15083,11 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>And I fully [MASK] it [MASK] return to solid growth and a solid labor [MASK] as well.</t>
+          <t>[MASK] I mentioned, once [MASK]—[MASK] you’[MASK], broadly speaking, in the range [MASK] neutral, I think it’[MASK] appropriate to be putting aside [MASK] estimates of [MASK] and be looking at what the incoming [MASK] are telling you about the outlook, updating your estimates of what neutral [MASK] be, of what the natural rate of unemployment might be, of the state [MASK] the economy, [MASK]—and letting that lead you to adjust your outlook and, therefore, your appropriate path for policy.</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C699" t="n">
         <v>2</v>
@@ -15104,14 +15104,14 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>[MASK], [MASK] inflation below 2 percent, I think it’s appropriate that [MASK] labor market be that tight.</t>
+          <t>But to [MASK] extent that continues to [MASK] the case, [MASK] should make it easier to restore price stability.</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C700" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D700" t="n">
         <v>1</v>
@@ -15125,11 +15125,11 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>[MASK] I mentioned, once [MASK]—[MASK] you’[MASK], broadly speaking, in the range [MASK] neutral, I think it’[MASK] appropriate to be putting aside [MASK] estimates of [MASK] and be looking at what the incoming [MASK] are telling you about the outlook, updating your estimates of what neutral [MASK] be, of what the natural rate of unemployment might be, of the state [MASK] the economy, [MASK]—and letting that lead you to adjust your outlook and, therefore, your appropriate path for policy.</t>
+          <t>We heard [MASK] today in the meeting [MASK] firms that might be government contractors [MASK] [MASK], you know, not sure about whether the contracts would still be in [MASK] come January and making employment decisions [MASK] on that.</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C701" t="n">
         <v>2</v>
@@ -15146,11 +15146,11 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>But to [MASK] extent that continues to [MASK] the case, [MASK] should make it easier to restore price stability.</t>
+          <t>Inflation [MASK] moved up in recent months, mainly [MASK] higher prices for some commodities and imported [MASK].</t>
         </is>
       </c>
       <c r="B702" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C702" t="n">
         <v>1</v>
@@ -15167,14 +15167,14 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>We heard [MASK] today in the meeting [MASK] firms that might be government contractors [MASK] [MASK], you know, not sure about whether the contracts would still be in [MASK] come January and making employment decisions [MASK] on that.</t>
+          <t>By contrast, raising rates too slowly [MASK] raise the risk that monetary policy would need to tighten abruptly down [MASK] [MASK], which could [MASK] the economic expansion.</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C703" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D703" t="n">
         <v>1</v>
@@ -15188,11 +15188,11 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>Inflation [MASK] moved up in recent months, mainly [MASK] higher prices for some commodities and imported [MASK].</t>
+          <t>But, I would say, overall, we’re trying to sustain the [MASK] [MASK] keep, you know, close to our statutory goals, which are [MASK] [MASK] and stable prices.</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C704" t="n">
         <v>1</v>
@@ -15209,14 +15209,14 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly [MASK] raise the risk that monetary policy would need to tighten abruptly down [MASK] [MASK], which could [MASK] the economic expansion.</t>
+          <t>But I do think that—and [MASK] do think also that unemployment [MASK] benefits will run out in September, [MASK] to [MASK] extent that’s a factor, which is not [MASK], it will no longer [MASK] a factor fairly soon.</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C705" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D705" t="n">
         <v>1</v>
@@ -15230,14 +15230,14 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>But, I would say, overall, we’re trying to sustain the [MASK] [MASK] keep, you know, close to our statutory goals, which are [MASK] [MASK] and stable prices.</t>
+          <t>We had a 10 percent [MASK] rate, and our congressional mandate is maximum employment and price [MASK].</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="C706" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D706" t="n">
         <v>1</v>
@@ -15251,11 +15251,11 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>But I do think that—and [MASK] do think also that unemployment [MASK] benefits will run out in September, [MASK] to [MASK] extent that’s a factor, which is not [MASK], it will no longer [MASK] a factor fairly soon.</t>
+          <t>That is a positive [MASK] growth.</t>
         </is>
       </c>
       <c r="B707" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="C707" t="n">
         <v>2</v>
@@ -15264,48 +15264,6 @@
         <v>1</v>
       </c>
       <c r="E707" t="inlineStr">
-        <is>
-          <t>masking</t>
-        </is>
-      </c>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr">
-        <is>
-          <t>We had a 10 percent [MASK] rate, and our congressional mandate is maximum employment and price [MASK].</t>
-        </is>
-      </c>
-      <c r="B708" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C708" t="n">
-        <v>0</v>
-      </c>
-      <c r="D708" t="n">
-        <v>1</v>
-      </c>
-      <c r="E708" t="inlineStr">
-        <is>
-          <t>masking</t>
-        </is>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr">
-        <is>
-          <t>That is a positive [MASK] growth.</t>
-        </is>
-      </c>
-      <c r="B709" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C709" t="n">
-        <v>2</v>
-      </c>
-      <c r="D709" t="n">
-        <v>1</v>
-      </c>
-      <c r="E709" t="inlineStr">
         <is>
           <t>masking</t>
         </is>

--- a/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-5768.xlsx
+++ b/dataset/test-and-training/augmented_data/augmented_train_data/lab-manual-pc-train-5768.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E707"/>
+  <dimension ref="A1:E709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7628,11 +7628,11 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>But it's really not a monetary policy.</t>
+          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C344" t="n">
         <v>2</v>
@@ -7649,7 +7649,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>That was before inflation was really under control, but it's very interesting to look at history.</t>
+          <t>But it's really not a monetary policy.</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -7670,14 +7670,14 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>And I would explain it is that inflation, which is too low, means that interest rates are lower.</t>
+          <t>That was before inflation was really under control, but it's very interesting to look at history.</t>
         </is>
       </c>
       <c r="B346" t="n">
         <v>2022</v>
       </c>
       <c r="C346" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D346" t="n">
         <v>1</v>
@@ -7691,14 +7691,14 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>As a further step towards improving the clarity of our communications, the Committee has recently decided to publish information on the participants . Assessments of the relevant monetary policy , i.e. the policy path that each participant considers most likely to promote mandate-compliant results for employment and inflation when the economy develops as expected.</t>
+          <t>And I would explain it is that inflation, which is too low, means that interest rates are lower.</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C347" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D347" t="n">
         <v>1</v>
@@ -7712,14 +7712,14 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Unemployment has thus increased much faster for minorities and others at the lower limit of the income spectrum.</t>
+          <t>As a further step towards improving the clarity of our communications, the Committee has recently decided to publish information on the participants . Assessments of the relevant monetary policy , i.e. the policy path that each participant considers most likely to promote mandate-compliant results for employment and inflation when the economy develops as expected.</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C348" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D348" t="n">
         <v>1</v>
@@ -7733,14 +7733,14 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>I am old enough to remember how very high inflation was.</t>
+          <t>Unemployment has thus increased much faster for minorities and others at the lower limit of the income spectrum.</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D349" t="n">
         <v>1</v>
@@ -7754,11 +7754,11 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>We therefore consider maximum employment as the maximum sustainable level of employment, which means that it is not so much that it overheats the economy.</t>
+          <t>I am old enough to remember how very high inflation was.</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C350" t="n">
         <v>2</v>
@@ -7775,11 +7775,11 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>We have not yet seen wage growth accelerate.</t>
+          <t>We therefore consider maximum employment as the maximum sustainable level of employment, which means that it is not so much that it overheats the economy.</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C351" t="n">
         <v>2</v>
@@ -7796,14 +7796,14 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
+          <t>We have not yet seen wage growth accelerate.</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D352" t="n">
         <v>1</v>
@@ -7817,11 +7817,11 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>An unexpectedly strong increase in wages or inflation could tell you that you are reaching these points.</t>
+          <t>So that the kind of thinking we're going to do, and again, we're looking – after all, we're not going to explain victory until we see a number of these, really see convincing evidence, convincing evidence that inflation is sinking.</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C353" t="n">
         <v>1</v>
@@ -7838,14 +7838,14 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>I assure you that my colleagues and I will continue to pursue monetary policy without regard for political considerations.</t>
+          <t>An unexpectedly strong increase in wages or inflation could tell you that you are reaching these points.</t>
         </is>
       </c>
       <c r="B354" t="n">
         <v>2018</v>
       </c>
       <c r="C354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D354" t="n">
         <v>1</v>
@@ -7859,14 +7859,14 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>The central trend in unemployment projections is slightly lower than in the March forecasts and now stands at 6.0 to 6.1 percent at the end of the year.</t>
+          <t>I assure you that my colleagues and I will continue to pursue monetary policy without regard for political considerations.</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D355" t="n">
         <v>1</v>
@@ -7880,14 +7880,14 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>And that means that the Federal Reserve cannot add monetary adjustment by lowering short-term interest rates, the usual approach.</t>
+          <t>The central trend in unemployment projections is slightly lower than in the March forecasts and now stands at 6.0 to 6.1 percent at the end of the year.</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D356" t="n">
         <v>1</v>
@@ -7901,7 +7901,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>We also do not have monetary policy to prove our independence.</t>
+          <t>And that means that the Federal Reserve cannot add monetary adjustment by lowering short-term interest rates, the usual approach.</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -7922,14 +7922,14 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>And that is – that's it again – that's going to be as short as possible on this episode and preventing unnecessary business bankruptcy, unnecessary household bankruptcy and unnecessary long-term stays of unemployment or support from them so that they can maintain their financial basis and their lives and return to work productively.</t>
+          <t>We also do not have monetary policy to prove our independence.</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C358" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D358" t="n">
         <v>1</v>
@@ -7943,11 +7943,11 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>In the U-6, unemployment has tripled from 7 to 21 percent.</t>
+          <t>And that is – that's it again – that's going to be as short as possible on this episode and preventing unnecessary business bankruptcy, unnecessary household bankruptcy and unnecessary long-term stays of unemployment or support from them so that they can maintain their financial basis and their lives and return to work productively.</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="C359" t="n">
         <v>0</v>
@@ -7964,14 +7964,14 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>With regard to inflation, a few things – your second question.</t>
+          <t>In the U-6, unemployment has tripled from 7 to 21 percent.</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D360" t="n">
         <v>1</v>
@@ -7985,14 +7985,14 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>I don't think we're looking at -- I understand what you're asking, but we're looking at -- our mandate is price inflation and maximum employment, and that's what we're looking at with setting interest rates.</t>
+          <t>With regard to inflation, a few things – your second question.</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C361" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D361" t="n">
         <v>1</v>
@@ -8006,14 +8006,14 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>So you will have different perspectives of committee participants on how fast growth will be, how quickly the labour market will heal, or how quickly – inflation will increase.</t>
+          <t>I don't think we're looking at -- I understand what you're asking, but we're looking at -- our mandate is price inflation and maximum employment, and that's what we're looking at with setting interest rates.</t>
         </is>
       </c>
       <c r="B362" t="n">
         <v>2019</v>
       </c>
       <c r="C362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D362" t="n">
         <v>1</v>
@@ -8027,14 +8027,14 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Recent lower inflation measurements have been driven significantly by the seemingly one-off price reductions of certain price categories such as wireless telephone services and prescription medicines.</t>
+          <t>So you will have different perspectives of committee participants on how fast growth will be, how quickly the labour market will heal, or how quickly – inflation will increase.</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D363" t="n">
         <v>1</v>
@@ -8048,14 +8048,14 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>After a sharp decline in March and April, employment increased sharply in May and June, as many people returned from temporary redundancies.</t>
+          <t>Recent lower inflation measurements have been driven significantly by the seemingly one-off price reductions of certain price categories such as wireless telephone services and prescription medicines.</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D364" t="n">
         <v>1</v>
@@ -8069,14 +8069,14 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>We believe that the economy will need a very accommodative monetary policy and the use of our instruments for a longer period of time.</t>
+          <t>After a sharp decline in March and April, employment increased sharply in May and June, as many people returned from temporary redundancies.</t>
         </is>
       </c>
       <c r="B365" t="n">
         <v>2019</v>
       </c>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -8090,11 +8090,11 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>And you know, we haven't touched – we just touched 2 percent core inflation to select a measure – just a few months, and then we fell back.</t>
+          <t>We believe that the economy will need a very accommodative monetary policy and the use of our instruments for a longer period of time.</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C366" t="n">
         <v>0</v>
@@ -8111,11 +8111,11 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>The shock experienced by the pandemic in its nature, size and level of unemployment and the shock of economic activity was unprecedented.</t>
+          <t>And you know, we haven't touched – we just touched 2 percent core inflation to select a measure – just a few months, and then we fell back.</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C367" t="n">
         <v>0</v>
@@ -8132,11 +8132,11 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>The Committee's forecasts and most external forecasters show growth this year and next, which is below its longer-term potential.</t>
+          <t>The shock experienced by the pandemic in its nature, size and level of unemployment and the shock of economic activity was unprecedented.</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C368" t="n">
         <v>0</v>
@@ -8153,14 +8153,14 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>So, and, and, you know, the shorter ones, tend to be based on, for example, gasoline prices.</t>
+          <t>The Committee's forecasts and most external forecasters show growth this year and next, which is below its longer-term potential.</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C369" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D369" t="n">
         <v>1</v>
@@ -8174,14 +8174,14 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>But you see growth in services, so you - this pattern around the world by Chair Powell .Press conference FINAL weak manufacturing, but growth in the far larger part of the service economy that has led to low unemployment, good job creation, rising wages, that is type of the two large parts of it that you see.</t>
+          <t>So, and, and, you know, the shorter ones, tend to be based on, for example, gasoline prices.</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D370" t="n">
         <v>1</v>
@@ -8195,14 +8195,14 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>We also said that we would increase rates not only in response to very low unemployment, in the absence of inflation.</t>
+          <t>But you see growth in services, so you - this pattern around the world by Chair Powell .Press conference FINAL weak manufacturing, but growth in the far larger part of the service economy that has led to low unemployment, good job creation, rising wages, that is type of the two large parts of it that you see.</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D371" t="n">
         <v>1</v>
@@ -8216,11 +8216,11 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>And, in particular, I personally believe that the weakening is at least partially temporary and that we will see greater growth in the future.</t>
+          <t>We also said that we would increase rates not only in response to very low unemployment, in the absence of inflation.</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C372" t="n">
         <v>0</v>
@@ -8237,14 +8237,14 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1 Chairman Yellen wanted to say that interest rate differentials worldwide lead to capital flows that have an impact on exchange rates. .</t>
+          <t>And, in particular, I personally believe that the weakening is at least partially temporary and that we will see greater growth in the future.</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C373" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D373" t="n">
         <v>1</v>
@@ -8258,11 +8258,11 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>If we do not see that the improvement projected in the base outlook is that June 18, 2014 would be compared to the truth and the pace of the time and pace of the rate hikes would be the chairman Yellen , press conference FINAL later and more gradual.</t>
+          <t>1 Chairman Yellen wanted to say that interest rate differentials worldwide lead to capital flows that have an impact on exchange rates. .</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C374" t="n">
         <v>2</v>
@@ -8279,11 +8279,11 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>So in the low 20s, and that, post May's employment report.</t>
+          <t>If we do not see that the improvement projected in the base outlook is that June 18, 2014 would be compared to the truth and the pace of the time and pace of the rate hikes would be the chairman Yellen , press conference FINAL later and more gradual.</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="C375" t="n">
         <v>2</v>
@@ -8300,14 +8300,14 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>And we were actually very concerned that growth was not enough to further reduce the unemployment rate.</t>
+          <t>So in the low 20s, and that, post May's employment report.</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D376" t="n">
         <v>1</v>
@@ -8321,11 +8321,11 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>I do not really believe that asset prices themselves pose a significant threat to financial stability, because the budgets are in good financial shape when they were.</t>
+          <t>And we were actually very concerned that growth was not enough to further reduce the unemployment rate.</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C377" t="n">
         <v>0</v>
@@ -8342,11 +8342,11 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>And I think that monetary policy in a broader sense also supports household spending and housing by keeping the labour market strong, increasing workers' incomes and maintaining consumer confidence at a high level where it is currently.</t>
+          <t>I do not really believe that asset prices themselves pose a significant threat to financial stability, because the budgets are in good financial shape when they were.</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="C378" t="n">
         <v>0</v>
@@ -8363,14 +8363,14 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>We have a much more resilient, stronger banking system, and we do not see any frightening increase in debt capital or credit growth at successive levels.1 So, you know, this is something that FOMC is paying attention to, but if you ask me, this is an important factor that monetary policy now, well, on the list of risks, it's not an important factor – it's not an important factor.</t>
+          <t>And I think that monetary policy in a broader sense also supports household spending and housing by keeping the labour market strong, increasing workers' incomes and maintaining consumer confidence at a high level where it is currently.</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="C379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D379" t="n">
         <v>1</v>
@@ -8384,14 +8384,14 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>So, you're right, you see -- I can't remember the number, but it could be in the 3s -- 3, 31⁄2 percent growth for next year.</t>
+          <t>We have a much more resilient, stronger banking system, and we do not see any frightening increase in debt capital or credit growth at successive levels.1 So, you know, this is something that FOMC is paying attention to, but if you ask me, this is an important factor that monetary policy now, well, on the list of risks, it's not an important factor – it's not an important factor.</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C380" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D380" t="n">
         <v>1</v>
@@ -8405,14 +8405,14 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>The American economy is very strong and well positioned to cope with a tighter monetary policy.</t>
+          <t>So, you're right, you see -- I can't remember the number, but it could be in the 3s -- 3, 31⁄2 percent growth for next year.</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D381" t="n">
         <v>1</v>
@@ -8426,14 +8426,14 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>And we have seen how significant capital outflows from these countries were under pressure on their exchange rates and concerns about their future performance.</t>
+          <t>The American economy is very strong and well positioned to cope with a tighter monetary policy.</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C382" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
         <v>1</v>
@@ -8447,14 +8447,14 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Inflationary pressures remain subdued and longer-term inflation expectations indicators are at the bottom of their historical range.</t>
+          <t>And we have seen how significant capital outflows from these countries were under pressure on their exchange rates and concerns about their future performance.</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D383" t="n">
         <v>1</v>
@@ -8468,11 +8468,11 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>The changes – the changes in the financial market you have described, in particular the increase in share prices, the increase in longer-term interest rates and the strengthening of the dollar – suggest that many market participants expect expansionary fiscal policies that would slightly increase interest rates in the United States compared to abroad and will result in a strengthening of the dollar.</t>
+          <t>Inflationary pressures remain subdued and longer-term inflation expectations indicators are at the bottom of their historical range.</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C384" t="n">
         <v>0</v>
@@ -8489,11 +8489,11 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Well, we - as committee - do not want inflation undercutting.</t>
+          <t>The changes – the changes in the financial market you have described, in particular the increase in share prices, the increase in longer-term interest rates and the strengthening of the dollar – suggest that many market participants expect expansionary fiscal policies that would slightly increase interest rates in the United States compared to abroad and will result in a strengthening of the dollar.</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C385" t="n">
         <v>0</v>
@@ -8510,14 +8510,14 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Finally, I would like to say that the Committee is anxious to explain its monetary policy decisions as clearly as possible and we will continue to look for ways to improve the clarity of our public communication.</t>
+          <t>Well, we - as committee - do not want inflation undercutting.</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C386" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D386" t="n">
         <v>1</v>
@@ -8531,11 +8531,11 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>I believe, however, that - and I also believe that unemployment insurance will expire in September - it will no longer be a factor as it is a factor which is not clear.</t>
+          <t>Finally, I would like to say that the Committee is anxious to explain its monetary policy decisions as clearly as possible and we will continue to look for ways to improve the clarity of our public communication.</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C387" t="n">
         <v>2</v>
@@ -8552,14 +8552,14 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Well, our policy approach does not deliberately involve an attempt to increase inflation.</t>
+          <t>. . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . . .</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D388" t="n">
         <v>1</v>
@@ -8573,14 +8573,14 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Last year we had 1.9 percent productivity, which is much higher.</t>
+          <t>I believe, however, that - and I also believe that unemployment insurance will expire in September - it will no longer be a factor as it is a factor which is not clear.</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C389" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D389" t="n">
         <v>1</v>
@@ -8594,14 +8594,14 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>However, I would like to stress that we are committed to raising inflation to 2%.</t>
+          <t>Well, our policy approach does not deliberately involve an attempt to increase inflation.</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C390" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D390" t="n">
         <v>1</v>
@@ -8615,14 +8615,14 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>But it is not easy to get a clear reading of the impact of asset prices on overall prospects.</t>
+          <t>Last year we had 1.9 percent productivity, which is much higher.</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C391" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D391" t="n">
         <v>1</v>
@@ -8636,11 +8636,11 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>I mean, some parts of South Carolina have developed quite strongly, but the part I come from – mostly agricultural, it has a little bit of production – has a very high unemployment rate, a high foreclosure rate, and people have a hard time there.</t>
+          <t>However, I would like to stress that we are committed to raising inflation to 2%.</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C392" t="n">
         <v>0</v>
@@ -8657,14 +8657,14 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>At the time of our FOMC meeting in January, the prospects for sustained economic growth remained favourable, and we felt that monetary policy was well positioned to support these prospects.</t>
+          <t>But it is not easy to get a clear reading of the impact of asset prices on overall prospects.</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C393" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D393" t="n">
         <v>1</v>
@@ -8678,14 +8678,14 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>What I am telling you is that the attitude of monetary policy that we have today, we believe, is appropriate.</t>
+          <t>I mean, some parts of South Carolina have developed quite strongly, but the part I come from – mostly agricultural, it has a little bit of production – has a very high unemployment rate, a high foreclosure rate, and people have a hard time there.</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D394" t="n">
         <v>1</v>
@@ -8699,14 +8699,14 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>The Committee therefore estimates that the unemployment rate is usually 5.0 to 5.2.</t>
+          <t>At the time of our FOMC meeting in January, the prospects for sustained economic growth remained favourable, and we felt that monetary policy was well positioned to support these prospects.</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C395" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D395" t="n">
         <v>1</v>
@@ -8720,14 +8720,14 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>We have not focused on whether we are fulfilling the downforce test, because we are not now fulfilling the downforce test because we are not at maximum employment.</t>
+          <t>What I am telling you is that the attitude of monetary policy that we have today, we believe, is appropriate.</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C396" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D396" t="n">
         <v>1</v>
@@ -8741,14 +8741,14 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Now, with inflation below 2 percent, I think it's appropriate that the labour market be so tight.</t>
+          <t>The Committee therefore estimates that the unemployment rate is usually 5.0 to 5.2.</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="C397" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D397" t="n">
         <v>1</v>
@@ -8762,11 +8762,11 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>I can only say in qualitative terms that the Committee will continue to examine the prospects, will try to assess whether unemployment is sufficiently advanced to our objectives and, in particular, whether the recovery will continue.</t>
+          <t>We have not focused on whether we are fulfilling the downforce test, because we are not now fulfilling the downforce test because we are not at maximum employment.</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C398" t="n">
         <v>0</v>
@@ -8783,14 +8783,14 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
+          <t>Now, with inflation below 2 percent, I think it's appropriate that the labour market be so tight.</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C399" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D399" t="n">
         <v>1</v>
@@ -8804,14 +8804,14 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
+          <t>I can only say in qualitative terms that the Committee will continue to examine the prospects, will try to assess whether unemployment is sufficiently advanced to our objectives and, in particular, whether the recovery will continue.</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C400" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D400" t="n">
         <v>1</v>
@@ -8825,14 +8825,14 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>And perhaps they are reducing their level of natural unemployment, which was the trend.</t>
+          <t>This transition could help to reduce inflation, because people would probably spend a little less on goods, while spending more on travel and all kinds of travel services and things like that.</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D401" t="n">
         <v>1</v>
@@ -8846,14 +8846,14 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Well, we've been expecting a long time, as most analysts have, to see some slowdown in Chinese growth over time, how they're balancing their economy.</t>
+          <t>And when I went into detail in Jackson Hole and didn't want to repeat all of this there, there are other ways we see underutilization – high levels that are very marginal of part-time employment for economic – or involuntary part-time employment, perhaps still a deficit of labour force participation as a result of cyclical factors.</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C402" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D402" t="n">
         <v>1</v>
@@ -8867,14 +8867,14 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>They say we're going to try to find inflation, which is over 2% for some time.</t>
+          <t>And perhaps they are reducing their level of natural unemployment, which was the trend.</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C403" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D403" t="n">
         <v>1</v>
@@ -8888,11 +8888,11 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>We want less unemployment.</t>
+          <t>Well, we've been expecting a long time, as most analysts have, to see some slowdown in Chinese growth over time, how they're balancing their economy.</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C404" t="n">
         <v>0</v>
@@ -8909,14 +8909,14 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>I have pointed out that I have concerns about the possibilities for monetary policy.</t>
+          <t>They say we're going to try to find inflation, which is over 2% for some time.</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="C405" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D405" t="n">
         <v>1</v>
@@ -8930,14 +8930,14 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>And those who frankly have no significant impact on inflation or the American economy have no long-term impact.</t>
+          <t>We want less unemployment.</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C406" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D406" t="n">
         <v>1</v>
@@ -8951,14 +8951,14 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Inflation has increased in recent months, mainly due to higher prices for some raw materials and imported goods.</t>
+          <t>I have pointed out that I have concerns about the possibilities for monetary policy.</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C407" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D407" t="n">
         <v>1</v>
@@ -8972,11 +8972,11 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>In the coming months, as the previous declines fall from the calculation, inflation should approach closer to 2 percent and stabilise around this level in the medium term.</t>
+          <t>And those who frankly have no significant impact on inflation or the American economy have no long-term impact.</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C408" t="n">
         <v>2</v>
@@ -8993,14 +8993,14 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>It was the year of synchronised global growth.</t>
+          <t>Inflation has increased in recent months, mainly due to higher prices for some raw materials and imported goods.</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>2021</v>
+        <v>2012</v>
       </c>
       <c r="C409" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D409" t="n">
         <v>1</v>
@@ -9014,11 +9014,11 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>It would consist of inflation plus — plus productivity growth.</t>
+          <t>In the coming months, as the previous declines fall from the calculation, inflation should approach closer to 2 percent and stabilise around this level in the medium term.</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C410" t="n">
         <v>2</v>
@@ -9035,14 +9035,14 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>If you look at the core inflation of PCE, which is a good measure of where inflation is now running, if you look at it on an annualised basis that has been up to 3, 6 and 12 months ago, then you will see that inflation is 4.8 percent, 4.5 percent and 4.8 percent.</t>
+          <t>It was the year of synchronised global growth.</t>
         </is>
       </c>
       <c r="B411" t="n">
         <v>2021</v>
       </c>
       <c r="C411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D411" t="n">
         <v>1</v>
@@ -9056,11 +9056,11 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>If you come to – in the forecast – you can adapt all that, you know, to the supply and demand of the economy.</t>
+          <t>It would consist of inflation plus — plus productivity growth.</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C412" t="n">
         <v>2</v>
@@ -9077,14 +9077,14 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>And some of the answer to that can be price.</t>
+          <t>If you look at the core inflation of PCE, which is a good measure of where inflation is now running, if you look at it on an annualised basis that has been up to 3, 6 and 12 months ago, then you will see that inflation is 4.8 percent, 4.5 percent and 4.8 percent.</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C413" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D413" t="n">
         <v>1</v>
@@ -9098,14 +9098,14 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>To do this, we must have price stability, and we must return to price stability so that we can have a labour market where people's wages are not eaten up by inflation and where we can have a long expansion.</t>
+          <t>If you come to – in the forecast – you can adapt all that, you know, to the supply and demand of the economy.</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D414" t="n">
         <v>1</v>
@@ -9119,11 +9119,11 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>And that's because of this misalignment between supply and demand.</t>
+          <t>And some of the answer to that can be price.</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C415" t="n">
         <v>2</v>
@@ -9140,14 +9140,14 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>And our plan, as we do, is that we believe that we can gradually reduce these products, and we believe that we can also gradually reduce Repo, because we are reaching a sufficient level, as we are now buying more from the underlying reserves from the invoices than from Repo.</t>
+          <t>To do this, we must have price stability, and we must return to price stability so that we can have a labour market where people's wages are not eaten up by inflation and where we can have a long expansion.</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="C416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D416" t="n">
         <v>1</v>
@@ -9161,11 +9161,11 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>If we - if we analyse inflation data and find that we clearly restrain temporary influences - then I do not want to say that we would respond to it.</t>
+          <t>And that's because of this misalignment between supply and demand.</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C417" t="n">
         <v>2</v>
@@ -9182,14 +9182,14 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Despite such slow growth, disappointing productivity growth, we have a labour market that generated an average of around 230,000 jobs per month last year and has generated around 180,000 jobs per month this year.</t>
+          <t>And our plan, as we do, is that we believe that we can gradually reduce these products, and we believe that we can also gradually reduce Repo, because we are reaching a sufficient level, as we are now buying more from the underlying reserves from the invoices than from Repo.</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D418" t="n">
         <v>1</v>
@@ -9203,7 +9203,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>The sooner we get the virus under control, the sooner people can regain this trust and regain their economic activity.</t>
+          <t>If we - if we analyse inflation data and find that we clearly restrain temporary influences - then I do not want to say that we would respond to it.</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -9224,14 +9224,14 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Now, members of the committee have different views on why this is likely to be true, that the money rate – when the labour market is normalized and inflation is back to our goal – may have some different views on why it is likely that interest rates will be slightly lower than they would in the longer term.</t>
+          <t>Despite such slow growth, disappointing productivity growth, we have a labour market that generated an average of around 230,000 jobs per month last year and has generated around 180,000 jobs per month this year.</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="C420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D420" t="n">
         <v>1</v>
@@ -9245,14 +9245,14 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>But first, in terms of inflation expectations, it is true that breakevens have fallen from inflation-adjusted inflation index bonds.</t>
+          <t>The sooner we get the virus under control, the sooner people can regain this trust and regain their economic activity.</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D421" t="n">
         <v>1</v>
@@ -9266,14 +9266,14 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>We heard anecdotes today in the meeting about companies that may be government companies that, you know, were not sure if the contracts would still be in force, coming in January and making employment decisions on this basis.</t>
+          <t>Now, members of the committee have different views on why this is likely to be true, that the money rate – when the labour market is normalized and inflation is back to our goal – may have some different views on why it is likely that interest rates will be slightly lower than they would in the longer term.</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D422" t="n">
         <v>1</v>
@@ -9287,14 +9287,14 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>When we return to monetary policy, we see that today's political decision has been very focused.</t>
+          <t>But first, in terms of inflation expectations, it is true that breakevens have fallen from inflation-adjusted inflation index bonds.</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D423" t="n">
         <v>1</v>
@@ -9308,14 +9308,14 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>In any case, it is our job to ensure price stability, and I think that price stability can be imagined as an advantage that will bring great benefits to society over a long period of time.</t>
+          <t>We heard anecdotes today in the meeting about companies that may be government companies that, you know, were not sure if the contracts would still be in force, coming in January and making employment decisions on this basis.</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D424" t="n">
         <v>1</v>
@@ -9329,14 +9329,14 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>We are being accused by Congress of trying to pursue maximum employment, and we have taken this very seriously.</t>
+          <t>When we return to monetary policy, we see that today's political decision has been very focused.</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C425" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D425" t="n">
         <v>1</v>
@@ -9350,14 +9350,14 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>The same applies to economic activity.</t>
+          <t>In any case, it is our job to ensure price stability, and I think that price stability can be imagined as an advantage that will bring great benefits to society over a long period of time.</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D426" t="n">
         <v>1</v>
@@ -9371,14 +9371,14 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>As always, each participant's projections depend on his own view of the relevant monetary policy.</t>
+          <t>We are being accused by Congress of trying to pursue maximum employment, and we have taken this very seriously.</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D427" t="n">
         <v>1</v>
@@ -9392,14 +9392,14 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>As highlighted by the Bureau of Labor Statistics, this figure will probably underestimate the extent of unemployment; the unusually large number of workers registered as employed but not in their jobs would increase the unemployment rate by about 3 percentage points.</t>
+          <t>The same applies to economic activity.</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C428" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D428" t="n">
         <v>1</v>
@@ -9413,14 +9413,14 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>In fact, it is already – I think it is already understood – that there is more – although we are at 31⁄2 percent unemployment, there is actually more slackening out there, in a way.</t>
+          <t>As always, each participant's projections depend on his own view of the relevant monetary policy.</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C429" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D429" t="n">
         <v>1</v>
@@ -9434,14 +9434,14 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>And I fully expect it to return to solid growth and a solid labour market.</t>
+          <t>As highlighted by the Bureau of Labor Statistics, this figure will probably underestimate the extent of unemployment; the unusually large number of workers registered as employed but not in their jobs would increase the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C430" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D430" t="n">
         <v>1</v>
@@ -9455,14 +9455,14 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Monetary policy, maximum employment, stable prices – that is less obvious to me.</t>
+          <t>In fact, it is already – I think it is already understood – that there is more – although we are at 31⁄2 percent unemployment, there is actually more slackening out there, in a way.</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C431" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D431" t="n">
         <v>1</v>
@@ -9476,14 +9476,14 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>The US economy is in a good place, and we will continue to use our monetary policy instruments to keep it there.</t>
+          <t>And I fully expect it to return to solid growth and a solid labour market.</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D432" t="n">
         <v>1</v>
@@ -9497,14 +9497,14 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>By the way, we are not at maximum employment, as I have already mentioned.</t>
+          <t>Monetary policy, maximum employment, stable prices – that is less obvious to me.</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C433" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D433" t="n">
         <v>1</v>
@@ -9518,14 +9518,14 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>The unemployment rate in February was 3.5 percent and has been at or close to a low point in the half century for almost two years.</t>
+          <t>The US economy is in a good place, and we will continue to use our monetary policy instruments to keep it there.</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="C434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D434" t="n">
         <v>1</v>
@@ -9539,14 +9539,14 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>As you know, the ultimate focus we have is on the real economy: maximum employment and price stability.</t>
+          <t>By the way, we are not at maximum employment, as I have already mentioned.</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C435" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D435" t="n">
         <v>1</v>
@@ -9560,14 +9560,14 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>And that's a statement about productivity growth that was pretty disappointing.</t>
+          <t>The unemployment rate in February was 3.5 percent and has been at or close to a low point in the half century for almost two years.</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C436" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D436" t="n">
         <v>1</v>
@@ -9581,14 +9581,14 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>The stimulus of aggregate demand is one thing, but where part of the economy that resists it is there, a fiscal policy is also needed.</t>
+          <t>As you know, the ultimate focus we have is on the real economy: maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C437" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D437" t="n">
         <v>1</v>
@@ -9602,14 +9602,14 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>So, as I said, we're going to look at all these things: activity, labour market, inflation.</t>
+          <t>And that's a statement about productivity growth that was pretty disappointing.</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C438" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D438" t="n">
         <v>1</v>
@@ -9623,14 +9623,14 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>And – but inflation expectations have not developed strongly here in the United States.</t>
+          <t>The stimulus of aggregate demand is one thing, but where part of the economy that resists it is there, a fiscal policy is also needed.</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D439" t="n">
         <v>1</v>
@@ -9644,7 +9644,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>You can focus up to 20 if you wanted, easily, but the labour force participation, the unemployment rate, different age groups of - you know, prime-age labor participation, in particular, gets a lot of focus that JOLTS data get a lot.</t>
+          <t>So, as I said, we're going to look at all these things: activity, labour market, inflation.</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -9665,14 +9665,14 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Inflation has remained below our longer term target, partly due to lower energy prices.</t>
+          <t>And – but inflation expectations have not developed strongly here in the United States.</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="C441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D441" t="n">
         <v>1</v>
@@ -9686,11 +9686,11 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>We also see the different measures of negligence on the labour market for different assessments of what is maximum employment.</t>
+          <t>You can focus up to 20 if you wanted, easily, but the labour force participation, the unemployment rate, different age groups of - you know, prime-age labor participation, in particular, gets a lot of focus that JOLTS data get a lot.</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C442" t="n">
         <v>2</v>
@@ -9707,14 +9707,14 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Inflation is actually under control and is beginning to decline.</t>
+          <t>Inflation has remained below our longer term target, partly due to lower energy prices.</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="C443" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D443" t="n">
         <v>1</v>
@@ -9728,14 +9728,14 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>The unemployment rate dropped in May and, 2020 June, but at 11.1 percent, remains well above its level before the outbreak and greater than the chairman Powell .</t>
+          <t>We also see the different measures of negligence on the labour market for different assessments of what is maximum employment.</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C444" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D444" t="n">
         <v>1</v>
@@ -9749,14 +9749,14 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>So there have been effects from lower interest rates, but I think, by and large, the indirect effects are.</t>
+          <t>Inflation is actually under control and is beginning to decline.</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D445" t="n">
         <v>1</v>
@@ -9770,14 +9770,14 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>They had low unemployment, many social problems.</t>
+          <t>The unemployment rate dropped in May and, 2020 June, but at 11.1 percent, remains well above its level before the outbreak and greater than the chairman Powell .</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C446" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D446" t="n">
         <v>1</v>
@@ -9791,14 +9791,14 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>And then we will just have that in the background – and interest rates will be the active instrument of monetary policy again.</t>
+          <t>So there have been effects from lower interest rates, but I think, by and large, the indirect effects are.</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C447" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D447" t="n">
         <v>1</v>
@@ -9812,14 +9812,14 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>But, as it continues to be, it should be easier to restore price stability.</t>
+          <t>They had low unemployment, many social problems.</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C448" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D448" t="n">
         <v>1</v>
@@ -9833,7 +9833,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>And what it is, it is an expression of thinking about individual committee members about an appropriate monetary policy and the way of the economy.</t>
+          <t>And then we will just have that in the background – and interest rates will be the active instrument of monetary policy again.</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -9854,14 +9854,14 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Well, what happens is that the relationship between resource use or unemployment and inflation has become weaker and weaker over the years.</t>
+          <t>But, as it continues to be, it should be easier to restore price stability.</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>2020</v>
+        <v>2014</v>
       </c>
       <c r="C450" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D450" t="n">
         <v>1</v>
@@ -9875,14 +9875,14 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>And as I have already mentioned, the fall in unemployment last month was more than 100 percent, due to the decline in labour force participation.</t>
+          <t>And what it is, it is an expression of thinking about individual committee members about an appropriate monetary policy and the way of the economy.</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C451" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D451" t="n">
         <v>1</v>
@@ -9896,14 +9896,14 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Wage inflation has increased to 2 percent.</t>
+          <t>Well, what happens is that the relationship between resource use or unemployment and inflation has become weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D452" t="n">
         <v>1</v>
@@ -9917,14 +9917,14 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>The slow rise in interest rates, on the other hand, would increase the risk of monetary policy starting abruptly, which could jeopardise economic expansion.</t>
+          <t>And as I have already mentioned, the fall in unemployment last month was more than 100 percent, due to the decline in labour force participation.</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C453" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D453" t="n">
         <v>1</v>
@@ -9938,11 +9938,11 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>We continue to discuss whether the unemployment rate itself is an appropriate measure of how much underutilisation of labour resources actually exists.</t>
+          <t>Wage inflation has increased to 2 percent.</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C454" t="n">
         <v>2</v>
@@ -9959,14 +9959,14 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>For many, many years we have been far from maximum employment and stable prices, and the need for accommodative policies was clear.</t>
+          <t>The slow rise in interest rates, on the other hand, would increase the risk of monetary policy starting abruptly, which could jeopardise economic expansion.</t>
         </is>
       </c>
       <c r="B455" t="n">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="C455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D455" t="n">
         <v>1</v>
@@ -9980,14 +9980,14 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Inflation has continued to fall below our longer-term target, largely due to the lower energy prices I have mentioned.</t>
+          <t>We continue to discuss whether the unemployment rate itself is an appropriate measure of how much underutilisation of labour resources actually exists.</t>
         </is>
       </c>
       <c r="B456" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C456" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D456" t="n">
         <v>1</v>
@@ -10001,11 +10001,11 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>We had an unemployment rate of 10 percent, and our Congress mandate is maximum employment and price stability.</t>
+          <t>For many, many years we have been far from maximum employment and stable prices, and the need for accommodative policies was clear.</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C457" t="n">
         <v>0</v>
@@ -10022,11 +10022,11 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>So, you know, I can't -- all I can tell you is that we're going to look at a weak global growth.</t>
+          <t>Inflation has continued to fall below our longer-term target, largely due to the lower energy prices I have mentioned.</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C458" t="n">
         <v>0</v>
@@ -10043,14 +10043,14 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>It was about, you know, strong monetary policy and fiscal incentives to an economy that was rapidly recovering and where there were these supply-side barriers that effectively led to a so-called vertical supply curve in certain parts of the economy.</t>
+          <t>We had an unemployment rate of 10 percent, and our Congress mandate is maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C459" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D459" t="n">
         <v>1</v>
@@ -10064,11 +10064,11 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>As unemployment is still rising and inflation is below the longer term objective of the Committee, the Committee continues its extremely accommodating policy.</t>
+          <t>So, you know, I can't -- all I can tell you is that we're going to look at a weak global growth.</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C460" t="n">
         <v>0</v>
@@ -10085,14 +10085,14 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>So this time you saw a shift in most participants, assessing the appropriate way for policy, and, as I tried to show, I think that largely reflects a somewhat slower projected way for global growth – for growth in the world economy outside the United States – and for a certain tightening of credit conditions in the form of an increase in spreads.</t>
+          <t>It was about, you know, strong monetary policy and fiscal incentives to an economy that was rapidly recovering and where there were these supply-side barriers that effectively led to a so-called vertical supply curve in certain parts of the economy.</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D461" t="n">
         <v>1</v>
@@ -10106,14 +10106,14 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>And we learn to engage in economic activity.</t>
+          <t>As unemployment is still rising and inflation is below the longer term objective of the Committee, the Committee continues its extremely accommodating policy.</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C462" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D462" t="n">
         <v>1</v>
@@ -10127,11 +10127,11 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>And inflation is moving – I think we are going towards our 2 percent target.</t>
+          <t>So this time you saw a shift in most participants, assessing the appropriate way for policy, and, as I tried to show, I think that largely reflects a somewhat slower projected way for global growth – for growth in the world economy outside the United States – and for a certain tightening of credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C463" t="n">
         <v>0</v>
@@ -10148,14 +10148,14 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>The unemployment rate, however, remains high at 7.7 percent.</t>
+          <t>And we learn to engage in economic activity.</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="C464" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D464" t="n">
         <v>1</v>
@@ -10169,14 +10169,14 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Monetary policy is a forward-looking exercise, and I will do it – I will just stick to it.</t>
+          <t>And inflation is moving – I think we are going towards our 2 percent target.</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C465" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D465" t="n">
         <v>1</v>
@@ -10190,14 +10190,14 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>There is much more demand for risk sharing, for liquidity services, and so on.</t>
+          <t>The unemployment rate, however, remains high at 7.7 percent.</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C466" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D466" t="n">
         <v>1</v>
@@ -10211,11 +10211,11 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>For example, we have used some of our work to address interest rate risk and interest rate sensitivity, and you know that banks can also achieve a significant increase in long-term interest rates for a number of reasons, including higher interest rates increasing their franchise value because they increase their net interest rate margin over time.</t>
+          <t>Monetary policy is a forward-looking exercise, and I will do it – I will just stick to it.</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C467" t="n">
         <v>2</v>
@@ -10232,14 +10232,14 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Well, you are certainly right that we have been overoptimistic about growth during the year.</t>
+          <t>There is much more demand for risk sharing, for liquidity services, and so on.</t>
         </is>
       </c>
       <c r="B468" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C468" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D468" t="n">
         <v>1</v>
@@ -10253,11 +10253,11 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>It will contain all the data relevant to our dual mandate of stable prices and maximum employment.</t>
+          <t>For example, we have used some of our work to address interest rate risk and interest rate sensitivity, and you know that banks can also achieve a significant increase in long-term interest rates for a number of reasons, including higher interest rates increasing their franchise value because they increase their net interest rate margin over time.</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C469" t="n">
         <v>2</v>
@@ -10274,14 +10274,14 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>So I have no sense – the committee is not trying to judge what is the right level of stock prices.</t>
+          <t>Well, you are certainly right that we have been overoptimistic about growth during the year.</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C470" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D470" t="n">
         <v>1</v>
@@ -10295,14 +10295,14 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>So with this Corona virus that arrives, we have judged that the – the net effects of it – will bring inflation down a little further.</t>
+          <t>It will contain all the data relevant to our dual mandate of stable prices and maximum employment.</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C471" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D471" t="n">
         <v>1</v>
@@ -10316,14 +10316,14 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the current economy is – is the worst – the worst it has been in the post-war period.</t>
+          <t>So I have no sense – the committee is not trying to judge what is the right level of stock prices.</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C472" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D472" t="n">
         <v>1</v>
@@ -10337,14 +10337,14 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>But you have not been under the merely negative scenario that has been followed by an inflation shock followed by a rapid rise in short-term interest rates.</t>
+          <t>So with this Corona virus that arrives, we have judged that the – the net effects of it – will bring inflation down a little further.</t>
         </is>
       </c>
       <c r="B473" t="n">
         <v>2014</v>
       </c>
       <c r="C473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D473" t="n">
         <v>1</v>
@@ -10358,11 +10358,11 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>And we want inflation to be moderately above 2 percent.</t>
+          <t>Long-term unemployment in the current economy is – is the worst – the worst it has been in the post-war period.</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C474" t="n">
         <v>0</v>
@@ -10379,14 +10379,14 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Many members of the committee, the participants, have said that they believe that policy should be based on the actual development of economic activity and inflation, which tends to be variable over time, and therefore I say that I will assume that it will depend on data.</t>
+          <t>But you have not been under the merely negative scenario that has been followed by an inflation shock followed by a rapid rise in short-term interest rates.</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C475" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D475" t="n">
         <v>1</v>
@@ -10400,14 +10400,14 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>But, certainly, we enve had a lot of years in which interest rates were low.</t>
+          <t>And we want inflation to be moderately above 2 percent.</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C476" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D476" t="n">
         <v>1</v>
@@ -10421,14 +10421,14 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>These measures, together with our strong interest rate guidelines and our balance sheet, will ensure that monetary policy continues to support the economy until the full recovery.</t>
+          <t>Many members of the committee, the participants, have said that they believe that policy should be based on the actual development of economic activity and inflation, which tends to be variable over time, and therefore I say that I will assume that it will depend on data.</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C477" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D477" t="n">
         <v>1</v>
@@ -10442,14 +10442,14 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>The problem with the current situation is that if you have a long-term supply shock, you can actually start to undermine or work on it – decoding inflation expectations.</t>
+          <t>But, certainly, we enve had a lot of years in which interest rates were low.</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="C478" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D478" t="n">
         <v>1</v>
@@ -10463,11 +10463,11 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>The Federal Reserves will strengthen the orientation for their political intentions and their substantial and still growing stocks of longer-term securities to ensure that monetary policy remains highly accommodating, in line with the pursuit of their mandates for maximum employment and price stability.</t>
+          <t>These measures, together with our strong interest rate guidelines and our balance sheet, will ensure that monetary policy continues to support the economy until the full recovery.</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C479" t="n">
         <v>0</v>
@@ -10484,14 +10484,14 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>And part of it is just the effect of lower interest rates.</t>
+          <t>The problem with the current situation is that if you have a long-term supply shock, you can actually start to undermine or work on it – decoding inflation expectations.</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D480" t="n">
         <v>1</v>
@@ -10505,14 +10505,14 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>And when asset prices went up again, it will probably be a swing around there, a positive contribution.</t>
+          <t>The Federal Reserves will strengthen the orientation for their political intentions and their substantial and still growing stocks of longer-term securities to ensure that monetary policy remains highly accommodating, in line with the pursuit of their mandates for maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B481" t="n">
         <v>2020</v>
       </c>
       <c r="C481" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D481" t="n">
         <v>1</v>
@@ -10526,14 +10526,14 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>We understand that the pace of inflation is constantly evolving over time, but it does not change quickly.</t>
+          <t>And part of it is just the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C482" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D482" t="n">
         <v>1</v>
@@ -10547,11 +10547,11 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>So you're basically talking about the inflation target.</t>
+          <t>And when asset prices went up again, it will probably be a swing around there, a positive contribution.</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C483" t="n">
         <v>2</v>
@@ -10568,11 +10568,11 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>So, in terms of financial markets and monetary policy, as we say in our statement of each cycle, we take into account the financial conditions, because the financial conditions – the broader financial conditions – influence the economy, and they are one of the many things we take into account.</t>
+          <t>We understand that the pace of inflation is constantly evolving over time, but it does not change quickly.</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C484" t="n">
         <v>2</v>
@@ -10589,14 +10589,14 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to fall so that inflation will fall.</t>
+          <t>So you're basically talking about the inflation target.</t>
         </is>
       </c>
       <c r="B485" t="n">
         <v>2019</v>
       </c>
       <c r="C485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D485" t="n">
         <v>1</v>
@@ -10610,14 +10610,14 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>So if you get credit, along with the low prices of houses, you can buy a lot more house than it might be a few years ago.</t>
+          <t>So, in terms of financial markets and monetary policy, as we say in our statement of each cycle, we take into account the financial conditions, because the financial conditions – the broader financial conditions – influence the economy, and they are one of the many things we take into account.</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C486" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D486" t="n">
         <v>1</v>
@@ -10631,14 +10631,14 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>But – so I would simply say that we – there are many things that, as you know, serve to set the prices of assets.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to fall so that inflation will fall.</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D487" t="n">
         <v>1</v>
@@ -10652,14 +10652,14 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>But here too, our basic forecast is one that, as Mr Hilsenrath has already said, is a moderately optimistic forecast in which growth will increase as we go through this period of budgetary restraint; where unemployment is continuing to decline gradually, as it has been since last September – and we have made progress since last September; and inflation is slowly rising to 2 percent.</t>
+          <t>So if you get credit, along with the low prices of houses, you can buy a lot more house than it might be a few years ago.</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D488" t="n">
         <v>1</v>
@@ -10673,11 +10673,11 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>And the downward correction of the longer-term normal unemployment rate indicates in a way that the participants are now dwindling in the economy more than before.</t>
+          <t>But – so I would simply say that we – there are many things that, as you know, serve to set the prices of assets.</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="C489" t="n">
         <v>2</v>
@@ -10694,14 +10694,14 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>During this period of reopening, we will probably see some upward pressure on prices, and I will discuss why.</t>
+          <t>But here too, our basic forecast is one that, as Mr Hilsenrath has already said, is a moderately optimistic forecast in which growth will increase as we go through this period of budgetary restraint; where unemployment is continuing to decline gradually, as it has been since last September – and we have made progress since last September; and inflation is slowly rising to 2 percent.</t>
         </is>
       </c>
       <c r="B490" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D490" t="n">
         <v>1</v>
@@ -10715,11 +10715,11 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>And of course, all households in the economy benefit from a strong economy, including savers, from a better labour market and a safer economy.</t>
+          <t>And the downward correction of the longer-term normal unemployment rate indicates in a way that the participants are now dwindling in the economy more than before.</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C491" t="n">
         <v>2</v>
@@ -10736,14 +10736,14 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>As I have already mentioned, monetary policy is working with delays, and so the policies we are pursuing will gradually – only gradually – reduce inflation to 2 percent.</t>
+          <t>During this period of reopening, we will probably see some upward pressure on prices, and I will discuss why.</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C492" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D492" t="n">
         <v>1</v>
@@ -10757,11 +10757,11 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>As I have already mentioned, once you put aside the individual estimates of them, and look at what the incoming data tells you about the prospects, update your estimates of what might be neutral, what could be natural unemployment, about the state of the economy, and allow you to adjust your prospects and thus your appropriate way of doing politics.</t>
+          <t>And of course, all households in the economy benefit from a strong economy, including savers, from a better labour market and a safer economy.</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="C493" t="n">
         <v>2</v>
@@ -10778,14 +10778,14 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Our current framework for implementing monetary policy works very well.</t>
+          <t>As I have already mentioned, monetary policy is working with delays, and so the policies we are pursuing will gradually – only gradually – reduce inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C494" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D494" t="n">
         <v>1</v>
@@ -10799,14 +10799,14 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>The unemployment rate has increased by 0.3 percentage points since March and the new insurance rights have increased slightly.</t>
+          <t>As I have already mentioned, once you put aside the individual estimates of them, and look at what the incoming data tells you about the prospects, update your estimates of what might be neutral, what could be natural unemployment, about the state of the economy, and allow you to adjust your prospects and thus your appropriate way of doing politics.</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C495" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D495" t="n">
         <v>1</v>
@@ -10820,14 +10820,14 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>You know, this is – that is the economy with almost full employment or in the area – in the neighbourhood of full employment.</t>
+          <t>Our current framework for implementing monetary policy works very well.</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C496" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D496" t="n">
         <v>1</v>
@@ -10841,14 +10841,14 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>The Committee will also pay great attention to inflation expectations to ensure that these expectations remain well-established.</t>
+          <t>The unemployment rate has increased by 0.3 percentage points since March and the new insurance rights have increased slightly.</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D497" t="n">
         <v>1</v>
@@ -10862,14 +10862,14 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Wage growth is not – there are many factors that influence it – it is in no way definitive when it determines our policies, but it has an impact on inflation prospects.</t>
+          <t>You know, this is – that is the economy with almost full employment or in the area – in the neighbourhood of full employment.</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D498" t="n">
         <v>1</v>
@@ -10883,14 +10883,14 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
+          <t>The Committee will also pay great attention to inflation expectations to ensure that these expectations remain well-established.</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C499" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D499" t="n">
         <v>1</v>
@@ -10904,11 +10904,11 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>And as I have already mentioned, I think that the estimates of – by members of the committee since perhaps 2012, as we have seen, have fallen by a full percentage point – while unemployment has fallen and inflation has not really responded.</t>
+          <t>Wage growth is not – there are many factors that influence it – it is in no way definitive when it determines our policies, but it has an impact on inflation prospects.</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C500" t="n">
         <v>2</v>
@@ -10925,14 +10925,14 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Against this background, the Federal Committee on the Open Market today raised its key rate by 3⁄4 percentage points and expects that the current increases in this rate will be appropriate.</t>
+          <t>And we have talked about the impact on asset prices, but we continue to analyse the impact of changes in interest rates, for example on decisions such as investments or car purchases.</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C501" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D501" t="n">
         <v>1</v>
@@ -10946,14 +10946,14 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>And what we do -- it looks like we're seeing a slowdown in growth rate.</t>
+          <t>And as I have already mentioned, I think that the estimates of – by members of the committee since perhaps 2012, as we have seen, have fallen by a full percentage point – while unemployment has fallen and inflation has not really responded.</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>2022</v>
+        <v>2013</v>
       </c>
       <c r="C502" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D502" t="n">
         <v>1</v>
@@ -10967,14 +10967,14 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>The . enlarged period . the language is conditioned precisely to the same points: . extended period . is conditioned by resources, by subdued inflation and stable inflation expectations.</t>
+          <t>Against this background, the Federal Committee on the Open Market today raised its key rate by 3⁄4 percentage points and expects that the current increases in this rate will be appropriate.</t>
         </is>
       </c>
       <c r="B503" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D503" t="n">
         <v>1</v>
@@ -10988,53 +10988,53 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>But also we want to see inflation move up back to our 2 percent objective over the medium term, and so seeing above-trend growth and continuing slack—greater slack in labor and product markets—I think that will help us achieve our objective as well with respect to inflation.</t>
+          <t>And what we do -- it looks like we're seeing a slowdown in growth rate.</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D504" t="n">
         <v>1</v>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>back_translation</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
+          <t>The . enlarged period . the language is conditioned precisely to the same points: . extended period . is conditioned by resources, by subdued inflation and stable inflation expectations.</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="C505" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D505" t="n">
         <v>1</v>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>directional_swap</t>
+          <t>back_translation</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
+          <t>But also we want to see inflation move up back to our 2 percent objective over the medium term, and so seeing above-trend growth and continuing slack—greater slack in labor and product markets—I think that will help us achieve our objective as well with respect to inflation.</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C506" t="n">
         <v>1</v>
@@ -11051,11 +11051,11 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>For example, the unemployment rate has fallen by 0.3 percentage points since March, and new claims for unemployment insurance have moved somewhat lower.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term inflation expectations are at the higher end of their historic ranges.</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C507" t="n">
         <v>1</v>
@@ -11072,11 +11072,11 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-decreasing holdings of longer-term securities will ensure that monetary policy remains highly restrictive, consistent with the pursuit of its mandated objectives of maximum employment and price stability.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Extended period” is conditioned on resource tightness, on subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="C508" t="n">
         <v>1</v>
@@ -11093,11 +11093,11 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 percent productivity, which is much lower.</t>
+          <t>For example, the unemployment rate has fallen by 0.3 percentage points since March, and new claims for unemployment insurance have moved somewhat lower.</t>
         </is>
       </c>
       <c r="B509" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C509" t="n">
         <v>1</v>
@@ -11114,11 +11114,11 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>You know, what you hear out there is that demand—you talk to banks, and they’ll say demand for loans is very, very high right now.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-decreasing holdings of longer-term securities will ensure that monetary policy remains highly restrictive, consistent with the pursuit of its mandated objectives of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B510" t="n">
-        <v>2014</v>
+        <v>2020</v>
       </c>
       <c r="C510" t="n">
         <v>1</v>
@@ -11135,11 +11135,11 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>With unemployment still moderating and inflation below the Committee’s longer-run objective, the Committee is continuing its highly restrictive policies.</t>
+          <t>Last year, we had 1.9 percent productivity, which is much lower.</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="C511" t="n">
         <v>1</v>
@@ -11156,11 +11156,11 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
+          <t>You know, what you hear out there is that demand—you talk to banks, and they’ll say demand for loans is very, very high right now.</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="C512" t="n">
         <v>1</v>
@@ -11177,11 +11177,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
+          <t>With unemployment still moderating and inflation below the Committee’s longer-run objective, the Committee is continuing its highly restrictive policies.</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C513" t="n">
         <v>1</v>
@@ -11198,11 +11198,11 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a commitment to cutting inflation to 2 percent.</t>
+          <t>And you know, we haven’t yet—we just touched 2 percent core inflation, to pick one measure—just touched it for a few months, and then we’ve risen back.</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C514" t="n">
         <v>1</v>
@@ -11219,11 +11219,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>So unemployment has tended to go up much faster for minorities and for others who are—tend to be at the high end of the income spectrum.</t>
+          <t>These measures, along with our weak guidance on interest rates and on our balance sheet, will ensure that monetary policy will continue to support the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C515" t="n">
         <v>1</v>
@@ -11240,11 +11240,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>In fact, it’s already—it’s already understood, I think, that—that there’s more—even though we’re at 3½ percent unemployment, there’s actually more tightness out there, in a sense.</t>
+          <t>But I want to emphasize that we do have a commitment to cutting inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C516" t="n">
         <v>1</v>
@@ -11261,11 +11261,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>As was highlighted by the Bureau of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but absent from their jobs would cut the unemployment rate by about 3 percentage points.</t>
+          <t>So unemployment has tended to go up much faster for minorities and for others who are—tend to be at the high end of the income spectrum.</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C517" t="n">
         <v>1</v>
@@ -11282,11 +11282,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>So, there has been impact through higher interest rates, but I think more broadly is the indirect effects.</t>
+          <t>In fact, it’s already—it’s already understood, I think, that—that there’s more—even though we’re at 3½ percent unemployment, there’s actually more tightness out there, in a sense.</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C518" t="n">
         <v>1</v>
@@ -11303,7 +11303,7 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some downward pressure on prices, and I’ll discuss why.</t>
+          <t>As was highlighted by the Bureau of Labor Statistics, this figure likely understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but absent from their jobs would cut the unemployment rate by about 3 percentage points.</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -11324,11 +11324,11 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Inflation has declined further below our longer-run objective, largely reflecting the higher energy prices I just mentioned.</t>
+          <t>So, there has been impact through higher interest rates, but I think more broadly is the indirect effects.</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C520" t="n">
         <v>1</v>
@@ -11345,14 +11345,14 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>By contrast, cutting rates too slowly would cut the risk that monetary policy would need to ease abruptly down the road, which could jeopardize the economic expansion.</t>
+          <t>During this time of reopening, we are likely to see some downward pressure on prices, and I’ll discuss why.</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C521" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D521" t="n">
         <v>1</v>
@@ -11366,14 +11366,14 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Well, our policy approach doesn’t involve intentionally trying to cut inflation.</t>
+          <t>Inflation has declined further below our longer-run objective, largely reflecting the higher energy prices I just mentioned.</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D522" t="n">
         <v>1</v>
@@ -11387,11 +11387,11 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Admittedly, some of the wage decreases is being eaten away by inflation.</t>
+          <t>By contrast, cutting rates too slowly would cut the risk that monetary policy would need to ease abruptly down the road, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C523" t="n">
         <v>0</v>
@@ -11408,11 +11408,11 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
+          <t>Well, our policy approach doesn’t involve intentionally trying to cut inflation.</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C524" t="n">
         <v>0</v>
@@ -11429,11 +11429,11 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>The American economy is very weak and well positioned to handle softer monetary policy.</t>
+          <t>Admittedly, some of the wage decreases is being eaten away by inflation.</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C525" t="n">
         <v>0</v>
@@ -11450,11 +11450,11 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, which featured an inflation shock followed by a quick fall in short-term rates.</t>
+          <t>But again, our basic forecast is one which is basically, as was pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this period of fiscal restraint; where unemployment continues to rise at a gradual pace as it has been since last September—and we have made some progress since last September; and inflation falls slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B526" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C526" t="n">
         <v>0</v>
@@ -11471,11 +11471,11 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>An unexpectedly sharp decrease in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>The American economy is very weak and well positioned to handle softer monetary policy.</t>
         </is>
       </c>
       <c r="B527" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="C527" t="n">
         <v>0</v>
@@ -11492,11 +11492,11 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>It was to do with, you know, weak monetary policy and fiscal stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively led to, you know, in certain parts of the economy, what you might call a vertical supply curve.</t>
+          <t>But you didn’t under the merely adverse scenario, which featured an inflation shock followed by a quick fall in short-term rates.</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>2021</v>
+        <v>2014</v>
       </c>
       <c r="C528" t="n">
         <v>0</v>
@@ -11513,11 +11513,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>We have a much more resilient, weaker banking system, and we’re not seeing some worrisome buildup in leverage or credit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor shaping monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major factor.</t>
+          <t>An unexpectedly sharp decrease in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="C529" t="n">
         <v>0</v>
@@ -11534,11 +11534,11 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can cut interest rates at the appropriate time, even if the balance sheet remains large for an extended period.</t>
+          <t>It was to do with, you know, weak monetary policy and fiscal stimulus into an economy that was recovering rapidly, and in which there were these supply-side barriers which effectively led to, you know, in certain parts of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B530" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C530" t="n">
         <v>0</v>
@@ -11555,11 +11555,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>The blow that the—from the pandemic was unprecedented both in its nature and in its sizing and in the amount of unemployment that it created and in the shock to economic activity.</t>
+          <t>We have a much more resilient, weaker banking system, and we’re not seeing some worrisome buildup in leverage or credit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor shaping monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major factor.</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="C531" t="n">
         <v>0</v>
@@ -11569,39 +11569,39 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>We are rather aware that very low interest rates, particularly for a protracted period, do have costs for a lot of people.</t>
+          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can cut interest rates at the appropriate time, even if the balance sheet remains large for an extended period.</t>
         </is>
       </c>
       <c r="B532" t="n">
         <v>2020</v>
       </c>
       <c r="C532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D532" t="n">
         <v>1</v>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>synonym_replacement</t>
+          <t>directional_swap</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak globular growth.</t>
+          <t>The blow that the—from the pandemic was unprecedented both in its nature and in its sizing and in the amount of unemployment that it created and in the shock to economic activity.</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C533" t="n">
         <v>0</v>
@@ -11618,14 +11618,14 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>But many other commodity prices have fallen further, and the reason I would give for that is that the emerging markets—China, the reside of Asia, and some other parts of the planetary—plus Europe, of course, are softer, and so global good demand is weaker.</t>
+          <t>We are rather aware that very low interest rates, particularly for a protracted period, do have costs for a lot of people.</t>
         </is>
       </c>
       <c r="B534" t="n">
         <v>2020</v>
       </c>
       <c r="C534" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D534" t="n">
         <v>1</v>
@@ -11639,14 +11639,14 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>And we’d like to see that in the conformation of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
+          <t>So, you know, I can’t—all I can tell you is, we’ll be looking at weak globular growth.</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="C535" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D535" t="n">
         <v>1</v>
@@ -11660,14 +11660,14 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>The American economy is very strong and well set to handle tighter monetary policy.</t>
+          <t>But many other commodity prices have fallen further, and the reason I would give for that is that the emerging markets—China, the reside of Asia, and some other parts of the planetary—plus Europe, of course, are softer, and so global good demand is weaker.</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>2016</v>
+        <v>2020</v>
       </c>
       <c r="C536" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D536" t="n">
         <v>1</v>
@@ -11681,14 +11681,14 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>And, you know, we do want inflation to run moderately supra 2 percent.</t>
+          <t>And we’d like to see that in the conformation of a series of declining monthly inflation readings—that’s what we’re looking for.</t>
         </is>
       </c>
       <c r="B537" t="n">
-        <v>2011</v>
+        <v>2017</v>
       </c>
       <c r="C537" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D537" t="n">
         <v>1</v>
@@ -11702,14 +11702,14 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>So in—in—in U-6, the U-6 unwavering of unemployment has tripled from 7 percent to 21 percent.</t>
+          <t>The American economy is very strong and well set to handle tighter monetary policy.</t>
         </is>
       </c>
       <c r="B538" t="n">
         <v>2016</v>
       </c>
       <c r="C538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D538" t="n">
         <v>1</v>
@@ -11723,11 +11723,11 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running below its longer-run likely this year and next year.</t>
+          <t>And, you know, we do want inflation to run moderately supra 2 percent.</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C539" t="n">
         <v>0</v>
@@ -11744,14 +11744,14 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>These are, you know, this is—this is the economy at closely full employment or in the range—in the neighborhood of full employment.</t>
+          <t>So in—in—in U-6, the U-6 unwavering of unemployment has tripled from 7 percent to 21 percent.</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="C540" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D540" t="n">
         <v>1</v>
@@ -11765,11 +11765,11 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>And inflation is moving—moving up, I think, toward our 2 pct objective.</t>
+          <t>So on the first, the Committee’s forecasts and those of most alfresco forecasters do show growth running below its longer-run likely this year and next year.</t>
         </is>
       </c>
       <c r="B541" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C541" t="n">
         <v>0</v>
@@ -11786,14 +11786,14 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Immediately, we’ve long expected, as most analysts have, to see some slowing in Taiwanese growth over time as they rebalance their economy.</t>
+          <t>These are, you know, this is—this is the economy at closely full employment or in the range—in the neighborhood of full employment.</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D542" t="n">
         <v>1</v>
@@ -11807,14 +11807,14 @@
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—ultimately, we’re not going to declare victory until we see a series of these, really look convincing evidence, compel evidence, that inflation is coming devour.</t>
+          <t>And inflation is moving—moving up, I think, toward our 2 pct objective.</t>
         </is>
       </c>
       <c r="B543" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D543" t="n">
         <v>1</v>
@@ -11828,14 +11828,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>The problem with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to cave or to work—to work on de-anchoring inflation outlook.</t>
+          <t>Immediately, we’ve long expected, as most analysts have, to see some slowing in Taiwanese growth over time as they rebalance their economy.</t>
         </is>
       </c>
       <c r="B544" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C544" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D544" t="n">
         <v>1</v>
@@ -11849,11 +11849,11 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>As I mentioned, monetary policy operates with incarcerate, so, the policies we have in place, we cerebrate, will gradually—only gradually—move inflation back to 2 percent.</t>
+          <t>So that’s the kind of thinking we’ll be doing, and, again, we’re looking—ultimately, we’re not going to declare victory until we see a series of these, really look convincing evidence, compel evidence, that inflation is coming devour.</t>
         </is>
       </c>
       <c r="B545" t="n">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="C545" t="n">
         <v>1</v>
@@ -11870,14 +11870,14 @@
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>And part of that just is the effect of lower involvement rates.</t>
+          <t>The problem with the current situation is that, that if you have a sustained period of supply shocks, those can actually start to cave or to work—to work on de-anchoring inflation outlook.</t>
         </is>
       </c>
       <c r="B546" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D546" t="n">
         <v>1</v>
@@ -11891,14 +11891,14 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>When we strain maximum employment, when we reach a state where labor grocery conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
+          <t>As I mentioned, monetary policy operates with incarcerate, so, the policies we have in place, we cerebrate, will gradually—only gradually—move inflation back to 2 percent.</t>
         </is>
       </c>
       <c r="B547" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D547" t="n">
         <v>1</v>
@@ -11912,11 +11912,11 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>We also suppose we wouldn’t raise rates just in response to very low unemployment, in the absence of inflation.</t>
+          <t>And part of that just is the effect of lower involvement rates.</t>
         </is>
       </c>
       <c r="B548" t="n">
-        <v>2020</v>
+        <v>2011</v>
       </c>
       <c r="C548" t="n">
         <v>0</v>
@@ -11933,11 +11933,11 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>Now, appendage of the Committee have different views about why this is likely to be true, that the funds rate—when the labor market is normalized and inflation is back to our objective—they maybe have slightly different views on exactly wherefore it’s likely to be the showcase that interest rates will be a little lower than they would in the longer run.</t>
+          <t>When we strain maximum employment, when we reach a state where labor grocery conditions are at maximum employment in the Committee’s judgment, it’s very possible that the inflation test will already be met.</t>
         </is>
       </c>
       <c r="B549" t="n">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="C549" t="n">
         <v>0</v>
@@ -11954,11 +11954,11 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>The entire Committee is committed to achieving our 2 pct inflation objective over the December 16, 2015 medium term, just as we want to fix sure that inflation doesn’t persist at levels above our Chair Yellen’s Press Conference FINAL 2 percent target.</t>
+          <t>We also suppose we wouldn’t raise rates just in response to very low unemployment, in the absence of inflation.</t>
         </is>
       </c>
       <c r="B550" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C550" t="n">
         <v>0</v>
@@ -11975,11 +11975,11 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>So, if we maintain a highly accommodative monetary policy for a very long time from here and the economy do as we gestate—namely, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have often more tightening in labor markets than you see in these projections.</t>
+          <t>Now, appendage of the Committee have different views about why this is likely to be true, that the funds rate—when the labor market is normalized and inflation is back to our objective—they maybe have slightly different views on exactly wherefore it’s likely to be the showcase that interest rates will be a little lower than they would in the longer run.</t>
         </is>
       </c>
       <c r="B551" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C551" t="n">
         <v>0</v>
@@ -11996,11 +11996,11 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>By getting unemployment down, we hope to work back to work some of the people who’ve been out of exploit as long as they have and, in that respect, try to avoid the longer-term consequences of people being out of work for month at a time.</t>
+          <t>The entire Committee is committed to achieving our 2 pct inflation objective over the December 16, 2015 medium term, just as we want to fix sure that inflation doesn’t persist at levels above our Chair Yellen’s Press Conference FINAL 2 percent target.</t>
         </is>
       </c>
       <c r="B552" t="n">
-        <v>2017</v>
+        <v>2021</v>
       </c>
       <c r="C552" t="n">
         <v>0</v>
@@ -12017,11 +12017,11 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>But I want to emphasize that we do have a committal to raising inflation to 2 percent.</t>
+          <t>So, if we maintain a highly accommodative monetary policy for a very long time from here and the economy do as we gestate—namely, it’s strong and the risks that are out there don’t materialize—my concern will be that we will have often more tightening in labor markets than you see in these projections.</t>
         </is>
       </c>
       <c r="B553" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C553" t="n">
         <v>0</v>
@@ -12038,7 +12038,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>Core inflation, which excludes energy and food prices, has been running fold to 1½ percent.</t>
+          <t>By getting unemployment down, we hope to work back to work some of the people who’ve been out of exploit as long as they have and, in that respect, try to avoid the longer-term consequences of people being out of work for month at a time.</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -12059,11 +12059,11 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
+          <t>But I want to emphasize that we do have a committal to raising inflation to 2 percent.</t>
         </is>
       </c>
       <c r="B555" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C555" t="n">
         <v>0</v>
@@ -12080,11 +12080,11 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>Well, that’s—what’s happening there is the fact that the relationship between resourcefulness utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
+          <t>Core inflation, which excludes energy and food prices, has been running fold to 1½ percent.</t>
         </is>
       </c>
       <c r="B556" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="C556" t="n">
         <v>0</v>
@@ -12101,11 +12101,11 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>We have not focussed on whether we play the liftoff test, because we don’t meet the liftoff test now because we’re not at maximum employment.</t>
+          <t>And what we—it looks like we’re seeing a retardation in the rate of growth.</t>
         </is>
       </c>
       <c r="B557" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C557" t="n">
         <v>0</v>
@@ -12122,11 +12122,11 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>And our plan as we do that is, as those purchases get to that level, we believe we can gradually reduce them, and we conceive we can also gradually tighten repo as—as we reach an ample level, as we’re satisfying demand immediately more from underlying reserves from bill leverage rather than from repo.</t>
+          <t>Well, that’s—what’s happening there is the fact that the relationship between resourcefulness utilization, or unemployment, and inflation has just gotten weaker and weaker over the years.</t>
         </is>
       </c>
       <c r="B558" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C558" t="n">
         <v>0</v>
@@ -12143,14 +12143,14 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Well, our policy approach doesn’t demand intentionally trying to raise inflation.</t>
+          <t>We have not focussed on whether we play the liftoff test, because we don’t meet the liftoff test now because we’re not at maximum employment.</t>
         </is>
       </c>
       <c r="B559" t="n">
         <v>2020</v>
       </c>
       <c r="C559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D559" t="n">
         <v>1</v>
@@ -12164,14 +12164,14 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>The jobs picture continue to be strong, with the unemployment rate near historic lows and with stronger wage gains.</t>
+          <t>And our plan as we do that is, as those purchases get to that level, we believe we can gradually reduce them, and we conceive we can also gradually tighten repo as—as we reach an ample level, as we’re satisfying demand immediately more from underlying reserves from bill leverage rather than from repo.</t>
         </is>
       </c>
       <c r="B560" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C560" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D560" t="n">
         <v>1</v>
@@ -12185,14 +12185,14 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>But in many countries around the Chair Yellen’s Press Conference FINAL man that are important commodity exporters, the decline we’ve seen in oil prices has had a depress effect on their growth, their craft with us and other trade partners, and caused problems that have had spillovers to the global thriftiness as well.</t>
+          <t>Well, our policy approach doesn’t demand intentionally trying to raise inflation.</t>
         </is>
       </c>
       <c r="B561" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C561" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D561" t="n">
         <v>1</v>
@@ -12206,11 +12206,11 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>But, I would tell, overall, we’re trying to sustain the expansion and keep, you know, close to our statutory goals, which are maximal employment and stable prices.</t>
+          <t>The jobs picture continue to be strong, with the unemployment rate near historic lows and with stronger wage gains.</t>
         </is>
       </c>
       <c r="B562" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C562" t="n">
         <v>1</v>
@@ -12227,11 +12227,11 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reductions in certain family of prices, such as tuner telephone services and prescription drugs.</t>
+          <t>But in many countries around the Chair Yellen’s Press Conference FINAL man that are important commodity exporters, the decline we’ve seen in oil prices has had a depress effect on their growth, their craft with us and other trade partners, and caused problems that have had spillovers to the global thriftiness as well.</t>
         </is>
       </c>
       <c r="B563" t="n">
-        <v>2012</v>
+        <v>2018</v>
       </c>
       <c r="C563" t="n">
         <v>0</v>
@@ -12248,14 +12248,14 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>And, in particular, I do personally believe that the slowdown is at least partly temp, and that we’ll see greater growth going onward.</t>
+          <t>But, I would tell, overall, we’re trying to sustain the expansion and keep, you know, close to our statutory goals, which are maximal employment and stable prices.</t>
         </is>
       </c>
       <c r="B564" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D564" t="n">
         <v>1</v>
@@ -12269,14 +12269,14 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of the longer-run normal unemployment rate proceed down a tenth to 4.6 percentage.</t>
+          <t>The recent lower readings on inflation have been driven significantly by what appear to be one-off reductions in certain family of prices, such as tuner telephone services and prescription drugs.</t>
         </is>
       </c>
       <c r="B565" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="C565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D565" t="n">
         <v>1</v>
@@ -12290,11 +12290,11 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>In light of increased uncertainties and muted inflation pressures, we now emphasize that the Committee will close reminder the implications of incoming information for the economic prospect and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
+          <t>And, in particular, I do personally believe that the slowdown is at least partly temp, and that we’ll see greater growth going onward.</t>
         </is>
       </c>
       <c r="B566" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -12311,14 +12311,14 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>We’re charged by Congress with try to pursue maximum employment, and we have taken that very seriously.</t>
+          <t>In addition, the median estimate of the longer-run normal unemployment rate proceed down a tenth to 4.6 percentage.</t>
         </is>
       </c>
       <c r="B567" t="n">
         <v>2022</v>
       </c>
       <c r="C567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D567" t="n">
         <v>1</v>
@@ -12332,14 +12332,14 @@
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can raise interest rates at the appropriate time, even if the equaliser sheet remains orotund for an extended period.</t>
+          <t>In light of increased uncertainties and muted inflation pressures, we now emphasize that the Committee will close reminder the implications of incoming information for the economic prospect and will act as appropriate to sustain the expansion with a strong labor market and inflation near its 2 percent objective.</t>
         </is>
       </c>
       <c r="B568" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D568" t="n">
         <v>1</v>
@@ -12353,14 +12353,14 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>Against this backdrop, today the Federal Exposed Commercialize Committee raised its policy interest rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
+          <t>We’re charged by Congress with try to pursue maximum employment, and we have taken that very seriously.</t>
         </is>
       </c>
       <c r="B569" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C569" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D569" t="n">
         <v>1</v>
@@ -12374,14 +12374,14 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Again, that’s not a forecast, I’ve made a hypothesis, which would imply slower betterment in unemployment.</t>
+          <t>So I, you know, I’m—I feel quite comfortable that we can—in particular, that we can raise interest rates at the appropriate time, even if the equaliser sheet remains orotund for an extended period.</t>
         </is>
       </c>
       <c r="B570" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D570" t="n">
         <v>1</v>
@@ -12395,14 +12395,14 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>For example, the unemployment rate has risen by 0.3 portion points since March, and new claims for unemployment insurance have moved fairly higher.</t>
+          <t>Against this backdrop, today the Federal Exposed Commercialize Committee raised its policy interest rate by ¾ percentage point and anticipates that ongoing increases in that rate will be appropriate.</t>
         </is>
       </c>
       <c r="B571" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C571" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D571" t="n">
         <v>1</v>
@@ -12416,11 +12416,11 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>So, with this coronavirus arriving, we evaluate that the—the net effectuate of this will be to—to have inflation move down even a little bit more.</t>
+          <t>Again, that’s not a forecast, I’ve made a hypothesis, which would imply slower betterment in unemployment.</t>
         </is>
       </c>
       <c r="B572" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C572" t="n">
         <v>0</v>
@@ -12437,11 +12437,11 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>But, first, on inflation expectations, it is genuine that the breakevens from the inflation-adjusted—inflation-indexed bonds have come down.</t>
+          <t>For example, the unemployment rate has risen by 0.3 portion points since March, and new claims for unemployment insurance have moved fairly higher.</t>
         </is>
       </c>
       <c r="B573" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C573" t="n">
         <v>0</v>
@@ -12458,14 +12458,14 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>After overhasty drops in March and April, employment rose strongly in May and June as many people returned to process from temporary layoffs.</t>
+          <t>So, with this coronavirus arriving, we evaluate that the—the net effectuate of this will be to—to have inflation move down even a little bit more.</t>
         </is>
       </c>
       <c r="B574" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D574" t="n">
         <v>1</v>
@@ -12479,11 +12479,11 @@
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially in sectors that have been most affected by the pandemic, has adjudge gloomy consumer prices, and overall, inflation is running well below our 2 percent thirster-run objective.</t>
+          <t>But, first, on inflation expectations, it is genuine that the breakevens from the inflation-adjusted—inflation-indexed bonds have come down.</t>
         </is>
       </c>
       <c r="B575" t="n">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C575" t="n">
         <v>0</v>
@@ -12500,11 +12500,11 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>I would say, in the area of commercial real estate, while rating are high, we are seeing some tightening of loaning standards and less debt growth associated with that rise in commercial real estate prices.</t>
+          <t>After overhasty drops in March and April, employment rose strongly in May and June as many people returned to process from temporary layoffs.</t>
         </is>
       </c>
       <c r="B576" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="C576" t="n">
         <v>1</v>
@@ -12521,11 +12521,11 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>And, and those are—that’s again—that goes to keeping this sequence as short as it can be and avoiding unnecessary business bankruptcies, unneeded household bankruptcies, and unnecessary long-term stays of unemployment or supporting people through them so that they can maintain their financial footing and their living and be able to go back to work in a productive mode.</t>
+          <t>More broadly, however, weaker demand, especially in sectors that have been most affected by the pandemic, has adjudge gloomy consumer prices, and overall, inflation is running well below our 2 percent thirster-run objective.</t>
         </is>
       </c>
       <c r="B577" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C577" t="n">
         <v>0</v>
@@ -12542,14 +12542,14 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-increasing retention of longer-condition securities will ensure that monetary policy remains highly accommodative, consistent with the pursuit of its mandate objectives of maximum employment and price stability.</t>
+          <t>I would say, in the area of commercial real estate, while rating are high, we are seeing some tightening of loaning standards and less debt growth associated with that rise in commercial real estate prices.</t>
         </is>
       </c>
       <c r="B578" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C578" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D578" t="n">
         <v>1</v>
@@ -12563,11 +12563,11 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>We think that the economy will need highly accommodative monetary policy and the use of our tools for an go period.</t>
+          <t>And, and those are—that’s again—that goes to keeping this sequence as short as it can be and avoiding unnecessary business bankruptcies, unneeded household bankruptcies, and unnecessary long-term stays of unemployment or supporting people through them so that they can maintain their financial footing and their living and be able to go back to work in a productive mode.</t>
         </is>
       </c>
       <c r="B579" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C579" t="n">
         <v>0</v>
@@ -12584,14 +12584,14 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>It isn’t the kind of inflation that’s spread broadly crosswise the economy.</t>
+          <t>The Federal Reserve’s enhanced guidance about its policy intentions and its substantial and still-increasing retention of longer-condition securities will ensure that monetary policy remains highly accommodative, consistent with the pursuit of its mandate objectives of maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B580" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D580" t="n">
         <v>1</v>
@@ -12605,14 +12605,14 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>As the factors restraining economic growth are contrive to fade further over time, the median rate rises to 3 percent by the end of 2018, close to its longer-run normal flush.</t>
+          <t>We think that the economy will need highly accommodative monetary policy and the use of our tools for an go period.</t>
         </is>
       </c>
       <c r="B581" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C581" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D581" t="n">
         <v>1</v>
@@ -12626,14 +12626,14 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
+          <t>It isn’t the kind of inflation that’s spread broadly crosswise the economy.</t>
         </is>
       </c>
       <c r="B582" t="n">
-        <v>2012</v>
+        <v>2021</v>
       </c>
       <c r="C582" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D582" t="n">
         <v>1</v>
@@ -12647,11 +12647,11 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>Our role, though, is also to, you bonk, to make certain that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually raising rates.</t>
+          <t>As the factors restraining economic growth are contrive to fade further over time, the median rate rises to 3 percent by the end of 2018, close to its longer-run normal flush.</t>
         </is>
       </c>
       <c r="B583" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C583" t="n">
         <v>1</v>
@@ -12668,14 +12668,14 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>In spite of having such slowly growth, disappointing productivity growth, we have a labor mart that last year generated an average of about 230,000 jobs a month and so alir this year has been generating about 180,000 jobs a month.</t>
+          <t>Long-term unemployment in the stream economy is—is the worst—really the worst it’s been in the postwar period.</t>
         </is>
       </c>
       <c r="B584" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="C584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D584" t="n">
         <v>1</v>
@@ -12689,14 +12689,14 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>The “extended period” language is conditioned on exactly those same points: “Lengthened period” is conditioned on resource slack, on subdued inflation, and on stable inflation expectation.</t>
+          <t>Our role, though, is also to, you bonk, to make certain that—that maximum employment happens in a context of price stability and financial stability, which is why we’re gradually raising rates.</t>
         </is>
       </c>
       <c r="B585" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D585" t="n">
         <v>1</v>
@@ -12710,14 +12710,14 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>At the sentence of our FOMC meeting in January, prospects for continued economic growth remained favorable, and we judged that monetary policy was well positioned to reenforcement that outlook.</t>
+          <t>In spite of having such slowly growth, disappointing productivity growth, we have a labor mart that last year generated an average of about 230,000 jobs a month and so alir this year has been generating about 180,000 jobs a month.</t>
         </is>
       </c>
       <c r="B586" t="n">
-        <v>2017</v>
+        <v>2013</v>
       </c>
       <c r="C586" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D586" t="n">
         <v>1</v>
@@ -12731,14 +12731,14 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly down the route, which could jeopardize the economic expansion.</t>
+          <t>The “extended period” language is conditioned on exactly those same points: “Lengthened period” is conditioned on resource slack, on subdued inflation, and on stable inflation expectation.</t>
         </is>
       </c>
       <c r="B587" t="n">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="C587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D587" t="n">
         <v>1</v>
@@ -12752,11 +12752,11 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>And I think, more loosely, monetary policy is also supporting house spending and home buying by keeping the labor market strong, keeping workers’ incomes rising, and save consumer confidence at high levels, where it currently is.</t>
+          <t>At the sentence of our FOMC meeting in January, prospects for continued economic growth remained favorable, and we judged that monetary policy was well positioned to reenforcement that outlook.</t>
         </is>
       </c>
       <c r="B588" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C588" t="n">
         <v>0</v>
@@ -12773,14 +12773,14 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>And as I mentioned earlier, the unemployment wane last month was more than 100 percent accounted for by declines in participation.</t>
+          <t>By contrast, raising rates too slowly would raise the risk that monetary policy would need to tighten abruptly down the route, which could jeopardize the economic expansion.</t>
         </is>
       </c>
       <c r="B589" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C589" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D589" t="n">
         <v>1</v>
@@ -12794,11 +12794,11 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>These measures, along with our strong counselling on interest rates and on our balance sheet, will ensure that monetary policy will continue to livelihood the economy until the recovery is complete.</t>
+          <t>And I think, more loosely, monetary policy is also supporting house spending and home buying by keeping the labor market strong, keeping workers’ incomes rising, and save consumer confidence at high levels, where it currently is.</t>
         </is>
       </c>
       <c r="B590" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C590" t="n">
         <v>0</v>
@@ -12815,14 +12815,14 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>The Federal Reserve’s response is maneuver by our mandate to promote maximum employment and stable prices for the American people, along with our responsibilities to advertise the stability of the financial system.</t>
+          <t>And as I mentioned earlier, the unemployment wane last month was more than 100 percent accounted for by declines in participation.</t>
         </is>
       </c>
       <c r="B591" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C591" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D591" t="n">
         <v>1</v>
@@ -12836,11 +12836,11 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>By the room, we’re also not at maximum employment, as I mentioned.</t>
+          <t>These measures, along with our strong counselling on interest rates and on our balance sheet, will ensure that monetary policy will continue to livelihood the economy until the recovery is complete.</t>
         </is>
       </c>
       <c r="B592" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="C592" t="n">
         <v>0</v>
@@ -12857,14 +12857,14 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>Well, if the economy worsens and inflation stay relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t modification the language.</t>
+          <t>The Federal Reserve’s response is maneuver by our mandate to promote maximum employment and stable prices for the American people, along with our responsibilities to advertise the stability of the financial system.</t>
         </is>
       </c>
       <c r="B593" t="n">
         <v>2020</v>
       </c>
       <c r="C593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D593" t="n">
         <v>1</v>
@@ -12878,14 +12878,14 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>As always, our actions are conduct by our congressional mandate to promote maximum employment and price stability.</t>
+          <t>By the room, we’re also not at maximum employment, as I mentioned.</t>
         </is>
       </c>
       <c r="B594" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="C594" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D594" t="n">
         <v>1</v>
@@ -12899,14 +12899,14 @@
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>In any case, we, our job is to deliver price constancy, and I think—you can think of price stability as an asset that just delivers prominent benefits to society over a long period of time.</t>
+          <t>Well, if the economy worsens and inflation stay relatively low, then we wouldn’t begin to exit, and, therefore, we wouldn’t modification the language.</t>
         </is>
       </c>
       <c r="B595" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D595" t="n">
         <v>1</v>
@@ -12920,14 +12920,14 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>Monetary policy has a function, and it really is in, you know—our original role was providing liquidity to financial systems when they’re under stress, and that’s—that’s really split of what we did today.</t>
+          <t>As always, our actions are conduct by our congressional mandate to promote maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B596" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D596" t="n">
         <v>1</v>
@@ -12941,11 +12941,11 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>We have a much more resilient, stronger deposit system, and we’re not seeing some worrisome buildup in leverage or accredit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor determine monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major element.</t>
+          <t>In any case, we, our job is to deliver price constancy, and I think—you can think of price stability as an asset that just delivers prominent benefits to society over a long period of time.</t>
         </is>
       </c>
       <c r="B597" t="n">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="C597" t="n">
         <v>1</v>
@@ -12962,14 +12962,14 @@
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>And—but inflation expectations did not move strongly down here in the United Posit.</t>
+          <t>Monetary policy has a function, and it really is in, you know—our original role was providing liquidity to financial systems when they’re under stress, and that’s—that’s really split of what we did today.</t>
         </is>
       </c>
       <c r="B598" t="n">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="C598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D598" t="n">
         <v>1</v>
@@ -12983,14 +12983,14 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>So those who can get reference, together with the low prices of houses, are at—able to bribe much more house than they could have a few years ago.</t>
+          <t>We have a much more resilient, stronger deposit system, and we’re not seeing some worrisome buildup in leverage or accredit growth at successive levels.1 So, you know, this is something that the FOMC pays attention to, but if you ask me, is this a significant factor determine monetary policy now, well, it’s on the list of risks, it’s not a major—it’s not a major element.</t>
         </is>
       </c>
       <c r="B599" t="n">
-        <v>2021</v>
+        <v>2015</v>
       </c>
       <c r="C599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D599" t="n">
         <v>1</v>
@@ -13004,14 +13004,14 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>So unemployment has tended to go up much faster for minority and for others who are—tend to be at the low end of the income spectrum.</t>
+          <t>And—but inflation expectations did not move strongly down here in the United Posit.</t>
         </is>
       </c>
       <c r="B600" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="C600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D600" t="n">
         <v>1</v>
@@ -13025,14 +13025,14 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>So, you know, as I mention, the Committee acutely feels its obligation to move to make sure that we restore price stability and is determined to use its cock to do so.</t>
+          <t>So those who can get reference, together with the low prices of houses, are at—able to bribe much more house than they could have a few years ago.</t>
         </is>
       </c>
       <c r="B601" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C601" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D601" t="n">
         <v>1</v>
@@ -13046,14 +13046,14 @@
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>The U.S. economy is in a beneficial place, and we will continue to use our monetary policy tools to help keep it there.</t>
+          <t>So unemployment has tended to go up much faster for minority and for others who are—tend to be at the low end of the income spectrum.</t>
         </is>
       </c>
       <c r="B602" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C602" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D602" t="n">
         <v>1</v>
@@ -13067,14 +13067,14 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>I tight sure parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard sentence there.</t>
+          <t>So, you know, as I mention, the Committee acutely feels its obligation to move to make sure that we restore price stability and is determined to use its cock to do so.</t>
         </is>
       </c>
       <c r="B603" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D603" t="n">
         <v>1</v>
@@ -13088,14 +13088,14 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>But also we want to see inflation move up back to our 2 percent objective over the medium condition, and so seeing above-trend growth and continuing tightness—greater tightness in labor and product grocery—I think that will help us reach our objective as well with respect to inflation.</t>
+          <t>The U.S. economy is in a beneficial place, and we will continue to use our monetary policy tools to help keep it there.</t>
         </is>
       </c>
       <c r="B604" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D604" t="n">
         <v>1</v>
@@ -13109,7 +13109,7 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>I carry that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economic reasons.</t>
+          <t>I tight sure parts of South Carolina have developed pretty strongly but the part where I come from—mostly agricultural, it has a little bit of manufacturing—has a very high unemployment rate, a high foreclosure rate, and people are having a hard sentence there.</t>
         </is>
       </c>
       <c r="B605" t="n">
@@ -13130,11 +13130,11 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>However, at 7.7 percent, the unemployment rate clay elevated.</t>
+          <t>But also we want to see inflation move up back to our 2 percent objective over the medium condition, and so seeing above-trend growth and continuing tightness—greater tightness in labor and product grocery—I think that will help us reach our objective as well with respect to inflation.</t>
         </is>
       </c>
       <c r="B606" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="C606" t="n">
         <v>0</v>
@@ -13151,14 +13151,14 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>And inflation is well supra target.</t>
+          <t>I carry that to continue, and I would expect also to see some improvement in the point of part-time employment that’s for economic reasons.</t>
         </is>
       </c>
       <c r="B607" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C607" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D607" t="n">
         <v>1</v>
@@ -13172,14 +13172,14 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>And productiveness’s been very low.</t>
+          <t>However, at 7.7 percent, the unemployment rate clay elevated.</t>
         </is>
       </c>
       <c r="B608" t="n">
-        <v>2020</v>
+        <v>2013</v>
       </c>
       <c r="C608" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D608" t="n">
         <v>1</v>
@@ -13193,14 +13193,14 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>During this time of reopening, we are likely to see some upward pressing on prices, and I’ll discuss why.</t>
+          <t>And inflation is well supra target.</t>
         </is>
       </c>
       <c r="B609" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C609" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D609" t="n">
         <v>1</v>
@@ -13214,11 +13214,11 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how libertine the labor market will heal, or how fast—regretful, inflation will move up.</t>
+          <t>And productiveness’s been very low.</t>
         </is>
       </c>
       <c r="B610" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C610" t="n">
         <v>1</v>
@@ -13235,11 +13235,11 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>And you know, we haven’t yet—we just pertain 2 percentage core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
+          <t>During this time of reopening, we are likely to see some upward pressing on prices, and I’ll discuss why.</t>
         </is>
       </c>
       <c r="B611" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C611" t="n">
         <v>0</v>
@@ -13256,11 +13256,11 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>An accidentally sharp increase in wages or inflation could tell you that you’re reaching those points.</t>
+          <t>So you’re going to have different perspectives from Committee participants about how fast growth will be, how libertine the labor market will heal, or how fast—regretful, inflation will move up.</t>
         </is>
       </c>
       <c r="B612" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C612" t="n">
         <v>1</v>
@@ -13277,11 +13277,11 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>So we want to see that healthy process extend as we decide what the admittedly state of the economy is, and we think it will evolve in a way that will mean lower inflation.</t>
+          <t>And you know, we haven’t yet—we just pertain 2 percentage core inflation, to pick one measure—just touched it for a few months, and then we’ve fallen back.</t>
         </is>
       </c>
       <c r="B613" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C613" t="n">
         <v>0</v>
@@ -13298,14 +13298,14 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>In fact, it’s already—it’s already empathise, I think, that—that there’s more—even though we’re at 3½ percentage unemployment, there’s actually more slack out there, in a sense.</t>
+          <t>An accidentally sharp increase in wages or inflation could tell you that you’re reaching those points.</t>
         </is>
       </c>
       <c r="B614" t="n">
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="C614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D614" t="n">
         <v>1</v>
@@ -13319,14 +13319,14 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>But you do see growth in services, so you—this pattern round the creation of Chair Powell’s Press Conference FINAL weak manufacturing but growth in the far larger part of the services economy, which has led to low unemployment, good job creation, rising wages, that’s kind of the two vauntingly while of it that you see.</t>
+          <t>So we want to see that healthy process extend as we decide what the admittedly state of the economy is, and we think it will evolve in a way that will mean lower inflation.</t>
         </is>
       </c>
       <c r="B615" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D615" t="n">
         <v>1</v>
@@ -13340,14 +13340,14 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>And that is a assertion about productivity growth, which has been pretty disappointing.</t>
+          <t>In fact, it’s already—it’s already empathise, I think, that—that there’s more—even though we’re at 3½ percentage unemployment, there’s actually more slack out there, in a sense.</t>
         </is>
       </c>
       <c r="B616" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C616" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D616" t="n">
         <v>1</v>
@@ -13361,14 +13361,14 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>So you have visualise a shifting this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower plan route for global growth—for growth in the global economy outside the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
+          <t>But you do see growth in services, so you—this pattern round the creation of Chair Powell’s Press Conference FINAL weak manufacturing but growth in the far larger part of the services economy, which has led to low unemployment, good job creation, rising wages, that’s kind of the two vauntingly while of it that you see.</t>
         </is>
       </c>
       <c r="B617" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C617" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D617" t="n">
         <v>1</v>
@@ -13382,14 +13382,14 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>If we think that the potential growth rate of the economy is somewhere between, somewhere around 1.75 percent, 2.8 pct is strong economical growth.</t>
+          <t>And that is a assertion about productivity growth, which has been pretty disappointing.</t>
         </is>
       </c>
       <c r="B618" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C618" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D618" t="n">
         <v>1</v>
@@ -13403,11 +13403,11 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>So, there has been impact through lower interest rates, but I think more broadly is the indirect burden.</t>
+          <t>So you have visualise a shifting this time in most participants’ assessments of the appropriate path for policy, and, as I tried to indicate, I think that largely reflects a somewhat slower plan route for global growth—for growth in the global economy outside the United States—and for some tightening in credit conditions in the form of an increase in spreads.</t>
         </is>
       </c>
       <c r="B619" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="C619" t="n">
         <v>0</v>
@@ -13424,14 +13424,14 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>To do that you've got to have price stability, and we've bring to get back to price stability so that we can have a labor commercialize where people's wages aren't being eaten up by inflation and where we can have a long expansion too.</t>
+          <t>If we think that the potential growth rate of the economy is somewhere between, somewhere around 1.75 percent, 2.8 pct is strong economical growth.</t>
         </is>
       </c>
       <c r="B620" t="n">
         <v>2021</v>
       </c>
       <c r="C620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D620" t="n">
         <v>1</v>
@@ -13445,11 +13445,11 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>Last year, we had 1.9 pct productivity, which is much higher.</t>
+          <t>So, there has been impact through lower interest rates, but I think more broadly is the indirect burden.</t>
         </is>
       </c>
       <c r="B621" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C621" t="n">
         <v>0</v>
@@ -13466,11 +13466,11 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>In other vitrine, it’s pretty clear that inflation has spread more broadly across services.</t>
+          <t>To do that you've got to have price stability, and we've bring to get back to price stability so that we can have a labor commercialize where people's wages aren't being eaten up by inflation and where we can have a long expansion too.</t>
         </is>
       </c>
       <c r="B622" t="n">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="C622" t="n">
         <v>1</v>
@@ -13487,14 +13487,14 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>But to the extent that continues to be the case, that should make it easier to restitute price stability.</t>
+          <t>Last year, we had 1.9 pct productivity, which is much higher.</t>
         </is>
       </c>
       <c r="B623" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D623" t="n">
         <v>1</v>
@@ -13508,14 +13508,14 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>Inflation has continued to run under our longer-run objective, in part reflecting lower energy prices.</t>
+          <t>In other vitrine, it’s pretty clear that inflation has spread more broadly across services.</t>
         </is>
       </c>
       <c r="B624" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C624" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D624" t="n">
         <v>1</v>
@@ -13529,14 +13529,14 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>So for many, many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy has been—has been light.</t>
+          <t>But to the extent that continues to be the case, that should make it easier to restitute price stability.</t>
         </is>
       </c>
       <c r="B625" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="C625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D625" t="n">
         <v>1</v>
@@ -13550,11 +13550,11 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>Well, we—as a Committee, we do not hope inflation undershoots.</t>
+          <t>Inflation has continued to run under our longer-run objective, in part reflecting lower energy prices.</t>
         </is>
       </c>
       <c r="B626" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="C626" t="n">
         <v>0</v>
@@ -13571,11 +13571,11 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>I don’t think we look at—I understand what you’re asking, but we’re looking at—our mandate is price inflation and uttermost employment, and that’s what we’re await at with setting interest rates.</t>
+          <t>So for many, many years, we’ve been far from maximum employment and stable prices, and so the need for accommodative policy has been—has been light.</t>
         </is>
       </c>
       <c r="B627" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C627" t="n">
         <v>0</v>
@@ -13592,11 +13592,11 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>With unemployment still elevated and inflation under the Committee’s longer-run objective, the Committee is continuing its highly accommodative policies.</t>
+          <t>Well, we—as a Committee, we do not hope inflation undershoots.</t>
         </is>
       </c>
       <c r="B628" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C628" t="n">
         <v>0</v>
@@ -13613,11 +13613,11 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>The central tendency of the unemployment rate projections is slenderly lower than in the March expulsion and now stands at 6.0 to 6.1 percent at the end of this year.</t>
+          <t>I don’t think we look at—I understand what you’re asking, but we’re looking at—our mandate is price inflation and uttermost employment, and that’s what we’re await at with setting interest rates.</t>
         </is>
       </c>
       <c r="B629" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C629" t="n">
         <v>0</v>
@@ -13634,14 +13634,14 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to come downwards.</t>
+          <t>With unemployment still elevated and inflation under the Committee’s longer-run objective, the Committee is continuing its highly accommodative policies.</t>
         </is>
       </c>
       <c r="B630" t="n">
         <v>2019</v>
       </c>
       <c r="C630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D630" t="n">
         <v>1</v>
@@ -13655,11 +13655,11 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>As was highlighted by the Bureau of Labor Statistics, this figure belike understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but lacking from their jobs would raise the unemployment rate by about 3 percentage luff.</t>
+          <t>The central tendency of the unemployment rate projections is slenderly lower than in the March expulsion and now stands at 6.0 to 6.1 percent at the end of this year.</t>
         </is>
       </c>
       <c r="B631" t="n">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -13676,11 +13676,11 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>[MASK] role, [MASK], is also to, you know, to make sure that—that [MASK] employment happens in a context of price stability and financial stability, which is [MASK] we’re gradually [MASK] rates.</t>
+          <t>I mean, it really depends on how long it takes for wages and, more than that, prices to come down for inflation to come downwards.</t>
         </is>
       </c>
       <c r="B632" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C632" t="n">
         <v>1</v>
@@ -13690,42 +13690,42 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>masking</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>And we’ve seen [MASK] outflows of capital from [MASK] countries, pressures on their exchange rates, and concerns about their performance going [MASK].</t>
+          <t>As was highlighted by the Bureau of Labor Statistics, this figure belike understates the extent of unemployment; accounting for the unusually large number of workers who reported themselves as employed but lacking from their jobs would raise the unemployment rate by about 3 percentage luff.</t>
         </is>
       </c>
       <c r="B633" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C633" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D633" t="n">
         <v>1</v>
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>masking</t>
+          <t>synonym_replacement</t>
         </is>
       </c>
     </row>
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>[MASK] don’t [MASK] we look at—I understand what [MASK]’re asking, but we’[MASK] looking at—our mandate is price inflation and maximum employment, and [MASK]’s what we’re looking at [MASK] setting interest rates.</t>
+          <t>[MASK] role, [MASK], is also to, you know, to make sure that—that [MASK] employment happens in a context of price stability and financial stability, which is [MASK] we’re gradually [MASK] rates.</t>
         </is>
       </c>
       <c r="B634" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C634" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D634" t="n">
         <v>1</v>
@@ -13739,7 +13739,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>[MASK] the maximum level of employment that’s consistent with [MASK] [MASK] evolves over time within a—within a business cycle [MASK] over a longer period, in [MASK] reflecting [the] evolution of the [MASK] that affect labor [MASK], including those related to the pandemic.</t>
+          <t>And we’ve seen [MASK] outflows of capital from [MASK] countries, pressures on their exchange rates, and concerns about their performance going [MASK].</t>
         </is>
       </c>
       <c r="B635" t="n">
@@ -13760,14 +13760,14 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>And that [MASK] a statement about productivity growth, which [MASK] been pretty disappointing.</t>
+          <t>[MASK] don’t [MASK] we look at—I understand what [MASK]’re asking, but we’[MASK] looking at—our mandate is price inflation and maximum employment, and [MASK]’s what we’re looking at [MASK] setting interest rates.</t>
         </is>
       </c>
       <c r="B636" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C636" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D636" t="n">
         <v>1</v>
@@ -13781,14 +13781,14 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Inflation pressures remain muted, and indicators of longer-term [MASK] expectations are at the lower end [MASK] their historic [MASK].</t>
+          <t>[MASK] the maximum level of employment that’s consistent with [MASK] [MASK] evolves over time within a—within a business cycle [MASK] over a longer period, in [MASK] reflecting [the] evolution of the [MASK] that affect labor [MASK], including those related to the pandemic.</t>
         </is>
       </c>
       <c r="B637" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C637" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D637" t="n">
         <v>1</v>
@@ -13802,14 +13802,14 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>So the FOMC will always, in some sense, [MASK] [MASK] projections of forward interest [MASK], but clearly, because the participants and the people around the table are [MASK] same, the projections should give significant information about where the [MASK] is [MASK] to go.</t>
+          <t>And that [MASK] a statement about productivity growth, which [MASK] been pretty disappointing.</t>
         </is>
       </c>
       <c r="B638" t="n">
-        <v>2013</v>
+        <v>2020</v>
       </c>
       <c r="C638" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D638" t="n">
         <v>1</v>
@@ -13823,11 +13823,11 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>[MASK] inflation, [MASK] excludes energy and food prices, has been running close to 1½ percent.</t>
+          <t>Inflation pressures remain muted, and indicators of longer-term [MASK] expectations are at the lower end [MASK] their historic [MASK].</t>
         </is>
       </c>
       <c r="B639" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C639" t="n">
         <v>0</v>
@@ -13844,14 +13844,14 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>[MASK] part of that just [MASK] the effect of lower interest rates.</t>
+          <t>So the FOMC will always, in some sense, [MASK] [MASK] projections of forward interest [MASK], but clearly, because the participants and the people around the table are [MASK] same, the projections should give significant information about where the [MASK] is [MASK] to go.</t>
         </is>
       </c>
       <c r="B640" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="C640" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D640" t="n">
         <v>1</v>
@@ -13865,11 +13865,11 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>We’[MASK] charged [MASK] Congress with trying to pursue maximum [MASK], and we have taken that very seriously.</t>
+          <t>[MASK] inflation, [MASK] excludes energy and food prices, has been running close to 1½ percent.</t>
         </is>
       </c>
       <c r="B641" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C641" t="n">
         <v>0</v>
@@ -13886,14 +13886,14 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>And, at a high level, yes, I would say, and [MASK]’[MASK] said before, that it’s really [MASK] policy that is [MASK] [MASK] and that has much more to do with—fiscal policy can do [MASK] things that will increase the longer-run growth [MASK] of the United States by improving productivity and labor force [MASK] 18, 2019 participation and the [MASK] and [MASK] of workers.</t>
+          <t>[MASK] part of that just [MASK] the effect of lower interest rates.</t>
         </is>
       </c>
       <c r="B642" t="n">
         <v>2011</v>
       </c>
       <c r="C642" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D642" t="n">
         <v>1</v>
@@ -13907,11 +13907,11 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>The entire Committee is committed [MASK] achieving our 2 percent inflation objective over the December 16, 2015 [MASK] term, just [MASK] we want to make sure that [MASK] doesn’t persist at [MASK] above our Chair Yellen’s Press Conference [MASK] 2 percent objective.</t>
+          <t>We’[MASK] charged [MASK] Congress with trying to pursue maximum [MASK], and we have taken that very seriously.</t>
         </is>
       </c>
       <c r="B643" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C643" t="n">
         <v>0</v>
@@ -13928,11 +13928,11 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>[MASK] I’m telling you is [MASK] the stance of monetary policy we have today, [MASK] believe, is appropriate.</t>
+          <t>And, at a high level, yes, I would say, and [MASK]’[MASK] said before, that it’s really [MASK] policy that is [MASK] [MASK] and that has much more to do with—fiscal policy can do [MASK] things that will increase the longer-run growth [MASK] of the United States by improving productivity and labor force [MASK] 18, 2019 participation and the [MASK] and [MASK] of workers.</t>
         </is>
       </c>
       <c r="B644" t="n">
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="C644" t="n">
         <v>2</v>
@@ -13949,14 +13949,14 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>So let me start with the question pertaining to [MASK] [MASK].</t>
+          <t>The entire Committee is committed [MASK] achieving our 2 percent inflation objective over the December 16, 2015 [MASK] term, just [MASK] we want to make sure that [MASK] doesn’t persist at [MASK] above our Chair Yellen’s Press Conference [MASK] 2 percent objective.</t>
         </is>
       </c>
       <c r="B645" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C645" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D645" t="n">
         <v>1</v>
@@ -13970,14 +13970,14 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>In addition, the median estimate of [MASK] longer-[MASK] normal unemployment rate moved down a [MASK] to 4.6 percent.</t>
+          <t>[MASK] I’m telling you is [MASK] the stance of monetary policy we have today, [MASK] believe, is appropriate.</t>
         </is>
       </c>
       <c r="B646" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C646" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D646" t="n">
         <v>1</v>
@@ -13991,11 +13991,11 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>Inflation, in fact, is under [MASK], and starting [MASK] come down.</t>
+          <t>So let me start with the question pertaining to [MASK] [MASK].</t>
         </is>
       </c>
       <c r="B647" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C647" t="n">
         <v>2</v>
@@ -14012,14 +14012,14 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Again, that’s not a forecast, I’[MASK] made [MASK] hypothesis, which would imply [MASK] improvement in unemployment.</t>
+          <t>In addition, the median estimate of [MASK] longer-[MASK] normal unemployment rate moved down a [MASK] to 4.6 percent.</t>
         </is>
       </c>
       <c r="B648" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="C648" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D648" t="n">
         <v>1</v>
@@ -14033,11 +14033,11 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>We understand that [MASK] dynamics [MASK] constantly over time, but they don’t change rapidly.</t>
+          <t>Inflation, in fact, is under [MASK], and starting [MASK] come down.</t>
         </is>
       </c>
       <c r="B649" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C649" t="n">
         <v>2</v>
@@ -14054,14 +14054,14 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>The jobs [MASK] continues to be [MASK], with the unemployment rate [MASK] historic lows and with stronger wage gains.</t>
+          <t>Again, that’s not a forecast, I’[MASK] made [MASK] hypothesis, which would imply [MASK] improvement in unemployment.</t>
         </is>
       </c>
       <c r="B650" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C650" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D650" t="n">
         <v>1</v>
@@ -14075,14 +14075,14 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>The persistence [MASK] that into, into inflation over time is just not [MASK].</t>
+          <t>We understand that [MASK] dynamics [MASK] constantly over time, but they don’t change rapidly.</t>
         </is>
       </c>
       <c r="B651" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C651" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D651" t="n">
         <v>1</v>
@@ -14096,7 +14096,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>It was to do with, you know, strong monetary policy [MASK] fiscal [MASK] into an [MASK] [MASK] was recovering rapidly, and in [MASK] there were [MASK] supply-side barriers which effectively led to, you know, [MASK] certain parts of the economy, what you might call a vertical supply curve.</t>
+          <t>The jobs [MASK] continues to be [MASK], with the unemployment rate [MASK] historic lows and with stronger wage gains.</t>
         </is>
       </c>
       <c r="B652" t="n">
@@ -14117,14 +14117,14 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>If inflation remains higher during [MASK] course of 2022, [MASK] we may already have met [MASK] test by the time we reach liftoff.</t>
+          <t>The persistence [MASK] that into, into inflation over time is just not [MASK].</t>
         </is>
       </c>
       <c r="B653" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="C653" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D653" t="n">
         <v>1</v>
@@ -14138,14 +14138,14 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>And the way I would explain it is, is that inflation that’s too [MASK] will mean [MASK] interest [MASK] are lower.</t>
+          <t>It was to do with, you know, strong monetary policy [MASK] fiscal [MASK] into an [MASK] [MASK] was recovering rapidly, and in [MASK] there were [MASK] supply-side barriers which effectively led to, you know, [MASK] certain parts of the economy, what you might call a vertical supply curve.</t>
         </is>
       </c>
       <c r="B654" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C654" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D654" t="n">
         <v>1</v>
@@ -14159,14 +14159,14 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>And I think, [MASK] broadly, monetary policy is also supporting household spending and home buying by keeping the [MASK] [MASK] strong, keeping workers’ [MASK] rising, and keeping consumer confidence at high levels, where it currently [MASK].</t>
+          <t>If inflation remains higher during [MASK] course of 2022, [MASK] we may already have met [MASK] test by the time we reach liftoff.</t>
         </is>
       </c>
       <c r="B655" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="C655" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D655" t="n">
         <v>1</v>
@@ -14180,14 +14180,14 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>In any case, we, our job is to deliver price [MASK], and I think—you can think of price stability as an asset that [MASK] delivers large [MASK] [MASK] society over a long period of [MASK].</t>
+          <t>And the way I would explain it is, is that inflation that’s too [MASK] will mean [MASK] interest [MASK] are lower.</t>
         </is>
       </c>
       <c r="B656" t="n">
         <v>2022</v>
       </c>
       <c r="C656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D656" t="n">
         <v>1</v>
@@ -14201,14 +14201,14 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>It would consist of inflation [MASK]—plus productivity growth.</t>
+          <t>And I think, [MASK] broadly, monetary policy is also supporting household spending and home buying by keeping the [MASK] [MASK] strong, keeping workers’ [MASK] rising, and keeping consumer confidence at high levels, where it currently [MASK].</t>
         </is>
       </c>
       <c r="B657" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C657" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D657" t="n">
         <v>1</v>
@@ -14222,11 +14222,11 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>But again, our [MASK] forecast [MASK] one which is basically, as [MASK] pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this [MASK] of fiscal restraint; where unemployment [MASK] to [MASK] [MASK] a [MASK] pace as it has been since last September—[MASK] we have [MASK] some progress since last September; and inflation rises slowly towards 2 percent.</t>
+          <t>In any case, we, our job is to deliver price [MASK], and I think—you can think of price stability as an asset that [MASK] delivers large [MASK] [MASK] society over a long period of [MASK].</t>
         </is>
       </c>
       <c r="B658" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C658" t="n">
         <v>1</v>
@@ -14243,11 +14243,11 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>Again, while I do not shirk the responsibility [MASK] the Fed having to do what [MASK] can to meet its mandate, obviously, a [MASK] range of policies can [MASK] growth and employment, and I hope that there [MASK] be a [MASK] of actions that will complement [MASK] supplement the Federal Reserve’[MASK] efforts.</t>
+          <t>It would consist of inflation [MASK]—plus productivity growth.</t>
         </is>
       </c>
       <c r="B659" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="C659" t="n">
         <v>2</v>
@@ -14264,11 +14264,11 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>But you didn’t under the merely adverse scenario, [MASK] [MASK] an inflation shock followed by a quick rise [MASK] short-term rates.</t>
+          <t>But again, our [MASK] forecast [MASK] one which is basically, as [MASK] pointed out earlier by Mr. Hilsenrath, a moderately optimistic forecast, where growth picks up as we pass through this [MASK] of fiscal restraint; where unemployment [MASK] to [MASK] [MASK] a [MASK] pace as it has been since last September—[MASK] we have [MASK] some progress since last September; and inflation rises slowly towards 2 percent.</t>
         </is>
       </c>
       <c r="B660" t="n">
-        <v>2014</v>
+        <v>2018</v>
       </c>
       <c r="C660" t="n">
         <v>1</v>
@@ -14285,11 +14285,11 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>What monetary policy affects, primarily, is the state [MASK] the business [MASK], the amount of excess [MASK] or [MASK] extent of recession in the economy.</t>
+          <t>Again, while I do not shirk the responsibility [MASK] the Fed having to do what [MASK] can to meet its mandate, obviously, a [MASK] range of policies can [MASK] growth and employment, and I hope that there [MASK] be a [MASK] of actions that will complement [MASK] supplement the Federal Reserve’[MASK] efforts.</t>
         </is>
       </c>
       <c r="B661" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="C661" t="n">
         <v>2</v>
@@ -14306,14 +14306,14 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>[MASK] expect that to continue, and [MASK] would [MASK] also to see some improvement in the degree of part-[MASK] employment that’s for economic reasons.</t>
+          <t>But you didn’t under the merely adverse scenario, [MASK] [MASK] an inflation shock followed by a quick rise [MASK] short-term rates.</t>
         </is>
       </c>
       <c r="B662" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="C662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D662" t="n">
         <v>1</v>
@@ -14327,14 +14327,14 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>And as I [MASK] earlier, the unemployment decline last month was more than 100 percent accounted for [MASK] [MASK] in participation.</t>
+          <t>What monetary policy affects, primarily, is the state [MASK] the business [MASK], the amount of excess [MASK] or [MASK] extent of recession in the economy.</t>
         </is>
       </c>
       <c r="B663" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C663" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D663" t="n">
         <v>1</v>
@@ -14348,14 +14348,14 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>So that means a more prolonged shortfall of [MASK].</t>
+          <t>[MASK] expect that to continue, and [MASK] would [MASK] also to see some improvement in the degree of part-[MASK] employment that’s for economic reasons.</t>
         </is>
       </c>
       <c r="B664" t="n">
         <v>2019</v>
       </c>
       <c r="C664" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D664" t="n">
         <v>1</v>
@@ -14369,14 +14369,14 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>So we view [MASK] employment as the maximum sustainable level of employment, meaning it’s [MASK] so [MASK] that it will cause the economy to [MASK].</t>
+          <t>And as I [MASK] earlier, the unemployment decline last month was more than 100 percent accounted for [MASK] [MASK] in participation.</t>
         </is>
       </c>
       <c r="B665" t="n">
         <v>2019</v>
       </c>
       <c r="C665" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D665" t="n">
         <v>1</v>
@@ -14390,14 +14390,14 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>The central tendency of the [MASK] rate projections is slightly [MASK] than in the [MASK] projections and now stands at 6.0 to 6.1 percent at the [MASK] of this year.</t>
+          <t>So that means a more prolonged shortfall of [MASK].</t>
         </is>
       </c>
       <c r="B666" t="n">
-        <v>2012</v>
+        <v>2019</v>
       </c>
       <c r="C666" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D666" t="n">
         <v>1</v>
@@ -14411,14 +14411,14 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Admittedly, some of the [MASK] [MASK] is being eaten away by inflation.</t>
+          <t>So we view [MASK] employment as the maximum sustainable level of employment, meaning it’s [MASK] so [MASK] that it will cause the economy to [MASK].</t>
         </is>
       </c>
       <c r="B667" t="n">
         <v>2019</v>
       </c>
       <c r="C667" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D667" t="n">
         <v>1</v>
@@ -14432,14 +14432,14 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>[MASK] in terms of financial markets and monetary [MASK], we—as we say in our statement every cycle, we do take financial conditions into consideration [MASK] financial—[MASK] financial conditions do affect the broader [MASK], and they’[MASK] one of the many [MASK] that we take into account.</t>
+          <t>The central tendency of the [MASK] rate projections is slightly [MASK] than in the [MASK] projections and now stands at 6.0 to 6.1 percent at the [MASK] of this year.</t>
         </is>
       </c>
       <c r="B668" t="n">
-        <v>2016</v>
+        <v>2012</v>
       </c>
       <c r="C668" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D668" t="n">
         <v>1</v>
@@ -14453,14 +14453,14 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>[MASK] our plan as we do that is, as those purchases [MASK] to that level, we believe we can gradually reduce them, and we believe [MASK] can [MASK] gradually reduce repo as—as we reach an ample level, [MASK] we’re satisfying demand now more [MASK] underlying reserves from bill purchases rather [MASK] [MASK] repo.</t>
+          <t>Admittedly, some of the [MASK] [MASK] is being eaten away by inflation.</t>
         </is>
       </c>
       <c r="B669" t="n">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="C669" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D669" t="n">
         <v>1</v>
@@ -14474,11 +14474,11 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>So and, and, you know, the shorter-term [MASK] do tend to move around [MASK] on, for example, gasoline [MASK].</t>
+          <t>[MASK] in terms of financial markets and monetary [MASK], we—as we say in our statement every cycle, we do take financial conditions into consideration [MASK] financial—[MASK] financial conditions do affect the broader [MASK], and they’[MASK] one of the many [MASK] that we take into account.</t>
         </is>
       </c>
       <c r="B670" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="C670" t="n">
         <v>2</v>
@@ -14495,7 +14495,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>And, you know, we do want inflation to run [MASK] [MASK] 2 percent.</t>
+          <t>[MASK] our plan as we do that is, as those purchases [MASK] to that level, we believe we can gradually reduce them, and we believe [MASK] can [MASK] gradually reduce repo as—as we reach an ample level, [MASK] we’re satisfying demand now more [MASK] underlying reserves from bill purchases rather [MASK] [MASK] repo.</t>
         </is>
       </c>
       <c r="B671" t="n">
@@ -14516,14 +14516,14 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>When we [MASK] [MASK] employment, when we reach a state where labor market conditions are at maximum employment in [MASK] [MASK]’s judgment, it’s very possible that the inflation test will already be [MASK].</t>
+          <t>So and, and, you know, the shorter-term [MASK] do tend to move around [MASK] on, for example, gasoline [MASK].</t>
         </is>
       </c>
       <c r="B672" t="n">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="C672" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D672" t="n">
         <v>1</v>
@@ -14537,14 +14537,14 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>And obviously there are [MASK] from a [MASK] economy to every household in the economy, including savers, from having [MASK] better job market and a more [MASK] economy.</t>
+          <t>And, you know, we do want inflation to run [MASK] [MASK] 2 percent.</t>
         </is>
       </c>
       <c r="B673" t="n">
         <v>2011</v>
       </c>
       <c r="C673" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D673" t="n">
         <v>1</v>
@@ -14558,14 +14558,14 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>[MASK] of the things we’ve learned from our financial crisis and from a series of financial crises in [MASK] and around the [MASK] is that, very [MASK], when the economy takes a hit [MASK] falls into a [MASK], that productivity doesn’t pick [MASK] to pre-recession levels and that [MASK] looks like [MASK] is a permanent hit to the path of [MASK] output [MASK] the economy, which is called “[MASK].” And I [MASK] the question as to whether or not this [MASK] operate in the opposite direction as well.</t>
+          <t>When we [MASK] [MASK] employment, when we reach a state where labor market conditions are at maximum employment in [MASK] [MASK]’s judgment, it’s very possible that the inflation test will already be [MASK].</t>
         </is>
       </c>
       <c r="B674" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="C674" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D674" t="n">
         <v>1</v>
@@ -14579,14 +14579,14 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>I mean, it really depends [MASK] how long it takes for wages and, more [MASK] that, [MASK] [MASK] come down for inflation to come down.</t>
+          <t>And obviously there are [MASK] from a [MASK] economy to every household in the economy, including savers, from having [MASK] better job market and a more [MASK] economy.</t>
         </is>
       </c>
       <c r="B675" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="C675" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D675" t="n">
         <v>1</v>
@@ -14600,11 +14600,11 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage [MASK] to core inflation in April and [MASK].</t>
+          <t>[MASK] of the things we’ve learned from our financial crisis and from a series of financial crises in [MASK] and around the [MASK] is that, very [MASK], when the economy takes a hit [MASK] falls into a [MASK], that productivity doesn’t pick [MASK] to pre-recession levels and that [MASK] looks like [MASK] is a permanent hit to the path of [MASK] output [MASK] the economy, which is called “[MASK].” And I [MASK] the question as to whether or not this [MASK] operate in the opposite direction as well.</t>
         </is>
       </c>
       <c r="B676" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C676" t="n">
         <v>2</v>
@@ -14621,14 +14621,14 @@
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>1 Chair Yellen intended to say that “interest rate differentials globally [MASK] tend [MASK] induce capital flows [MASK] have [MASK] on exchange rates.” GREG ROBB.</t>
+          <t>I mean, it really depends [MASK] how long it takes for wages and, more [MASK] that, [MASK] [MASK] come down for inflation to come down.</t>
         </is>
       </c>
       <c r="B677" t="n">
         <v>2019</v>
       </c>
       <c r="C677" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D677" t="n">
         <v>1</v>
@@ -14642,11 +14642,11 @@
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Wage inflation has been [MASK] at 2 percent.</t>
+          <t>These base effects will contribute about 1 [MASK] point to headline inflation and about 0.7 percentage [MASK] to core inflation in April and [MASK].</t>
         </is>
       </c>
       <c r="B678" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C678" t="n">
         <v>2</v>
@@ -14663,11 +14663,11 @@
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>We also do see [MASK] different measures of slack in [MASK] labor market point [MASK] different assessments of just what maximum employment is.</t>
+          <t>1 Chair Yellen intended to say that “interest rate differentials globally [MASK] tend [MASK] induce capital flows [MASK] have [MASK] on exchange rates.” GREG ROBB.</t>
         </is>
       </c>
       <c r="B679" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C679" t="n">
         <v>2</v>
@@ -14684,14 +14684,14 @@
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>With unemployment still elevated and inflation below the [MASK]’s longer-[MASK] objective, [MASK] Committee is continuing its highly accommodative policies.</t>
+          <t>Wage inflation has been [MASK] at 2 percent.</t>
         </is>
       </c>
       <c r="B680" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="C680" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D680" t="n">
         <v>1</v>
@@ -14705,14 +14705,14 @@
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>As always, our [MASK] are guided [MASK] our congressional mandate to promote maximum employment [MASK] price stability.</t>
+          <t>We also do see [MASK] different measures of slack in [MASK] labor market point [MASK] different assessments of just what maximum employment is.</t>
         </is>
       </c>
       <c r="B681" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="C681" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D681" t="n">
         <v>1</v>
@@ -14726,14 +14726,14 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>Our mandate, sorry, is price [MASK].</t>
+          <t>With unemployment still elevated and inflation below the [MASK]’s longer-[MASK] objective, [MASK] Committee is continuing its highly accommodative policies.</t>
         </is>
       </c>
       <c r="B682" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C682" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D682" t="n">
         <v>1</v>
@@ -14747,14 +14747,14 @@
     <row r="683">
       <c r="A683" t="inlineStr">
         <is>
-          <t>So, as you know, the [MASK] [MASK] [MASK] we have is on the real economy: maximum employment and price stability.</t>
+          <t>As always, our [MASK] are guided [MASK] our congressional mandate to promote maximum employment [MASK] price stability.</t>
         </is>
       </c>
       <c r="B683" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C683" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D683" t="n">
         <v>1</v>
@@ -14768,14 +14768,14 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>More broadly, however, weaker demand, especially [MASK] [MASK] that have been most affected by the [MASK], has held down consumer prices, and [MASK], inflation is running well below our 2 [MASK] longer-run objective.</t>
+          <t>Our mandate, sorry, is price [MASK].</t>
         </is>
       </c>
       <c r="B684" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C684" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D684" t="n">
         <v>1</v>
@@ -14789,14 +14789,14 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>We, frankly, didn’t [MASK] get inflation back up to [MASK]—without seeing wages getting [MASK] of touch with—with where they should be, [MASK] that’s [MASK]—that’s the biggest thing we can do.</t>
+          <t>So, as you know, the [MASK] [MASK] [MASK] we have is on the real economy: maximum employment and price stability.</t>
         </is>
       </c>
       <c r="B685" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C685" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D685" t="n">
         <v>1</v>
@@ -14810,11 +14810,11 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>But in many countries around the Chair Yellen’s Press [MASK] FINAL world that are important commodity exporters, [MASK] decline we’ve seen [MASK] oil prices has had a depressing effect on their growth, their [MASK] with us and [MASK] trade partners, and caused problems that have had spillovers to [MASK] [MASK] economy as [MASK].</t>
+          <t>More broadly, however, weaker demand, especially [MASK] [MASK] that have been most affected by the [MASK], has held down consumer prices, and [MASK], inflation is running well below our 2 [MASK] longer-run objective.</t>
         </is>
       </c>
       <c r="B686" t="n">
-        <v>2018</v>
+        <v>2014</v>
       </c>
       <c r="C686" t="n">
         <v>0</v>
@@ -14831,14 +14831,14 @@
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>We have long said [MASK] the size of the balance [MASK] will be considered [MASK] when the balance sheet [MASK] once again at the [MASK] level consistent with conducting monetary policy efficiently and effectively.</t>
+          <t>We, frankly, didn’t [MASK] get inflation back up to [MASK]—without seeing wages getting [MASK] of touch with—with where they should be, [MASK] that’s [MASK]—that’s the biggest thing we can do.</t>
         </is>
       </c>
       <c r="B687" t="n">
         <v>2020</v>
       </c>
       <c r="C687" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D687" t="n">
         <v>1</v>
@@ -14852,14 +14852,14 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>If we—if we [MASK] inflation data and [MASK] that, clearly, transitory influences are [MASK] down [MASK], I do not want to say that we would respond to that.</t>
+          <t>But in many countries around the Chair Yellen’s Press [MASK] FINAL world that are important commodity exporters, [MASK] decline we’ve seen [MASK] oil prices has had a depressing effect on their growth, their [MASK] with us and [MASK] trade partners, and caused problems that have had spillovers to [MASK] [MASK] economy as [MASK].</t>
         </is>
       </c>
       <c r="B688" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="C688" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D688" t="n">
         <v>1</v>
@@ -14873,14 +14873,14 @@
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>And—but inflation expectations did [MASK] move [MASK] down here in the United States.</t>
+          <t>We have long said [MASK] the size of the balance [MASK] will be considered [MASK] when the balance sheet [MASK] once again at the [MASK] level consistent with conducting monetary policy efficiently and effectively.</t>
         </is>
       </c>
       <c r="B689" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="C689" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D689" t="n">
         <v>1</v>
@@ -14894,11 +14894,11 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>But [MASK]’s not easy to get a clear read on the implications of asset prices for [MASK] overall [MASK].</t>
+          <t>If we—if we [MASK] inflation data and [MASK] that, clearly, transitory influences are [MASK] down [MASK], I do not want to say that we would respond to that.</t>
         </is>
       </c>
       <c r="B690" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C690" t="n">
         <v>2</v>
@@ -14915,11 +14915,11 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>Well, [MASK]’re certainly [MASK] that we have been over-optimistic about out-year growth.</t>
+          <t>And—but inflation expectations did [MASK] move [MASK] down here in the United States.</t>
         </is>
       </c>
       <c r="B691" t="n">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="C691" t="n">
         <v>1</v>
@@ -14936,11 +14936,11 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>If you lay the crosscurrents on top of that—concerns about global [MASK] [MASK] trade developments—you [MASK] the full picture.</t>
+          <t>But [MASK]’s not easy to get a clear read on the implications of asset prices for [MASK] overall [MASK].</t>
         </is>
       </c>
       <c r="B692" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C692" t="n">
         <v>2</v>
@@ -14957,14 +14957,14 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>As [MASK] [MASK] step [MASK] enhancing the clarity of [MASK] communications, the Committee recently decided to begin publishing information about participants’ assessments of appropriate monetary policy—that is, the path of policy that each participant judges as most likely [MASK] foster mandate-consistent outcomes for [MASK] and inflation [MASK] the economy evolves [MASK] expected.</t>
+          <t>Well, [MASK]’re certainly [MASK] that we have been over-optimistic about out-year growth.</t>
         </is>
       </c>
       <c r="B693" t="n">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="C693" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D693" t="n">
         <v>1</v>
@@ -14978,14 +14978,14 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>The “[MASK] period” language is [MASK] on exactly those same points: “Extended period” is [MASK] on resource slack, [MASK] subdued inflation, and on stable inflation expectations.</t>
+          <t>If you lay the crosscurrents on top of that—concerns about global [MASK] [MASK] trade developments—you [MASK] the full picture.</t>
         </is>
       </c>
       <c r="B694" t="n">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="C694" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D694" t="n">
         <v>1</v>
@@ -14999,11 +14999,11 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>[MASK] those [MASK]’t—those, frankly, don’t carry significant implications in the long [MASK] for the—for inflation [MASK] for the American economy.</t>
+          <t>As [MASK] [MASK] step [MASK] enhancing the clarity of [MASK] communications, the Committee recently decided to begin publishing information about participants’ assessments of appropriate monetary policy—that is, the path of policy that each participant judges as most likely [MASK] foster mandate-consistent outcomes for [MASK] and inflation [MASK] the economy evolves [MASK] expected.</t>
         </is>
       </c>
       <c r="B695" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="C695" t="n">
         <v>2</v>
@@ -15020,11 +15020,11 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>[MASK] want to see lower unemployment.</t>
+          <t>The “[MASK] period” language is [MASK] on exactly those same points: “Extended period” is [MASK] on resource slack, [MASK] subdued inflation, and on stable inflation expectations.</t>
         </is>
       </c>
       <c r="B696" t="n">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="C696" t="n">
         <v>0</v>
@@ -15041,11 +15041,11 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>And I fully [MASK] it [MASK] return to solid growth and a solid labor [MASK] as well.</t>
+          <t>[MASK] those [MASK]’t—those, frankly, don’t carry significant implications in the long [MASK] for the—for inflation [MASK] for the American economy.</t>
         </is>
       </c>
       <c r="B697" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C697" t="n">
         <v>2</v>
@@ -15062,11 +15062,11 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>[MASK], [MASK] inflation below 2 percent, I think it’s appropriate that [MASK] labor market be that tight.</t>
+          <t>[MASK] want to see lower unemployment.</t>
         </is>
       </c>
       <c r="B698" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C698" t="n">
         <v>0</v>
@@ -15083,11 +15083,11 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>[MASK] I mentioned, once [MASK]—[MASK] you’[MASK], broadly speaking, in the range [MASK] neutral, I think it’[MASK] appropriate to be putting aside [MASK] estimates of [MASK] and be looking at what the incoming [MASK] are telling you about the outlook, updating your estimates of what neutral [MASK] be, of what the natural rate of unemployment might be, of the state [MASK] the economy, [MASK]—and letting that lead you to adjust your outlook and, therefore, your appropriate path for policy.</t>
+          <t>And I fully [MASK] it [MASK] return to solid growth and a solid labor [MASK] as well.</t>
         </is>
       </c>
       <c r="B699" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C699" t="n">
         <v>2</v>
@@ -15104,14 +15104,14 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>But to [MASK] extent that continues to [MASK] the case, [MASK] should make it easier to restore price stability.</t>
+          <t>[MASK], [MASK] inflation below 2 percent, I think it’s appropriate that [MASK] labor market be that tight.</t>
         </is>
       </c>
       <c r="B700" t="n">
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="C700" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D700" t="n">
         <v>1</v>
@@ -15125,11 +15125,11 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>We heard [MASK] today in the meeting [MASK] firms that might be government contractors [MASK] [MASK], you know, not sure about whether the contracts would still be in [MASK] come January and making employment decisions [MASK] on that.</t>
+          <t>[MASK] I mentioned, once [MASK]—[MASK] you’[MASK], broadly speaking, in the range [MASK] neutral, I think it’[MASK] appropriate to be putting aside [MASK] estimates of [MASK] and be looking at what the incoming [MASK] are telling you about the outlook, updating your estimates of what neutral [MASK] be, of what the natural rate of unemployment might be, of the state [MASK] the economy, [MASK]—and letting that lead you to adjust your outlook and, therefore, your appropriate path for policy.</t>
         </is>
       </c>
       <c r="B701" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="C701" t="n">
         <v>2</v>
@@ -15146,11 +15146,11 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Inflation [MASK] moved up in recent months, mainly [MASK] higher prices for some commodities and imported [MASK].</t>
+          <t>But to [MASK] extent that continues to [MASK] the case, [MASK] should make it easier to restore price stability.</t>
         </is>
       </c>
       <c r="B702" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="C702" t="n">
         <v>1</v>
@@ -15167,14 +15167,14 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>By contrast, raising rates too slowly [MASK] raise the risk that monetary policy would need to tighten abruptly down [MASK] [MASK], which could [MASK] the economic expansion.</t>
+          <t>We heard [MASK] today in the meeting [MASK] firms that might be government contractors [MASK] [MASK], you know, not sure about whether the contracts would still be in [MASK] come January and making employment decisions [MASK] on that.</t>
         </is>
       </c>
       <c r="B703" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="C703" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D703" t="n">
         <v>1</v>
@@ -15188,11 +15188,11 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>But, I would say, overall, we’re trying to sustain the [MASK] [MASK] keep, you know, close to our statutory goals, which are [MASK] [MASK] and stable prices.</t>
+          <t>Inflation [MASK] moved up in recent months, mainly [MASK] higher prices for some commodities and imported [MASK].</t>
         </is>
       </c>
       <c r="B704" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C704" t="n">
         <v>1</v>
@@ -15209,14 +15209,14 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>But I do think that—and [MASK] do think also that unemployment [MASK] benefits will run out in September, [MASK] to [MASK] extent that’s a factor, which is not [MASK], it will no longer [MASK] a factor fairly soon.</t>
+          <t>By contrast, raising rates too slowly [MASK] raise the risk that monetary policy would need to tighten abruptly down [MASK] [MASK], which could [MASK] the economic expansion.</t>
         </is>
       </c>
       <c r="B705" t="n">
-        <v>2011</v>
+        <v>2022</v>
       </c>
       <c r="C705" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D705" t="n">
         <v>1</v>
@@ -15230,14 +15230,14 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>We had a 10 percent [MASK] rate, and our congressional mandate is maximum employment and price [MASK].</t>
+          <t>But, I would say, overall, we’re trying to sustain the [MASK] [MASK] keep, you know, close to our statutory goals, which are [MASK] [MASK] and stable prices.</t>
         </is>
       </c>
       <c r="B706" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="C706" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D706" t="n">
         <v>1</v>
@@ -15251,19 +15251,61 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
+          <t>But I do think that—and [MASK] do think also that unemployment [MASK] benefits will run out in September, [MASK] to [MASK] extent that’s a factor, which is not [MASK], it will no longer [MASK] a factor fairly soon.</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C707" t="n">
+        <v>2</v>
+      </c>
+      <c r="D707" t="n">
+        <v>1</v>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>masking</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>We had a 10 percent [MASK] rate, and our congressional mandate is maximum employment and price [MASK].</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C708" t="n">
+        <v>0</v>
+      </c>
+      <c r="D708" t="n">
+        <v>1</v>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>masking</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
           <t>That is a positive [MASK] growth.</t>
         </is>
       </c>
-      <c r="B707" t="n">
+      <c r="B709" t="n">
         <v>2016</v>
       </c>
-      <c r="C707" t="n">
-        <v>2</v>
-      </c>
-      <c r="D707" t="n">
-        <v>1</v>
-      </c>
-      <c r="E707" t="inlineStr">
+      <c r="C709" t="n">
+        <v>2</v>
+      </c>
+      <c r="D709" t="n">
+        <v>1</v>
+      </c>
+      <c r="E709" t="inlineStr">
         <is>
           <t>masking</t>
         </is>
